--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH105"/>
+  <dimension ref="A1:BH109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22177,15 +22177,11 @@
           <t>5 050</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G102" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -22295,15 +22291,11 @@
           <t>4 468</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -22413,15 +22405,11 @@
           <t>2 955</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -22531,15 +22519,11 @@
           <t>1 707</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -22621,6 +22605,1034 @@
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>09.08.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>16 917</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>7 139</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Monza</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="BC106" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>09.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Genoa</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr"/>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="BC107" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>5 850</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Udinese</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Avellino</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>pazienza michele</t>
+        </is>
+      </c>
+      <c r="BC108" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Sassuolo</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr"/>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="BC109" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH109"/>
+  <dimension ref="A1:BL141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,26 @@
           <t>red_cards_away</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -938,6 +958,10 @@
       </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1152,6 +1176,10 @@
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1366,6 +1394,10 @@
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1580,6 +1612,10 @@
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1794,6 +1830,10 @@
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2008,6 +2048,10 @@
       </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2218,6 +2262,10 @@
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2432,6 +2480,10 @@
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2650,6 +2702,10 @@
       <c r="BH10" t="n">
         <v>1</v>
       </c>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2864,6 +2920,10 @@
       </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3078,6 +3138,10 @@
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3292,6 +3356,10 @@
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3502,6 +3570,10 @@
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3720,6 +3792,10 @@
       <c r="BH15" t="n">
         <v>0</v>
       </c>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3934,6 +4010,10 @@
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -4148,6 +4228,10 @@
       </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -4366,6 +4450,10 @@
       <c r="BH18" t="n">
         <v>1</v>
       </c>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4584,6 +4672,10 @@
       <c r="BH19" t="n">
         <v>0</v>
       </c>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4798,6 +4890,10 @@
       </c>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -5012,6 +5108,10 @@
       </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -5226,6 +5326,10 @@
       </c>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5440,6 +5544,10 @@
       </c>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5654,6 +5762,10 @@
       </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5868,6 +5980,10 @@
       </c>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -6082,6 +6198,10 @@
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -6296,6 +6416,10 @@
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -6514,6 +6638,10 @@
       <c r="BH28" t="n">
         <v>0</v>
       </c>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6728,6 +6856,10 @@
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6942,6 +7074,10 @@
       </c>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -7156,6 +7292,10 @@
       </c>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7366,6 +7506,10 @@
       </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -7576,6 +7720,10 @@
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -7790,6 +7938,10 @@
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -8004,6 +8156,10 @@
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -8218,6 +8374,10 @@
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -8432,6 +8592,10 @@
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8646,6 +8810,10 @@
       </c>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8864,6 +9032,10 @@
       <c r="BH39" t="n">
         <v>0</v>
       </c>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -9078,6 +9250,10 @@
       </c>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -9292,6 +9468,10 @@
       </c>
       <c r="BG41" t="inlineStr"/>
       <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -9506,6 +9686,10 @@
       </c>
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -9720,6 +9904,10 @@
       </c>
       <c r="BG43" t="inlineStr"/>
       <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -9934,6 +10122,10 @@
       </c>
       <c r="BG44" t="inlineStr"/>
       <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -10148,6 +10340,10 @@
       </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -10362,6 +10558,10 @@
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -10580,6 +10780,10 @@
       <c r="BH47" t="n">
         <v>0</v>
       </c>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -10794,6 +10998,10 @@
       <c r="BH48" t="n">
         <v>1</v>
       </c>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -11008,6 +11216,10 @@
       </c>
       <c r="BG49" t="inlineStr"/>
       <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -11222,6 +11434,10 @@
       </c>
       <c r="BG50" t="inlineStr"/>
       <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -11436,6 +11652,10 @@
       </c>
       <c r="BG51" t="inlineStr"/>
       <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -11650,6 +11870,10 @@
       </c>
       <c r="BG52" t="inlineStr"/>
       <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -11856,6 +12080,10 @@
       </c>
       <c r="BG53" t="inlineStr"/>
       <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -12074,6 +12302,10 @@
       <c r="BH54" t="n">
         <v>1</v>
       </c>
+      <c r="BI54" t="inlineStr"/>
+      <c r="BJ54" t="inlineStr"/>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -12288,6 +12520,10 @@
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -12498,6 +12734,10 @@
       </c>
       <c r="BG56" t="inlineStr"/>
       <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -12712,6 +12952,10 @@
       </c>
       <c r="BG57" t="inlineStr"/>
       <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr"/>
+      <c r="BJ57" t="inlineStr"/>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -12926,6 +13170,10 @@
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -13140,6 +13388,10 @@
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -13354,6 +13606,10 @@
       </c>
       <c r="BG60" t="inlineStr"/>
       <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -13568,6 +13824,10 @@
       </c>
       <c r="BG61" t="inlineStr"/>
       <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -13782,6 +14042,10 @@
       </c>
       <c r="BG62" t="inlineStr"/>
       <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -13996,6 +14260,10 @@
       </c>
       <c r="BG63" t="inlineStr"/>
       <c r="BH63" t="inlineStr"/>
+      <c r="BI63" t="inlineStr"/>
+      <c r="BJ63" t="inlineStr"/>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -14210,6 +14478,10 @@
       </c>
       <c r="BG64" t="inlineStr"/>
       <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr"/>
+      <c r="BJ64" t="inlineStr"/>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -14424,6 +14696,10 @@
       </c>
       <c r="BG65" t="inlineStr"/>
       <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr"/>
+      <c r="BJ65" t="inlineStr"/>
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -14638,6 +14914,10 @@
       </c>
       <c r="BG66" t="inlineStr"/>
       <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -14852,6 +15132,10 @@
       </c>
       <c r="BG67" t="inlineStr"/>
       <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr"/>
+      <c r="BJ67" t="inlineStr"/>
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -15070,6 +15354,10 @@
       <c r="BH68" t="n">
         <v>0</v>
       </c>
+      <c r="BI68" t="inlineStr"/>
+      <c r="BJ68" t="inlineStr"/>
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -15284,6 +15572,10 @@
       </c>
       <c r="BG69" t="inlineStr"/>
       <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
+      <c r="BJ69" t="inlineStr"/>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -15502,6 +15794,10 @@
       <c r="BH70" t="n">
         <v>0</v>
       </c>
+      <c r="BI70" t="inlineStr"/>
+      <c r="BJ70" t="inlineStr"/>
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -15716,6 +16012,10 @@
       </c>
       <c r="BG71" t="inlineStr"/>
       <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -15930,6 +16230,10 @@
       </c>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -16144,6 +16448,10 @@
       </c>
       <c r="BG73" t="inlineStr"/>
       <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -16358,6 +16666,10 @@
       </c>
       <c r="BG74" t="inlineStr"/>
       <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr"/>
+      <c r="BJ74" t="inlineStr"/>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -16572,6 +16884,10 @@
       </c>
       <c r="BG75" t="inlineStr"/>
       <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr"/>
+      <c r="BJ75" t="inlineStr"/>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -16786,6 +17102,10 @@
       </c>
       <c r="BG76" t="inlineStr"/>
       <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="inlineStr"/>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -17000,6 +17320,10 @@
       </c>
       <c r="BG77" t="inlineStr"/>
       <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="inlineStr"/>
+      <c r="BJ77" t="inlineStr"/>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -17214,6 +17538,10 @@
       </c>
       <c r="BG78" t="inlineStr"/>
       <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr"/>
+      <c r="BJ78" t="inlineStr"/>
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -17428,6 +17756,10 @@
       </c>
       <c r="BG79" t="inlineStr"/>
       <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr"/>
+      <c r="BJ79" t="inlineStr"/>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -17642,6 +17974,10 @@
       </c>
       <c r="BG80" t="inlineStr"/>
       <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -17860,6 +18196,10 @@
       <c r="BH81" t="n">
         <v>1</v>
       </c>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -18074,6 +18414,10 @@
       </c>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -18288,6 +18632,10 @@
       </c>
       <c r="BG83" t="inlineStr"/>
       <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -18502,6 +18850,10 @@
       </c>
       <c r="BG84" t="inlineStr"/>
       <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -18716,6 +19068,10 @@
       </c>
       <c r="BG85" t="inlineStr"/>
       <c r="BH85" t="inlineStr"/>
+      <c r="BI85" t="inlineStr"/>
+      <c r="BJ85" t="inlineStr"/>
+      <c r="BK85" t="inlineStr"/>
+      <c r="BL85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -18930,6 +19286,10 @@
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -19144,6 +19504,10 @@
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="inlineStr"/>
+      <c r="BI87" t="inlineStr"/>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -19358,6 +19722,10 @@
       </c>
       <c r="BG88" t="inlineStr"/>
       <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -19572,6 +19940,10 @@
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -19786,6 +20158,10 @@
       </c>
       <c r="BG90" t="inlineStr"/>
       <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -20004,6 +20380,10 @@
       <c r="BH91" t="n">
         <v>1</v>
       </c>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -20218,6 +20598,10 @@
       </c>
       <c r="BG92" t="inlineStr"/>
       <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -20432,6 +20816,10 @@
       </c>
       <c r="BG93" t="inlineStr"/>
       <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -20646,6 +21034,10 @@
       </c>
       <c r="BG94" t="inlineStr"/>
       <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -20860,6 +21252,10 @@
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -21078,6 +21474,10 @@
       <c r="BH96" t="n">
         <v>0</v>
       </c>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -21292,6 +21692,10 @@
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
+      <c r="BI97" t="inlineStr"/>
+      <c r="BJ97" t="inlineStr"/>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -21506,6 +21910,10 @@
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -21720,6 +22128,10 @@
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -21934,6 +22346,10 @@
       </c>
       <c r="BG100" t="inlineStr"/>
       <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -22148,6 +22564,10 @@
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -22262,6 +22682,10 @@
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -22376,6 +22800,10 @@
       </c>
       <c r="BG103" t="inlineStr"/>
       <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -22490,6 +22918,10 @@
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -22604,6 +23036,10 @@
       </c>
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -22638,15 +23074,11 @@
           <t>7 139</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -22681,165 +23113,101 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="AP106" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AT106" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q106" t="n">
+        <v>10</v>
+      </c>
+      <c r="R106" t="n">
+        <v>3</v>
+      </c>
+      <c r="S106" t="n">
+        <v>4</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>6</v>
+      </c>
+      <c r="V106" t="n">
+        <v>3</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>565</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>436</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>514</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>375</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>103</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>63</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>1</v>
       </c>
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr"/>
@@ -22879,6 +23247,10 @@
       </c>
       <c r="BG106" t="inlineStr"/>
       <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -22913,15 +23285,11 @@
           <t>22 000</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -22956,147 +23324,91 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q107" t="n">
+        <v>19</v>
+      </c>
+      <c r="R107" t="n">
+        <v>10</v>
+      </c>
+      <c r="S107" t="n">
+        <v>13</v>
+      </c>
+      <c r="T107" t="n">
+        <v>5</v>
+      </c>
+      <c r="U107" t="n">
+        <v>6</v>
+      </c>
+      <c r="V107" t="n">
+        <v>5</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>3</v>
       </c>
       <c r="AM107" t="inlineStr"/>
       <c r="AN107" t="inlineStr"/>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AT107" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="AO107" t="n">
+        <v>366</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>296</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>134</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>69</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>67</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>40</v>
       </c>
       <c r="AU107" t="inlineStr"/>
       <c r="AV107" t="inlineStr"/>
@@ -23138,6 +23450,10 @@
       </c>
       <c r="BG107" t="inlineStr"/>
       <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -23172,15 +23488,11 @@
           <t>5 850</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -23215,139 +23527,87 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q108" t="n">
+        <v>16</v>
+      </c>
+      <c r="R108" t="n">
+        <v>4</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>9</v>
+      </c>
+      <c r="V108" t="n">
+        <v>3</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>2</v>
       </c>
       <c r="AM108" t="inlineStr"/>
       <c r="AN108" t="inlineStr"/>
       <c r="AO108" t="inlineStr"/>
       <c r="AP108" t="inlineStr"/>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT108" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="AQ108" t="n">
+        <v>124</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>28</v>
       </c>
       <c r="AU108" t="inlineStr"/>
       <c r="AV108" t="inlineStr"/>
@@ -23389,6 +23649,10 @@
       </c>
       <c r="BG108" t="inlineStr"/>
       <c r="BH108" t="inlineStr"/>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -23423,15 +23687,11 @@
           <t>2 000</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -23466,105 +23726,65 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q109" t="n">
+        <v>15</v>
+      </c>
+      <c r="R109" t="n">
+        <v>5</v>
+      </c>
+      <c r="S109" t="n">
+        <v>9</v>
+      </c>
+      <c r="T109" t="n">
+        <v>2</v>
+      </c>
+      <c r="U109" t="n">
+        <v>6</v>
+      </c>
+      <c r="V109" t="n">
+        <v>3</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>9</v>
       </c>
       <c r="AK109" t="inlineStr"/>
       <c r="AL109" t="inlineStr"/>
@@ -23572,25 +23792,17 @@
       <c r="AN109" t="inlineStr"/>
       <c r="AO109" t="inlineStr"/>
       <c r="AP109" t="inlineStr"/>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AT109" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="AQ109" t="n">
+        <v>120</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>108</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>56</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>44</v>
       </c>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
@@ -23632,6 +23844,6954 @@
       </c>
       <c r="BG109" t="inlineStr"/>
       <c r="BH109" t="inlineStr"/>
+      <c r="BI109" t="inlineStr"/>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>12</v>
+      </c>
+      <c r="R110" t="n">
+        <v>13</v>
+      </c>
+      <c r="S110" t="n">
+        <v>2</v>
+      </c>
+      <c r="T110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U110" t="n">
+        <v>8</v>
+      </c>
+      <c r="V110" t="n">
+        <v>8</v>
+      </c>
+      <c r="W110" t="n">
+        <v>2</v>
+      </c>
+      <c r="X110" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>335</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>443</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>258</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>363</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>118</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>37</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>76</v>
+      </c>
+      <c r="AU110" t="inlineStr"/>
+      <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>de rossi daniele</t>
+        </is>
+      </c>
+      <c r="BC110" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
+      <c r="BI110" t="inlineStr"/>
+      <c r="BJ110" t="inlineStr"/>
+      <c r="BK110" t="inlineStr"/>
+      <c r="BL110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>13</v>
+      </c>
+      <c r="R111" t="n">
+        <v>11</v>
+      </c>
+      <c r="S111" t="n">
+        <v>6</v>
+      </c>
+      <c r="T111" t="n">
+        <v>3</v>
+      </c>
+      <c r="U111" t="n">
+        <v>6</v>
+      </c>
+      <c r="V111" t="n">
+        <v>5</v>
+      </c>
+      <c r="W111" t="n">
+        <v>1</v>
+      </c>
+      <c r="X111" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>596</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>288</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>542</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>233</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>101</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>68</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU111" t="inlineStr"/>
+      <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr"/>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BC111" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr"/>
+      <c r="BH111" t="inlineStr"/>
+      <c r="BI111" t="inlineStr"/>
+      <c r="BJ111" t="inlineStr"/>
+      <c r="BK111" t="inlineStr"/>
+      <c r="BL111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Caputi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>26 418</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>22</v>
+      </c>
+      <c r="R112" t="n">
+        <v>4</v>
+      </c>
+      <c r="S112" t="n">
+        <v>7</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2</v>
+      </c>
+      <c r="U112" t="n">
+        <v>7</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>8</v>
+      </c>
+      <c r="X112" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>526</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>177</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>459</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>119</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>143</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>74</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>32</v>
+      </c>
+      <c r="AU112" t="inlineStr"/>
+      <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="BC112" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr"/>
+      <c r="BH112" t="inlineStr"/>
+      <c r="BI112" t="inlineStr"/>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>8</v>
+      </c>
+      <c r="R113" t="n">
+        <v>15</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="n">
+        <v>5</v>
+      </c>
+      <c r="U113" t="n">
+        <v>3</v>
+      </c>
+      <c r="V113" t="n">
+        <v>6</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>303</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>594</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>199</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>494</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>91</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>56</v>
+      </c>
+      <c r="AU113" t="inlineStr"/>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="BC113" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr"/>
+      <c r="BH113" t="inlineStr"/>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Maresca F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>20</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6</v>
+      </c>
+      <c r="S114" t="n">
+        <v>6</v>
+      </c>
+      <c r="T114" t="n">
+        <v>3</v>
+      </c>
+      <c r="U114" t="n">
+        <v>8</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
+      <c r="W114" t="n">
+        <v>6</v>
+      </c>
+      <c r="X114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>522</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>451</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>451</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>357</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>124</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>53</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>106</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="BC114" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>9</v>
+      </c>
+      <c r="R115" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>4</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1</v>
+      </c>
+      <c r="W115" t="n">
+        <v>4</v>
+      </c>
+      <c r="X115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>279</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>465</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>182</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>338</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>120</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>56</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="BC115" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr"/>
+      <c r="BH115" t="inlineStr"/>
+      <c r="BI115" t="inlineStr"/>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>10</v>
+      </c>
+      <c r="R116" t="n">
+        <v>14</v>
+      </c>
+      <c r="S116" t="n">
+        <v>6</v>
+      </c>
+      <c r="T116" t="n">
+        <v>9</v>
+      </c>
+      <c r="U116" t="n">
+        <v>4</v>
+      </c>
+      <c r="V116" t="n">
+        <v>3</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>488</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>173</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>430</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>76</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>38</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="BC116" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr"/>
+      <c r="BI116" t="inlineStr"/>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>13</v>
+      </c>
+      <c r="R117" t="n">
+        <v>14</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="n">
+        <v>7</v>
+      </c>
+      <c r="U117" t="n">
+        <v>4</v>
+      </c>
+      <c r="V117" t="n">
+        <v>3</v>
+      </c>
+      <c r="W117" t="n">
+        <v>4</v>
+      </c>
+      <c r="X117" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>263</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>416</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>354</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>79</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="BC117" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="inlineStr"/>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>12.08.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pezzuto I.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Cagliari</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>21</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6</v>
+      </c>
+      <c r="S118" t="n">
+        <v>8</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" t="n">
+        <v>10</v>
+      </c>
+      <c r="V118" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" t="n">
+        <v>3</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>452</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>417</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>375</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>321</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>125</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="BC118" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>12.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Rutella D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>6 905</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Salernitana</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>11</v>
+      </c>
+      <c r="R119" t="n">
+        <v>15</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="n">
+        <v>7</v>
+      </c>
+      <c r="U119" t="n">
+        <v>4</v>
+      </c>
+      <c r="V119" t="n">
+        <v>2</v>
+      </c>
+      <c r="W119" t="n">
+        <v>2</v>
+      </c>
+      <c r="X119" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>494</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>332</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>440</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>282</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>140</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>57</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>47</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BC119" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>12.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Perri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Lecce</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>19</v>
+      </c>
+      <c r="R120" t="n">
+        <v>3</v>
+      </c>
+      <c r="S120" t="n">
+        <v>9</v>
+      </c>
+      <c r="T120" t="n">
+        <v>2</v>
+      </c>
+      <c r="U120" t="n">
+        <v>6</v>
+      </c>
+      <c r="V120" t="n">
+        <v>1</v>
+      </c>
+      <c r="W120" t="n">
+        <v>4</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>333</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>596</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>286</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>530</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>113</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>63</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>77</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="BC120" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>12.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>9 384</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Pisa
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>5</v>
+      </c>
+      <c r="R121" t="n">
+        <v>16</v>
+      </c>
+      <c r="S121" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" t="n">
+        <v>4</v>
+      </c>
+      <c r="U121" t="n">
+        <v>2</v>
+      </c>
+      <c r="V121" t="n">
+        <v>9</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>483</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>321</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>406</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>91</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>110</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>31</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BC121" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>11.08.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>12 035</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Torino</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>8</v>
+      </c>
+      <c r="R122" t="n">
+        <v>15</v>
+      </c>
+      <c r="S122" t="n">
+        <v>2</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4</v>
+      </c>
+      <c r="U122" t="n">
+        <v>5</v>
+      </c>
+      <c r="V122" t="n">
+        <v>5</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>535</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>355</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>471</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>302</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>151</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>130</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>119</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BC122" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>11.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>14 196</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Sampdoria</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>11</v>
+      </c>
+      <c r="R123" t="n">
+        <v>11</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3</v>
+      </c>
+      <c r="T123" t="n">
+        <v>5</v>
+      </c>
+      <c r="U123" t="n">
+        <v>5</v>
+      </c>
+      <c r="V123" t="n">
+        <v>5</v>
+      </c>
+      <c r="W123" t="n">
+        <v>3</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>374</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>303</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>424</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>81</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>129</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>51</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>roberts osian</t>
+        </is>
+      </c>
+      <c r="BC123" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="inlineStr"/>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>11.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>5 034</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Palermo
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>17</v>
+      </c>
+      <c r="R124" t="n">
+        <v>13</v>
+      </c>
+      <c r="S124" t="n">
+        <v>4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>4</v>
+      </c>
+      <c r="U124" t="n">
+        <v>8</v>
+      </c>
+      <c r="V124" t="n">
+        <v>5</v>
+      </c>
+      <c r="W124" t="n">
+        <v>5</v>
+      </c>
+      <c r="X124" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>361</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>427</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>289</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>363</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>108</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>33</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BC124" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>11.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Caputi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>4 310</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Brescia</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>9</v>
+      </c>
+      <c r="R125" t="n">
+        <v>18</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="n">
+        <v>8</v>
+      </c>
+      <c r="U125" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" t="n">
+        <v>8</v>
+      </c>
+      <c r="W125" t="n">
+        <v>1</v>
+      </c>
+      <c r="X125" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>508</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>242</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>437</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>78</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>135</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>82</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BC125" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>10.08.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>52 000</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Napoli</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>28</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>6</v>
+      </c>
+      <c r="T126" t="n">
+        <v>2</v>
+      </c>
+      <c r="U126" t="n">
+        <v>11</v>
+      </c>
+      <c r="V126" t="n">
+        <v>1</v>
+      </c>
+      <c r="W126" t="n">
+        <v>11</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>690</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>628</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>168</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>187</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>59</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="BC126" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Arena A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1 738</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Empoli</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>22</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>8</v>
+      </c>
+      <c r="T127" t="n">
+        <v>3</v>
+      </c>
+      <c r="U127" t="n">
+        <v>12</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" t="n">
+        <v>2</v>
+      </c>
+      <c r="X127" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>472</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>362</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>415</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>303</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>86</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>32</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr"/>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BC127" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>10.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7 048</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Cesena
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>11</v>
+      </c>
+      <c r="R128" t="n">
+        <v>13</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>4</v>
+      </c>
+      <c r="U128" t="n">
+        <v>2</v>
+      </c>
+      <c r="V128" t="n">
+        <v>5</v>
+      </c>
+      <c r="W128" t="n">
+        <v>6</v>
+      </c>
+      <c r="X128" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>382</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>378</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>317</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>299</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>106</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>81</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>48</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="BC128" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>10.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Galipo S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>3 724</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Cremonese</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>13</v>
+      </c>
+      <c r="R129" t="n">
+        <v>11</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3</v>
+      </c>
+      <c r="T129" t="n">
+        <v>4</v>
+      </c>
+      <c r="U129" t="n">
+        <v>8</v>
+      </c>
+      <c r="V129" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" t="n">
+        <v>2</v>
+      </c>
+      <c r="X129" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>492</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>305</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>413</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>238</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>104</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>63</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>63</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="BC129" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>773</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>9</v>
+      </c>
+      <c r="R130" t="n">
+        <v>12</v>
+      </c>
+      <c r="S130" t="n">
+        <v>4</v>
+      </c>
+      <c r="T130" t="n">
+        <v>6</v>
+      </c>
+      <c r="U130" t="n">
+        <v>5</v>
+      </c>
+      <c r="V130" t="n">
+        <v>4</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>472</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>466</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>411</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>412</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>108</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>105</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>49</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>57</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW130" t="inlineStr"/>
+      <c r="AX130" t="inlineStr"/>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BC130" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>27</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>23 860</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>11 382</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>14</v>
+      </c>
+      <c r="R131" t="n">
+        <v>10</v>
+      </c>
+      <c r="S131" t="n">
+        <v>8</v>
+      </c>
+      <c r="T131" t="n">
+        <v>4</v>
+      </c>
+      <c r="U131" t="n">
+        <v>4</v>
+      </c>
+      <c r="V131" t="n">
+        <v>6</v>
+      </c>
+      <c r="W131" t="n">
+        <v>2</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>415</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>572</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>325</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>470</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>117</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>147</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>59</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="BC131" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>6 840</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>15</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7</v>
+      </c>
+      <c r="S132" t="n">
+        <v>6</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>8</v>
+      </c>
+      <c r="V132" t="n">
+        <v>4</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>262</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>528</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>178</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>438</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>129</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW132" t="inlineStr"/>
+      <c r="AX132" t="inlineStr"/>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="BC132" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>22</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>20</v>
+      </c>
+      <c r="R133" t="n">
+        <v>17</v>
+      </c>
+      <c r="S133" t="n">
+        <v>12</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4</v>
+      </c>
+      <c r="U133" t="n">
+        <v>4</v>
+      </c>
+      <c r="V133" t="n">
+        <v>9</v>
+      </c>
+      <c r="W133" t="n">
+        <v>4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>376</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>449</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>294</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>375</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>102</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>111</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>47</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW133" t="inlineStr"/>
+      <c r="AX133" t="inlineStr"/>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="BC133" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Arena A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>12</v>
+      </c>
+      <c r="R134" t="n">
+        <v>13</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2</v>
+      </c>
+      <c r="V134" t="n">
+        <v>8</v>
+      </c>
+      <c r="W134" t="n">
+        <v>4</v>
+      </c>
+      <c r="X134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>265</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>616</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>204</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>541</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>101</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>96</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>51</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW134" t="inlineStr"/>
+      <c r="AX134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="BC134" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
+      <c r="BI134" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>20 957</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>16</v>
+      </c>
+      <c r="R135" t="n">
+        <v>13</v>
+      </c>
+      <c r="S135" t="n">
+        <v>4</v>
+      </c>
+      <c r="T135" t="n">
+        <v>6</v>
+      </c>
+      <c r="U135" t="n">
+        <v>8</v>
+      </c>
+      <c r="V135" t="n">
+        <v>5</v>
+      </c>
+      <c r="W135" t="n">
+        <v>4</v>
+      </c>
+      <c r="X135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>376</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>285</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>301</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>216</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>69</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>33</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="BC135" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr"/>
+      <c r="BI135" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>8 770</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>19</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6</v>
+      </c>
+      <c r="S136" t="n">
+        <v>4</v>
+      </c>
+      <c r="T136" t="n">
+        <v>3</v>
+      </c>
+      <c r="U136" t="n">
+        <v>7</v>
+      </c>
+      <c r="V136" t="n">
+        <v>2</v>
+      </c>
+      <c r="W136" t="n">
+        <v>8</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>364</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>269</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>57</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW136" t="inlineStr"/>
+      <c r="AX136" t="inlineStr"/>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BC136" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
+      <c r="BI136" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>31</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>12 509</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>15</v>
+      </c>
+      <c r="R137" t="n">
+        <v>8</v>
+      </c>
+      <c r="S137" t="n">
+        <v>7</v>
+      </c>
+      <c r="T137" t="n">
+        <v>3</v>
+      </c>
+      <c r="U137" t="n">
+        <v>5</v>
+      </c>
+      <c r="V137" t="n">
+        <v>2</v>
+      </c>
+      <c r="W137" t="n">
+        <v>3</v>
+      </c>
+      <c r="X137" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>517</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>225</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>442</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>156</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW137" t="inlineStr"/>
+      <c r="AX137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="BC137" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
+      <c r="BI137" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Perri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>3 512</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>9</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3</v>
+      </c>
+      <c r="T138" t="n">
+        <v>2</v>
+      </c>
+      <c r="U138" t="n">
+        <v>4</v>
+      </c>
+      <c r="V138" t="n">
+        <v>2</v>
+      </c>
+      <c r="W138" t="n">
+        <v>2</v>
+      </c>
+      <c r="X138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>615</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>289</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>554</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>225</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>133</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW138" t="inlineStr"/>
+      <c r="AX138" t="inlineStr"/>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="BC138" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>5 317</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>18</v>
+      </c>
+      <c r="R139" t="n">
+        <v>10</v>
+      </c>
+      <c r="S139" t="n">
+        <v>6</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>9</v>
+      </c>
+      <c r="V139" t="n">
+        <v>5</v>
+      </c>
+      <c r="W139" t="n">
+        <v>3</v>
+      </c>
+      <c r="X139" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>317</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>542</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>259</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>479</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>119</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>57</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW139" t="inlineStr"/>
+      <c r="AX139" t="inlineStr"/>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BC139" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
+      <c r="BI139" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>19.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="AN140" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AU140" t="inlineStr"/>
+      <c r="AV140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr"/>
+      <c r="AX140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="BC140" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG140" t="inlineStr"/>
+      <c r="BH140" t="inlineStr"/>
+      <c r="BI140" t="inlineStr"/>
+      <c r="BJ140" t="inlineStr"/>
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>19.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>28 719</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AN141" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AU141" t="inlineStr"/>
+      <c r="AV141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr"/>
+      <c r="AX141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="BC141" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG141" t="inlineStr"/>
+      <c r="BH141" t="inlineStr"/>
+      <c r="BI141" t="inlineStr"/>
+      <c r="BJ141" t="inlineStr"/>
+      <c r="BK141" t="inlineStr"/>
+      <c r="BL141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL141"/>
+  <dimension ref="A1:BL145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30270,15 +30270,11 @@
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -30300,15 +30296,11 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
+      <c r="M140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.18</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -30320,155 +30312,95 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT140" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="Q140" t="n">
+        <v>12</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>9</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>562</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>421</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>527</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>369</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>106</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>26</v>
       </c>
       <c r="AU140" t="inlineStr"/>
       <c r="AV140" t="inlineStr"/>
@@ -30548,15 +30480,11 @@
           <t>28 719</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>4</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -30578,15 +30506,11 @@
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
+      <c r="M141" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2.04</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -30598,155 +30522,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AT141" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="Q141" t="n">
+        <v>19</v>
+      </c>
+      <c r="R141" t="n">
+        <v>10</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="n">
+        <v>6</v>
+      </c>
+      <c r="U141" t="n">
+        <v>11</v>
+      </c>
+      <c r="V141" t="n">
+        <v>3</v>
+      </c>
+      <c r="W141" t="n">
+        <v>3</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>452</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>508</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>336</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>388</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>111</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>34</v>
       </c>
       <c r="AU141" t="inlineStr"/>
       <c r="AV141" t="inlineStr"/>
@@ -30793,6 +30657,1146 @@
       <c r="BK141" t="inlineStr"/>
       <c r="BL141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AU142" t="inlineStr"/>
+      <c r="AV142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr"/>
+      <c r="AX142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="BC142" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr"/>
+      <c r="BH142" t="inlineStr"/>
+      <c r="BI142" t="inlineStr"/>
+      <c r="BJ142" t="inlineStr"/>
+      <c r="BK142" t="inlineStr"/>
+      <c r="BL142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AU143" t="inlineStr"/>
+      <c r="AV143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr"/>
+      <c r="AX143" t="inlineStr"/>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="BC143" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI143" t="inlineStr"/>
+      <c r="BJ143" t="inlineStr"/>
+      <c r="BK143" t="inlineStr"/>
+      <c r="BL143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr"/>
+      <c r="AX144" t="inlineStr"/>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BC144" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL144" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>10 248</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr"/>
+      <c r="AX145" t="inlineStr"/>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="BC145" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BK145" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BL145" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL145"/>
+  <dimension ref="A1:BL155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30686,15 +30686,11 @@
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -30716,15 +30712,11 @@
           <t>AC Milan</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
+      <c r="M142" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2.21</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -30736,155 +30728,95 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AT142" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="Q142" t="n">
+        <v>7</v>
+      </c>
+      <c r="R142" t="n">
+        <v>16</v>
+      </c>
+      <c r="S142" t="n">
+        <v>6</v>
+      </c>
+      <c r="T142" t="n">
+        <v>5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" t="n">
+        <v>8</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>404</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>590</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>511</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>81</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>135</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>69</v>
       </c>
       <c r="AU142" t="inlineStr"/>
       <c r="AV142" t="inlineStr"/>
@@ -30960,15 +30892,11 @@
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -30990,15 +30918,11 @@
           <t>Lazio</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="M143" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1.17</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -31010,155 +30934,95 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AT143" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="Q143" t="n">
+        <v>8</v>
+      </c>
+      <c r="R143" t="n">
+        <v>18</v>
+      </c>
+      <c r="S143" t="n">
+        <v>3</v>
+      </c>
+      <c r="T143" t="n">
+        <v>5</v>
+      </c>
+      <c r="U143" t="n">
+        <v>4</v>
+      </c>
+      <c r="V143" t="n">
+        <v>11</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>503</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>206</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>432</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>93</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>132</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>61</v>
       </c>
       <c r="AU143" t="inlineStr"/>
       <c r="AV143" t="inlineStr"/>
@@ -31198,15 +31062,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BG143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0</v>
       </c>
       <c r="BI143" t="inlineStr"/>
       <c r="BJ143" t="inlineStr"/>
@@ -31242,15 +31102,11 @@
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G144" t="n">
+        <v>3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -31284,165 +31140,101 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AT144" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q144" t="n">
+        <v>17</v>
+      </c>
+      <c r="R144" t="n">
+        <v>9</v>
+      </c>
+      <c r="S144" t="n">
+        <v>7</v>
+      </c>
+      <c r="T144" t="n">
+        <v>3</v>
+      </c>
+      <c r="U144" t="n">
+        <v>6</v>
+      </c>
+      <c r="V144" t="n">
+        <v>5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>4</v>
+      </c>
+      <c r="X144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>372</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>566</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>303</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>497</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>132</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>49</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>15</v>
       </c>
       <c r="AW144" t="inlineStr"/>
       <c r="AX144" t="inlineStr"/>
@@ -31482,25 +31274,17 @@
       </c>
       <c r="BG144" t="inlineStr"/>
       <c r="BH144" t="inlineStr"/>
-      <c r="BI144" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BK144" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL144" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BI144" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="145">
@@ -31536,15 +31320,11 @@
           <t>10 248</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -31578,165 +31358,101 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="AP145" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AT145" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AV145" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="Q145" t="n">
+        <v>16</v>
+      </c>
+      <c r="R145" t="n">
+        <v>14</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="n">
+        <v>4</v>
+      </c>
+      <c r="U145" t="n">
+        <v>7</v>
+      </c>
+      <c r="V145" t="n">
+        <v>8</v>
+      </c>
+      <c r="W145" t="n">
+        <v>4</v>
+      </c>
+      <c r="X145" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>297</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>405</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>225</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>348</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>94</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>47</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>47</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>18</v>
       </c>
       <c r="AW145" t="inlineStr"/>
       <c r="AX145" t="inlineStr"/>
@@ -31776,22 +31492,2850 @@
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="inlineStr"/>
-      <c r="BI145" t="inlineStr">
+      <c r="BI145" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>27</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>25.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="BJ145" t="inlineStr">
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU146" t="inlineStr"/>
+      <c r="AV146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr"/>
+      <c r="AX146" t="inlineStr"/>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BC146" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
+      <c r="BI146" t="inlineStr"/>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>25.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20 451</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AU147" t="inlineStr"/>
+      <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="BC147" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
+      <c r="BI147" t="inlineStr"/>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU148" t="inlineStr"/>
+      <c r="AV148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr"/>
+      <c r="AX148" t="inlineStr"/>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="BC148" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
+      <c r="BI148" t="inlineStr"/>
+      <c r="BJ148" t="inlineStr"/>
+      <c r="BK148" t="inlineStr"/>
+      <c r="BL148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AU149" t="inlineStr"/>
+      <c r="AV149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr"/>
+      <c r="AX149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BC149" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr"/>
+      <c r="BI149" t="inlineStr"/>
+      <c r="BJ149" t="inlineStr"/>
+      <c r="BK149" t="inlineStr"/>
+      <c r="BL149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Galipo S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr"/>
+      <c r="AX150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="BC150" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BJ150" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BK150" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL150" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="BK145" t="inlineStr">
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="AN151" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr"/>
+      <c r="AX151" t="inlineStr"/>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="BC151" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
+      <c r="BI151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BJ151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BK151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>8 811</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BL145" t="inlineStr">
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr"/>
+      <c r="AX152" t="inlineStr"/>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BC152" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
+      <c r="BI152" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BJ152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK152" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BL152" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>23 061</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr"/>
+      <c r="AX153" t="inlineStr"/>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="BC153" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
+      <c r="BI153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ153" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BK153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL153" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Massimi L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>5 017</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr"/>
+      <c r="AR154" t="inlineStr"/>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr"/>
+      <c r="AX154" t="inlineStr"/>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="BC154" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
+      <c r="BI154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BK154" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BL154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Pezzuto I.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Picco
+ (La Spezia)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>11 466</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr"/>
+      <c r="AX155" t="inlineStr"/>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="BC155" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
+      <c r="BI155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ155" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK155" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL155" t="inlineStr">
         <is>
           <t>22</t>
         </is>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL155"/>
+  <dimension ref="A1:BL161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31534,15 +31534,11 @@
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -31564,15 +31560,11 @@
           <t>Venezia</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+      <c r="M146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.43</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -31584,155 +31576,95 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AT146" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="Q146" t="n">
+        <v>12</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7</v>
+      </c>
+      <c r="S146" t="n">
+        <v>8</v>
+      </c>
+      <c r="T146" t="n">
+        <v>4</v>
+      </c>
+      <c r="U146" t="n">
+        <v>3</v>
+      </c>
+      <c r="V146" t="n">
+        <v>2</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1</v>
+      </c>
+      <c r="X146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>474</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>394</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>394</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>311</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>94</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>96</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>30</v>
       </c>
       <c r="AU146" t="inlineStr"/>
       <c r="AV146" t="inlineStr"/>
@@ -31812,15 +31744,11 @@
           <t>20 451</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -31842,15 +31770,11 @@
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>3.51</t>
-        </is>
+      <c r="M147" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N147" t="n">
+        <v>3.51</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -31862,155 +31786,95 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AT147" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="Q147" t="n">
+        <v>13</v>
+      </c>
+      <c r="R147" t="n">
+        <v>24</v>
+      </c>
+      <c r="S147" t="n">
+        <v>6</v>
+      </c>
+      <c r="T147" t="n">
+        <v>8</v>
+      </c>
+      <c r="U147" t="n">
+        <v>4</v>
+      </c>
+      <c r="V147" t="n">
+        <v>13</v>
+      </c>
+      <c r="W147" t="n">
+        <v>3</v>
+      </c>
+      <c r="X147" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>367</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>371</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>298</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>431</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>71</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>98</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>59</v>
       </c>
       <c r="AU147" t="inlineStr"/>
       <c r="AV147" t="inlineStr"/>
@@ -32086,15 +31950,11 @@
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -32116,15 +31976,11 @@
           <t>Lecce</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
+      <c r="M148" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0.38</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -32136,155 +31992,95 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="AP148" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AT148" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="Q148" t="n">
+        <v>11</v>
+      </c>
+      <c r="R148" t="n">
+        <v>10</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3</v>
+      </c>
+      <c r="T148" t="n">
+        <v>4</v>
+      </c>
+      <c r="U148" t="n">
+        <v>5</v>
+      </c>
+      <c r="V148" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" t="n">
+        <v>3</v>
+      </c>
+      <c r="X148" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>645</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>385</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>522</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>317</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>93</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>93</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>62</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>36</v>
       </c>
       <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr"/>
@@ -32360,15 +32156,11 @@
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -32390,15 +32182,11 @@
           <t>Genoa</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="M149" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.66</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -32410,155 +32198,95 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="AP149" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AT149" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="Q149" t="n">
+        <v>9</v>
+      </c>
+      <c r="R149" t="n">
+        <v>11</v>
+      </c>
+      <c r="S149" t="n">
+        <v>2</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" t="n">
+        <v>5</v>
+      </c>
+      <c r="V149" t="n">
+        <v>7</v>
+      </c>
+      <c r="W149" t="n">
+        <v>2</v>
+      </c>
+      <c r="X149" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>623</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>256</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>561</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>213</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>81</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>54</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>29</v>
       </c>
       <c r="AU149" t="inlineStr"/>
       <c r="AV149" t="inlineStr"/>
@@ -32634,15 +32362,11 @@
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -32676,165 +32400,101 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AT150" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AV150" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Q150" t="n">
+        <v>18</v>
+      </c>
+      <c r="R150" t="n">
+        <v>15</v>
+      </c>
+      <c r="S150" t="n">
+        <v>6</v>
+      </c>
+      <c r="T150" t="n">
+        <v>3</v>
+      </c>
+      <c r="U150" t="n">
+        <v>8</v>
+      </c>
+      <c r="V150" t="n">
+        <v>9</v>
+      </c>
+      <c r="W150" t="n">
+        <v>4</v>
+      </c>
+      <c r="X150" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>424</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>303</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>354</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>228</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>131</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>51</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>39</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>22</v>
       </c>
       <c r="AW150" t="inlineStr"/>
       <c r="AX150" t="inlineStr"/>
@@ -32872,35 +32532,23 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BI150" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BJ150" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BK150" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL150" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="BG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>21</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="151">
@@ -32932,15 +32580,11 @@
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -32974,157 +32618,97 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q151" t="n">
+        <v>16</v>
+      </c>
+      <c r="R151" t="n">
+        <v>10</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="n">
+        <v>3</v>
+      </c>
+      <c r="U151" t="n">
+        <v>7</v>
+      </c>
+      <c r="V151" t="n">
+        <v>4</v>
+      </c>
+      <c r="W151" t="n">
+        <v>5</v>
+      </c>
+      <c r="X151" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>14</v>
       </c>
       <c r="AK151" t="inlineStr"/>
       <c r="AL151" t="inlineStr"/>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="AP151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AT151" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AV151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="AM151" t="n">
+        <v>544</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>452</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>241</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>156</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>86</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>68</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>14</v>
       </c>
       <c r="AW151" t="inlineStr"/>
       <c r="AX151" t="inlineStr"/>
@@ -33164,25 +32748,17 @@
       </c>
       <c r="BG151" t="inlineStr"/>
       <c r="BH151" t="inlineStr"/>
-      <c r="BI151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BJ151" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL151" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BI151" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="152">
@@ -33218,15 +32794,11 @@
           <t>8 811</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -33260,165 +32832,101 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AT152" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AV152" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="Q152" t="n">
+        <v>11</v>
+      </c>
+      <c r="R152" t="n">
+        <v>16</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" t="n">
+        <v>4</v>
+      </c>
+      <c r="U152" t="n">
+        <v>5</v>
+      </c>
+      <c r="V152" t="n">
+        <v>8</v>
+      </c>
+      <c r="W152" t="n">
+        <v>2</v>
+      </c>
+      <c r="X152" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>242</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>479</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>164</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>416</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>67</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>141</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>60</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>33</v>
       </c>
       <c r="AW152" t="inlineStr"/>
       <c r="AX152" t="inlineStr"/>
@@ -33458,25 +32966,17 @@
       </c>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
-      <c r="BI152" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BJ152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK152" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BL152" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="BI152" t="n">
+        <v>28</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="153">
@@ -33512,15 +33012,11 @@
           <t>23 061</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -33554,165 +33050,101 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="AP153" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT153" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AV153" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q153" t="n">
+        <v>9</v>
+      </c>
+      <c r="R153" t="n">
+        <v>19</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
+        <v>4</v>
+      </c>
+      <c r="U153" t="n">
+        <v>3</v>
+      </c>
+      <c r="V153" t="n">
+        <v>6</v>
+      </c>
+      <c r="W153" t="n">
+        <v>5</v>
+      </c>
+      <c r="X153" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>412</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>359</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>333</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>298</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>82</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>10</v>
       </c>
       <c r="AW153" t="inlineStr"/>
       <c r="AX153" t="inlineStr"/>
@@ -33752,25 +33184,17 @@
       </c>
       <c r="BG153" t="inlineStr"/>
       <c r="BH153" t="inlineStr"/>
-      <c r="BI153" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BJ153" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BK153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL153" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="BI153" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="154">
@@ -33806,15 +33230,11 @@
           <t>5 017</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -33848,149 +33268,93 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="Q154" t="n">
+        <v>13</v>
+      </c>
+      <c r="R154" t="n">
+        <v>23</v>
+      </c>
+      <c r="S154" t="n">
+        <v>6</v>
+      </c>
+      <c r="T154" t="n">
+        <v>6</v>
+      </c>
+      <c r="U154" t="n">
+        <v>4</v>
+      </c>
+      <c r="V154" t="n">
+        <v>9</v>
+      </c>
+      <c r="W154" t="n">
+        <v>3</v>
+      </c>
+      <c r="X154" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>589</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>506</v>
       </c>
       <c r="AQ154" t="inlineStr"/>
       <c r="AR154" t="inlineStr"/>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="inlineStr"/>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AV154" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="AU154" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>25</v>
       </c>
       <c r="AW154" t="inlineStr"/>
       <c r="AX154" t="inlineStr"/>
@@ -34030,25 +33394,17 @@
       </c>
       <c r="BG154" t="inlineStr"/>
       <c r="BH154" t="inlineStr"/>
-      <c r="BI154" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BJ154" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BK154" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BL154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BI154" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="155">
@@ -34080,15 +33436,11 @@
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -34122,165 +33474,101 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="AP155" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AT155" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AV155" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="Q155" t="n">
+        <v>12</v>
+      </c>
+      <c r="R155" t="n">
+        <v>8</v>
+      </c>
+      <c r="S155" t="n">
+        <v>6</v>
+      </c>
+      <c r="T155" t="n">
+        <v>3</v>
+      </c>
+      <c r="U155" t="n">
+        <v>4</v>
+      </c>
+      <c r="V155" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" t="n">
+        <v>2</v>
+      </c>
+      <c r="X155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>344</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>323</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>262</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>234</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>97</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>106</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>11</v>
       </c>
       <c r="AW155" t="inlineStr"/>
       <c r="AX155" t="inlineStr"/>
@@ -34320,24 +33608,1716 @@
       </c>
       <c r="BG155" t="inlineStr"/>
       <c r="BH155" t="inlineStr"/>
-      <c r="BI155" t="inlineStr">
+      <c r="BI155" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>26.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>29 575</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU156" t="inlineStr"/>
+      <c r="AV156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr"/>
+      <c r="AX156" t="inlineStr"/>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="BC156" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG156" t="inlineStr"/>
+      <c r="BH156" t="inlineStr"/>
+      <c r="BI156" t="inlineStr"/>
+      <c r="BJ156" t="inlineStr"/>
+      <c r="BK156" t="inlineStr"/>
+      <c r="BL156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>26.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>16 365</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="BJ155" t="inlineStr">
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AU157" t="inlineStr"/>
+      <c r="AV157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr"/>
+      <c r="AX157" t="inlineStr"/>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="BC157" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr"/>
+      <c r="BI157" t="inlineStr"/>
+      <c r="BJ157" t="inlineStr"/>
+      <c r="BK157" t="inlineStr"/>
+      <c r="BL157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>67 517</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr"/>
+      <c r="AV158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr"/>
+      <c r="AX158" t="inlineStr"/>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>de rossi daniele</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="BC158" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="inlineStr"/>
+      <c r="BI158" t="inlineStr"/>
+      <c r="BJ158" t="inlineStr"/>
+      <c r="BK158" t="inlineStr"/>
+      <c r="BL158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AU159" t="inlineStr"/>
+      <c r="AV159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr"/>
+      <c r="AX159" t="inlineStr"/>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="BC159" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG159" t="inlineStr"/>
+      <c r="BH159" t="inlineStr"/>
+      <c r="BI159" t="inlineStr"/>
+      <c r="BJ159" t="inlineStr"/>
+      <c r="BK159" t="inlineStr"/>
+      <c r="BL159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Rutella D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>11 788</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BK155" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL155" t="inlineStr">
+      <c r="AW160" t="inlineStr"/>
+      <c r="AX160" t="inlineStr"/>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="BC160" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG160" t="inlineStr"/>
+      <c r="BH160" t="inlineStr"/>
+      <c r="BI160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BJ160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK160" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL160" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Stadio Danilo Martelli
+ (Mantova)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>8 262</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
         <is>
           <t>22</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr"/>
+      <c r="AX161" t="inlineStr"/>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BC161" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG161" t="inlineStr"/>
+      <c r="BH161" t="inlineStr"/>
+      <c r="BI161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BJ161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK161" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BL161" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL161"/>
+  <dimension ref="A1:BL173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33654,15 +33654,11 @@
           <t>29 575</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -33684,15 +33680,11 @@
           <t>Juventus</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="M156" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1.38</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -33704,155 +33696,95 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AT156" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="Q156" t="n">
+        <v>7</v>
+      </c>
+      <c r="R156" t="n">
+        <v>8</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="n">
+        <v>5</v>
+      </c>
+      <c r="U156" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>1</v>
+      </c>
+      <c r="W156" t="n">
+        <v>5</v>
+      </c>
+      <c r="X156" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>407</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>653</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>334</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>547</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>98</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>92</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>20</v>
       </c>
       <c r="AU156" t="inlineStr"/>
       <c r="AV156" t="inlineStr"/>
@@ -33932,15 +33864,11 @@
           <t>16 365</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -33962,15 +33890,11 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
+      <c r="M157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1.36</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -33982,155 +33906,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AT157" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="Q157" t="n">
+        <v>11</v>
+      </c>
+      <c r="R157" t="n">
+        <v>13</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="n">
+        <v>4</v>
+      </c>
+      <c r="U157" t="n">
+        <v>4</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>2</v>
+      </c>
+      <c r="X157" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>386</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>450</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>296</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>358</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>102</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>51</v>
       </c>
       <c r="AU157" t="inlineStr"/>
       <c r="AV157" t="inlineStr"/>
@@ -34210,15 +34074,11 @@
           <t>67 517</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -34240,15 +34100,11 @@
           <t>Empoli</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
+      <c r="M158" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N158" t="n">
+        <v>2.87</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -34260,155 +34116,95 @@
           <t>27%</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AT158" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="Q158" t="n">
+        <v>26</v>
+      </c>
+      <c r="R158" t="n">
+        <v>14</v>
+      </c>
+      <c r="S158" t="n">
+        <v>7</v>
+      </c>
+      <c r="T158" t="n">
+        <v>4</v>
+      </c>
+      <c r="U158" t="n">
+        <v>10</v>
+      </c>
+      <c r="V158" t="n">
+        <v>6</v>
+      </c>
+      <c r="W158" t="n">
+        <v>9</v>
+      </c>
+      <c r="X158" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>614</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>229</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>547</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>172</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>164</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>89</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>21</v>
       </c>
       <c r="AU158" t="inlineStr"/>
       <c r="AV158" t="inlineStr"/>
@@ -34488,15 +34284,11 @@
           <t>45 000</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -34518,15 +34310,11 @@
           <t>Bologna</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+      <c r="M159" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.46</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -34538,155 +34326,95 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AT159" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="Q159" t="n">
+        <v>16</v>
+      </c>
+      <c r="R159" t="n">
+        <v>8</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="n">
+        <v>2</v>
+      </c>
+      <c r="U159" t="n">
+        <v>4</v>
+      </c>
+      <c r="V159" t="n">
+        <v>4</v>
+      </c>
+      <c r="W159" t="n">
+        <v>7</v>
+      </c>
+      <c r="X159" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>337</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>531</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>263</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>457</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>76</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>155</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>37</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>38</v>
       </c>
       <c r="AU159" t="inlineStr"/>
       <c r="AV159" t="inlineStr"/>
@@ -34766,15 +34494,11 @@
           <t>11 788</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -34808,165 +34532,101 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT160" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AV160" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q160" t="n">
+        <v>11</v>
+      </c>
+      <c r="R160" t="n">
+        <v>11</v>
+      </c>
+      <c r="S160" t="n">
+        <v>2</v>
+      </c>
+      <c r="T160" t="n">
+        <v>2</v>
+      </c>
+      <c r="U160" t="n">
+        <v>6</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2</v>
+      </c>
+      <c r="W160" t="n">
+        <v>3</v>
+      </c>
+      <c r="X160" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>391</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>360</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>283</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>270</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>110</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>15</v>
       </c>
       <c r="AW160" t="inlineStr"/>
       <c r="AX160" t="inlineStr"/>
@@ -35006,25 +34666,17 @@
       </c>
       <c r="BG160" t="inlineStr"/>
       <c r="BH160" t="inlineStr"/>
-      <c r="BI160" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BJ160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK160" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL160" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="BI160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="161">
@@ -35060,15 +34712,11 @@
           <t>8 262</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G161" t="n">
+        <v>3</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -35102,165 +34750,101 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AT161" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AV161" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="Q161" t="n">
+        <v>9</v>
+      </c>
+      <c r="R161" t="n">
+        <v>22</v>
+      </c>
+      <c r="S161" t="n">
+        <v>6</v>
+      </c>
+      <c r="T161" t="n">
+        <v>10</v>
+      </c>
+      <c r="U161" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" t="n">
+        <v>10</v>
+      </c>
+      <c r="W161" t="n">
+        <v>2</v>
+      </c>
+      <c r="X161" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>378</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>308</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>258</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>111</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>76</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>27</v>
       </c>
       <c r="AW161" t="inlineStr"/>
       <c r="AX161" t="inlineStr"/>
@@ -35300,24 +34884,3520 @@
       </c>
       <c r="BG161" t="inlineStr"/>
       <c r="BH161" t="inlineStr"/>
-      <c r="BI161" t="inlineStr">
+      <c r="BI161" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>28</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AU162" t="inlineStr"/>
+      <c r="AV162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr"/>
+      <c r="AX162" t="inlineStr"/>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="BC162" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
+      <c r="BI162" t="inlineStr"/>
+      <c r="BJ162" t="inlineStr"/>
+      <c r="BK162" t="inlineStr"/>
+      <c r="BL162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="BJ161" t="inlineStr">
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr"/>
+      <c r="AX163" t="inlineStr"/>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="BC163" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG163" t="inlineStr"/>
+      <c r="BH163" t="inlineStr"/>
+      <c r="BI163" t="inlineStr"/>
+      <c r="BJ163" t="inlineStr"/>
+      <c r="BK163" t="inlineStr"/>
+      <c r="BL163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>23 860</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>11 870</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BK161" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BL161" t="inlineStr">
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr"/>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BC164" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG164" t="inlineStr"/>
+      <c r="BH164" t="inlineStr"/>
+      <c r="BI164" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BJ164" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BL164" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>8 006</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr"/>
+      <c r="AX165" t="inlineStr"/>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BC165" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG165" t="inlineStr"/>
+      <c r="BH165" t="inlineStr"/>
+      <c r="BI165" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BJ165" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK165" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="BL165" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Perri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Stadio Leonardo Garilli
+ (Piacenza)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>21 668</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1 480</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr"/>
+      <c r="AX166" t="inlineStr"/>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="BC166" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG166" t="inlineStr"/>
+      <c r="BH166" t="inlineStr"/>
+      <c r="BI166" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="BJ166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BK166" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>15 733</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr"/>
+      <c r="AX167" t="inlineStr"/>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BC167" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BK167" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL167" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Monaldi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1 987</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr"/>
+      <c r="AX168" t="inlineStr"/>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="BC168" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr"/>
+      <c r="BH168" t="inlineStr"/>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Arena A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>3 685</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr"/>
+      <c r="AX169" t="inlineStr"/>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BC169" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr"/>
+      <c r="BH169" t="inlineStr"/>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BJ169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BK169" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>9 394</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr"/>
+      <c r="AL170" t="inlineStr"/>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr"/>
+      <c r="AX170" t="inlineStr"/>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BC170" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr"/>
+      <c r="BH170" t="inlineStr"/>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ170" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL170" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>9 841</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr"/>
+      <c r="AX171" t="inlineStr"/>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="BC171" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr"/>
+      <c r="BH171" t="inlineStr"/>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ171" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BK171" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BL171" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>9 252</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr"/>
+      <c r="AX172" t="inlineStr"/>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="BC172" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr"/>
+      <c r="BH172" t="inlineStr"/>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>15 683</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr"/>
+      <c r="AX173" t="inlineStr"/>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="BC173" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BJ173" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BK173" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL173" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL173"/>
+  <dimension ref="A1:BL181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34926,15 +34926,11 @@
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -34956,15 +34952,11 @@
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="M162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1.04</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -34976,155 +34968,95 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AT162" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="Q162" t="n">
+        <v>13</v>
+      </c>
+      <c r="R162" t="n">
+        <v>11</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1</v>
+      </c>
+      <c r="U162" t="n">
+        <v>4</v>
+      </c>
+      <c r="V162" t="n">
+        <v>6</v>
+      </c>
+      <c r="W162" t="n">
+        <v>4</v>
+      </c>
+      <c r="X162" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>561</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>443</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>490</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>392</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>74</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>115</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>75</v>
       </c>
       <c r="AU162" t="inlineStr"/>
       <c r="AV162" t="inlineStr"/>
@@ -35200,15 +35132,11 @@
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -35230,15 +35158,11 @@
           <t>Torino</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="M163" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0.88</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -35250,165 +35174,101 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AT163" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q163" t="n">
+        <v>13</v>
+      </c>
+      <c r="R163" t="n">
+        <v>12</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4</v>
+      </c>
+      <c r="T163" t="n">
+        <v>6</v>
+      </c>
+      <c r="U163" t="n">
+        <v>6</v>
+      </c>
+      <c r="V163" t="n">
+        <v>4</v>
+      </c>
+      <c r="W163" t="n">
+        <v>3</v>
+      </c>
+      <c r="X163" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>401</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>566</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>291</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>433</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>76</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>125</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>61</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
       </c>
       <c r="AW163" t="inlineStr"/>
       <c r="AX163" t="inlineStr"/>
@@ -35486,15 +35346,11 @@
           <t>11 870</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -35528,165 +35384,101 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AT164" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AV164" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="Q164" t="n">
+        <v>12</v>
+      </c>
+      <c r="R164" t="n">
+        <v>15</v>
+      </c>
+      <c r="S164" t="n">
+        <v>5</v>
+      </c>
+      <c r="T164" t="n">
+        <v>2</v>
+      </c>
+      <c r="U164" t="n">
+        <v>5</v>
+      </c>
+      <c r="V164" t="n">
+        <v>8</v>
+      </c>
+      <c r="W164" t="n">
+        <v>2</v>
+      </c>
+      <c r="X164" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>308</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>596</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>243</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>535</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>133</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>37</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>21</v>
       </c>
       <c r="AW164" t="inlineStr"/>
       <c r="AX164" t="inlineStr"/>
@@ -35726,25 +35518,17 @@
       </c>
       <c r="BG164" t="inlineStr"/>
       <c r="BH164" t="inlineStr"/>
-      <c r="BI164" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BJ164" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BL164" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BI164" t="n">
+        <v>18</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="165">
@@ -35780,15 +35564,11 @@
           <t>8 006</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -35822,165 +35602,101 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT165" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AV165" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Q165" t="n">
+        <v>14</v>
+      </c>
+      <c r="R165" t="n">
+        <v>9</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2</v>
+      </c>
+      <c r="T165" t="n">
+        <v>4</v>
+      </c>
+      <c r="U165" t="n">
+        <v>5</v>
+      </c>
+      <c r="V165" t="n">
+        <v>1</v>
+      </c>
+      <c r="W165" t="n">
+        <v>7</v>
+      </c>
+      <c r="X165" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>398</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>305</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>152</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>106</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>22</v>
       </c>
       <c r="AW165" t="inlineStr"/>
       <c r="AX165" t="inlineStr"/>
@@ -36020,25 +35736,17 @@
       </c>
       <c r="BG165" t="inlineStr"/>
       <c r="BH165" t="inlineStr"/>
-      <c r="BI165" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BJ165" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BK165" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="BL165" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="BI165" t="n">
+        <v>18</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>34</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="166">
@@ -36074,15 +35782,11 @@
           <t>1 480</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -36116,165 +35820,101 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="AP166" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AT166" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AV166" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="Q166" t="n">
+        <v>6</v>
+      </c>
+      <c r="R166" t="n">
+        <v>13</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3</v>
+      </c>
+      <c r="T166" t="n">
+        <v>2</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2</v>
+      </c>
+      <c r="V166" t="n">
+        <v>5</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1</v>
+      </c>
+      <c r="X166" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>519</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>171</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>449</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>96</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>98</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>20</v>
       </c>
       <c r="AW166" t="inlineStr"/>
       <c r="AX166" t="inlineStr"/>
@@ -36314,25 +35954,17 @@
       </c>
       <c r="BG166" t="inlineStr"/>
       <c r="BH166" t="inlineStr"/>
-      <c r="BI166" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BJ166" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BK166" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL166" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BI166" t="n">
+        <v>16</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="167">
@@ -36368,15 +36000,11 @@
           <t>15 733</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -36410,165 +36038,101 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE167" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AT167" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AV167" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q167" t="n">
+        <v>26</v>
+      </c>
+      <c r="R167" t="n">
+        <v>8</v>
+      </c>
+      <c r="S167" t="n">
+        <v>4</v>
+      </c>
+      <c r="T167" t="n">
+        <v>2</v>
+      </c>
+      <c r="U167" t="n">
+        <v>7</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2</v>
+      </c>
+      <c r="W167" t="n">
+        <v>15</v>
+      </c>
+      <c r="X167" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>353</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>388</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>292</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>71</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>35</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>47</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>14</v>
       </c>
       <c r="AW167" t="inlineStr"/>
       <c r="AX167" t="inlineStr"/>
@@ -36606,35 +36170,23 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BI167" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BJ167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK167" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL167" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="BG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="168">
@@ -36670,15 +36222,11 @@
           <t>1 987</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -36712,165 +36260,101 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AP168" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AT168" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AV168" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Q168" t="n">
+        <v>12</v>
+      </c>
+      <c r="R168" t="n">
+        <v>16</v>
+      </c>
+      <c r="S168" t="n">
+        <v>3</v>
+      </c>
+      <c r="T168" t="n">
+        <v>4</v>
+      </c>
+      <c r="U168" t="n">
+        <v>3</v>
+      </c>
+      <c r="V168" t="n">
+        <v>4</v>
+      </c>
+      <c r="W168" t="n">
+        <v>6</v>
+      </c>
+      <c r="X168" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>417</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>405</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>328</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>323</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>73</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>98</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>22</v>
       </c>
       <c r="AW168" t="inlineStr"/>
       <c r="AX168" t="inlineStr"/>
@@ -36910,25 +36394,17 @@
       </c>
       <c r="BG168" t="inlineStr"/>
       <c r="BH168" t="inlineStr"/>
-      <c r="BI168" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BJ168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BK168" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BL168" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BI168" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>29</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="169">
@@ -36964,15 +36440,11 @@
           <t>3 685</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -37006,165 +36478,101 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AP169" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AT169" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AV169" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q169" t="n">
+        <v>9</v>
+      </c>
+      <c r="R169" t="n">
+        <v>18</v>
+      </c>
+      <c r="S169" t="n">
+        <v>4</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1</v>
+      </c>
+      <c r="U169" t="n">
+        <v>2</v>
+      </c>
+      <c r="V169" t="n">
+        <v>11</v>
+      </c>
+      <c r="W169" t="n">
+        <v>3</v>
+      </c>
+      <c r="X169" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>424</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>374</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>323</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>290</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>127</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>86</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>15</v>
       </c>
       <c r="AW169" t="inlineStr"/>
       <c r="AX169" t="inlineStr"/>
@@ -37204,25 +36612,17 @@
       </c>
       <c r="BG169" t="inlineStr"/>
       <c r="BH169" t="inlineStr"/>
-      <c r="BI169" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BJ169" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BK169" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL169" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="BI169" t="n">
+        <v>21</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="170">
@@ -37258,15 +36658,11 @@
           <t>9 394</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -37300,157 +36696,97 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="Q170" t="n">
+        <v>18</v>
+      </c>
+      <c r="R170" t="n">
+        <v>5</v>
+      </c>
+      <c r="S170" t="n">
+        <v>4</v>
+      </c>
+      <c r="T170" t="n">
+        <v>3</v>
+      </c>
+      <c r="U170" t="n">
+        <v>10</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>4</v>
+      </c>
+      <c r="X170" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>21</v>
       </c>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AT170" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AV170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="AM170" t="n">
+        <v>558</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>314</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>499</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>256</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>128</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>52</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>66</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>31</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>7</v>
       </c>
       <c r="AW170" t="inlineStr"/>
       <c r="AX170" t="inlineStr"/>
@@ -37490,25 +36826,17 @@
       </c>
       <c r="BG170" t="inlineStr"/>
       <c r="BH170" t="inlineStr"/>
-      <c r="BI170" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BJ170" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BK170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BL170" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="BI170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="171">
@@ -37544,15 +36872,11 @@
           <t>9 841</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -37586,165 +36910,101 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AT171" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AV171" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="Q171" t="n">
+        <v>12</v>
+      </c>
+      <c r="R171" t="n">
+        <v>10</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3</v>
+      </c>
+      <c r="T171" t="n">
+        <v>3</v>
+      </c>
+      <c r="U171" t="n">
+        <v>5</v>
+      </c>
+      <c r="V171" t="n">
+        <v>5</v>
+      </c>
+      <c r="W171" t="n">
+        <v>4</v>
+      </c>
+      <c r="X171" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>415</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>432</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>337</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>359</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>89</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>17</v>
       </c>
       <c r="AW171" t="inlineStr"/>
       <c r="AX171" t="inlineStr"/>
@@ -37784,25 +37044,17 @@
       </c>
       <c r="BG171" t="inlineStr"/>
       <c r="BH171" t="inlineStr"/>
-      <c r="BI171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ171" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BK171" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BL171" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BI171" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>21</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="172">
@@ -37838,15 +37090,11 @@
           <t>9 252</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -37880,165 +37128,101 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT172" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AV172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="Q172" t="n">
+        <v>11</v>
+      </c>
+      <c r="R172" t="n">
+        <v>17</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="n">
+        <v>4</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>5</v>
+      </c>
+      <c r="W172" t="n">
+        <v>3</v>
+      </c>
+      <c r="X172" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>331</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>506</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>243</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>415</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>86</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>107</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>56</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>20</v>
       </c>
       <c r="AW172" t="inlineStr"/>
       <c r="AX172" t="inlineStr"/>
@@ -38078,25 +37262,17 @@
       </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
-      <c r="BI172" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BJ172" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BK172" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BL172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BI172" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>27</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -38132,15 +37308,11 @@
           <t>15 683</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -38174,165 +37346,101 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AT173" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AV173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="Q173" t="n">
+        <v>24</v>
+      </c>
+      <c r="R173" t="n">
+        <v>13</v>
+      </c>
+      <c r="S173" t="n">
+        <v>8</v>
+      </c>
+      <c r="T173" t="n">
+        <v>4</v>
+      </c>
+      <c r="U173" t="n">
+        <v>8</v>
+      </c>
+      <c r="V173" t="n">
+        <v>5</v>
+      </c>
+      <c r="W173" t="n">
+        <v>8</v>
+      </c>
+      <c r="X173" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>479</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>323</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>418</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>95</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>20</v>
       </c>
       <c r="AW173" t="inlineStr"/>
       <c r="AX173" t="inlineStr"/>
@@ -38370,34 +37478,2334 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG173" t="inlineStr">
+      <c r="BG173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BH173" t="inlineStr">
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BI173" t="inlineStr">
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr"/>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr"/>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="BC174" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
+      <c r="BI174" t="inlineStr"/>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="inlineStr"/>
+      <c r="BL174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>25 960</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="BC175" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>26 386</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="BJ173" t="inlineStr">
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BC176" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="BC177" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK177" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BL177" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Galipo S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="BK173" t="inlineStr">
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AN178" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="BC178" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF178" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK178" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BL178" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="BL173" t="inlineStr">
-        <is>
-          <t>27</t>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr"/>
+      <c r="AX179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="BC179" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF179" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL179" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Rutella D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="BC180" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF180" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ180" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BK180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL180" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Maresca F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="BC181" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ181" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK181" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL181"/>
+  <dimension ref="A1:BL191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37526,15 +37526,11 @@
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -37556,15 +37552,11 @@
           <t>AC Milan</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
+      <c r="M174" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1.28</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -37576,155 +37568,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT174" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="Q174" t="n">
+        <v>5</v>
+      </c>
+      <c r="R174" t="n">
+        <v>8</v>
+      </c>
+      <c r="S174" t="n">
+        <v>4</v>
+      </c>
+      <c r="T174" t="n">
+        <v>3</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" t="n">
+        <v>3</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1</v>
+      </c>
+      <c r="X174" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>383</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>331</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>485</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>105</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>80</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>23</v>
       </c>
       <c r="AU174" t="inlineStr"/>
       <c r="AV174" t="inlineStr"/>
@@ -37804,15 +37736,11 @@
           <t>25 960</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -37834,15 +37762,11 @@
           <t>Empoli</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
+      <c r="M175" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.89</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -37854,165 +37778,101 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AT175" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q175" t="n">
+        <v>14</v>
+      </c>
+      <c r="R175" t="n">
+        <v>4</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3</v>
+      </c>
+      <c r="T175" t="n">
+        <v>2</v>
+      </c>
+      <c r="U175" t="n">
+        <v>9</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2</v>
+      </c>
+      <c r="W175" t="n">
+        <v>2</v>
+      </c>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>651</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>299</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>508</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>199</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>127</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>69</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>5</v>
       </c>
       <c r="AW175" t="inlineStr"/>
       <c r="AX175" t="inlineStr"/>
@@ -38090,15 +37950,11 @@
           <t>26 386</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -38120,15 +37976,11 @@
           <t>Cagliari</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="M176" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1.75</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -38140,165 +37992,101 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AT176" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AV176" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="Q176" t="n">
+        <v>17</v>
+      </c>
+      <c r="R176" t="n">
+        <v>21</v>
+      </c>
+      <c r="S176" t="n">
+        <v>4</v>
+      </c>
+      <c r="T176" t="n">
+        <v>2</v>
+      </c>
+      <c r="U176" t="n">
+        <v>8</v>
+      </c>
+      <c r="V176" t="n">
+        <v>7</v>
+      </c>
+      <c r="W176" t="n">
+        <v>5</v>
+      </c>
+      <c r="X176" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>279</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>508</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>181</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>379</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>129</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>23</v>
       </c>
       <c r="AW176" t="inlineStr"/>
       <c r="AX176" t="inlineStr"/>
@@ -38336,15 +38124,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BG176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>0</v>
       </c>
       <c r="BI176" t="inlineStr"/>
       <c r="BJ176" t="inlineStr"/>
@@ -38380,15 +38164,11 @@
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -38422,165 +38202,101 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AT177" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AV177" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="Q177" t="n">
+        <v>18</v>
+      </c>
+      <c r="R177" t="n">
+        <v>10</v>
+      </c>
+      <c r="S177" t="n">
+        <v>6</v>
+      </c>
+      <c r="T177" t="n">
+        <v>4</v>
+      </c>
+      <c r="U177" t="n">
+        <v>10</v>
+      </c>
+      <c r="V177" t="n">
+        <v>3</v>
+      </c>
+      <c r="W177" t="n">
+        <v>2</v>
+      </c>
+      <c r="X177" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>310</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>338</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>221</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>110</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>11</v>
       </c>
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr"/>
@@ -38620,25 +38336,17 @@
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
-      <c r="BI177" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BJ177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK177" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BL177" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="BI177" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>24</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="178">
@@ -38670,15 +38378,11 @@
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -38712,165 +38416,101 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="AN178" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AT178" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AV178" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="Q178" t="n">
+        <v>15</v>
+      </c>
+      <c r="R178" t="n">
+        <v>8</v>
+      </c>
+      <c r="S178" t="n">
+        <v>5</v>
+      </c>
+      <c r="T178" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" t="n">
+        <v>7</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2</v>
+      </c>
+      <c r="W178" t="n">
+        <v>3</v>
+      </c>
+      <c r="X178" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>276</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>518</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>186</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>425</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>75</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>135</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>19</v>
       </c>
       <c r="AW178" t="inlineStr"/>
       <c r="AX178" t="inlineStr"/>
@@ -38910,25 +38550,17 @@
       </c>
       <c r="BG178" t="inlineStr"/>
       <c r="BH178" t="inlineStr"/>
-      <c r="BI178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ178" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK178" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BL178" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="BI178" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>27</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="179">
@@ -38960,15 +38592,11 @@
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -39002,165 +38630,101 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="AN179" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AT179" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AV179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q179" t="n">
+        <v>12</v>
+      </c>
+      <c r="R179" t="n">
+        <v>11</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4</v>
+      </c>
+      <c r="T179" t="n">
+        <v>6</v>
+      </c>
+      <c r="U179" t="n">
+        <v>3</v>
+      </c>
+      <c r="V179" t="n">
+        <v>4</v>
+      </c>
+      <c r="W179" t="n">
+        <v>5</v>
+      </c>
+      <c r="X179" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>417</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>428</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>348</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>366</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>85</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>58</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>5</v>
       </c>
       <c r="AW179" t="inlineStr"/>
       <c r="AX179" t="inlineStr"/>
@@ -39200,25 +38764,17 @@
       </c>
       <c r="BG179" t="inlineStr"/>
       <c r="BH179" t="inlineStr"/>
-      <c r="BI179" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BJ179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BK179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL179" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="BI179" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="180">
@@ -39250,15 +38806,11 @@
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -39292,165 +38844,101 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AT180" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AV180" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q180" t="n">
+        <v>19</v>
+      </c>
+      <c r="R180" t="n">
+        <v>5</v>
+      </c>
+      <c r="S180" t="n">
+        <v>7</v>
+      </c>
+      <c r="T180" t="n">
+        <v>2</v>
+      </c>
+      <c r="U180" t="n">
+        <v>5</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2</v>
+      </c>
+      <c r="W180" t="n">
+        <v>7</v>
+      </c>
+      <c r="X180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>573</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>288</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>488</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>205</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>153</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>86</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>15</v>
       </c>
       <c r="AW180" t="inlineStr"/>
       <c r="AX180" t="inlineStr"/>
@@ -39490,25 +38978,17 @@
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
-      <c r="BI180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BJ180" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BK180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL180" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="BI180" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="181">
@@ -39540,15 +39020,11 @@
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -39582,165 +39058,101 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="AN181" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="AP181" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AT181" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AV181" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="Q181" t="n">
+        <v>9</v>
+      </c>
+      <c r="R181" t="n">
+        <v>25</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4</v>
+      </c>
+      <c r="T181" t="n">
+        <v>7</v>
+      </c>
+      <c r="U181" t="n">
+        <v>4</v>
+      </c>
+      <c r="V181" t="n">
+        <v>9</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1</v>
+      </c>
+      <c r="X181" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>278</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>426</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>218</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>375</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>69</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>19</v>
       </c>
       <c r="AW181" t="inlineStr"/>
       <c r="AX181" t="inlineStr"/>
@@ -39778,34 +39190,2866 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BG181" t="inlineStr">
+      <c r="BG181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>41 375</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BH181" t="inlineStr">
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BI181" t="inlineStr">
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr"/>
+      <c r="AV182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>de rossi daniele</t>
+        </is>
+      </c>
+      <c r="BC182" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF182" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>7 020</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BJ181" t="inlineStr">
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr"/>
+      <c r="AV183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr"/>
+      <c r="AX183" t="inlineStr"/>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="BC183" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG183" t="inlineStr"/>
+      <c r="BH183" t="inlineStr"/>
+      <c r="BI183" t="inlineStr"/>
+      <c r="BJ183" t="inlineStr"/>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>18 376</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr"/>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr"/>
+      <c r="AX184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="BC184" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF184" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>30 747</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BK181" t="inlineStr">
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU185" t="inlineStr"/>
+      <c r="AV185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr"/>
+      <c r="AX185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="BC185" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr"/>
+      <c r="BI185" t="inlineStr"/>
+      <c r="BJ185" t="inlineStr"/>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr"/>
+      <c r="AX186" t="inlineStr"/>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="BC186" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF186" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>9 348</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU187" t="inlineStr"/>
+      <c r="AV187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr"/>
+      <c r="AX187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="BC187" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF187" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
+      <c r="BI187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK187" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BL187" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>10 755</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU188" t="inlineStr"/>
+      <c r="AV188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr"/>
+      <c r="AX188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="BC188" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF188" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI188" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ188" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK188" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL188" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Stadio Danilo Martelli
+ (Mantova)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>8 651</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr"/>
+      <c r="AV189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr"/>
+      <c r="AX189" t="inlineStr"/>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BC189" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF189" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
+      <c r="BI189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ189" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Massimi L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Stadio Renzo Barbera
+ (Palermo)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>36 349</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>25 787</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr"/>
+      <c r="AV190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr"/>
+      <c r="AX190" t="inlineStr"/>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BC190" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
+      <c r="BI190" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Picco
+ (La Spezia)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>11 466</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>7 573</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr"/>
+      <c r="AV191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr"/>
+      <c r="AX191" t="inlineStr"/>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="BC191" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>774</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF191" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BJ191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL191" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="BL181" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL199"/>
+  <dimension ref="A1:BL211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41330,15 +41330,11 @@
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -41360,15 +41356,11 @@
           <t>Juventus</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="M192" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0.88</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -41380,155 +41372,95 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AT192" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="Q192" t="n">
+        <v>5</v>
+      </c>
+      <c r="R192" t="n">
+        <v>16</v>
+      </c>
+      <c r="S192" t="n">
+        <v>3</v>
+      </c>
+      <c r="T192" t="n">
+        <v>3</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2</v>
+      </c>
+      <c r="V192" t="n">
+        <v>7</v>
+      </c>
+      <c r="W192" t="n">
+        <v>0</v>
+      </c>
+      <c r="X192" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>368</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>705</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>287</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>654</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>158</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>55</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
@@ -41604,15 +41536,11 @@
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -41634,15 +41562,11 @@
           <t>Bologna</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="M193" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1.74</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -41654,155 +41578,95 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="AN193" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="AP193" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AT193" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="Q193" t="n">
+        <v>14</v>
+      </c>
+      <c r="R193" t="n">
+        <v>14</v>
+      </c>
+      <c r="S193" t="n">
+        <v>4</v>
+      </c>
+      <c r="T193" t="n">
+        <v>4</v>
+      </c>
+      <c r="U193" t="n">
+        <v>6</v>
+      </c>
+      <c r="V193" t="n">
+        <v>5</v>
+      </c>
+      <c r="W193" t="n">
+        <v>4</v>
+      </c>
+      <c r="X193" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>374</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>469</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>307</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>399</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>75</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>56</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
@@ -41882,15 +41746,11 @@
           <t>14 003</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G194" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -41924,155 +41784,95 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="AN194" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AT194" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="Q194" t="n">
+        <v>13</v>
+      </c>
+      <c r="R194" t="n">
+        <v>9</v>
+      </c>
+      <c r="S194" t="n">
+        <v>2</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1</v>
+      </c>
+      <c r="U194" t="n">
+        <v>5</v>
+      </c>
+      <c r="V194" t="n">
+        <v>4</v>
+      </c>
+      <c r="W194" t="n">
+        <v>6</v>
+      </c>
+      <c r="X194" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>255</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>609</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>206</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>534</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>112</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>85</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>62</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>30</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
@@ -42110,37 +41910,25 @@
       </c>
       <c r="BC194" t="inlineStr"/>
       <c r="BD194" t="inlineStr"/>
-      <c r="BE194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE194" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>1</v>
       </c>
       <c r="BG194" t="inlineStr"/>
       <c r="BH194" t="inlineStr"/>
-      <c r="BI194" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BJ194" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BK194" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL194" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BI194" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="195">
@@ -42176,15 +41964,11 @@
           <t>5 715</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G195" t="n">
+        <v>4</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -42218,155 +42002,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="AN195" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="AP195" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AT195" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="Q195" t="n">
+        <v>14</v>
+      </c>
+      <c r="R195" t="n">
+        <v>8</v>
+      </c>
+      <c r="S195" t="n">
+        <v>7</v>
+      </c>
+      <c r="T195" t="n">
+        <v>2</v>
+      </c>
+      <c r="U195" t="n">
+        <v>6</v>
+      </c>
+      <c r="V195" t="n">
+        <v>4</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1</v>
+      </c>
+      <c r="X195" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>428</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>445</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>363</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>385</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>108</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>111</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>50</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
@@ -42404,37 +42128,25 @@
       </c>
       <c r="BC195" t="inlineStr"/>
       <c r="BD195" t="inlineStr"/>
-      <c r="BE195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>1</v>
       </c>
       <c r="BG195" t="inlineStr"/>
       <c r="BH195" t="inlineStr"/>
-      <c r="BI195" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ195" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK195" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL195" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BI195" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="196">
@@ -42470,15 +42182,11 @@
           <t>2 269</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -42512,155 +42220,95 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="AN196" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AT196" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="Q196" t="n">
+        <v>13</v>
+      </c>
+      <c r="R196" t="n">
+        <v>5</v>
+      </c>
+      <c r="S196" t="n">
+        <v>4</v>
+      </c>
+      <c r="T196" t="n">
+        <v>2</v>
+      </c>
+      <c r="U196" t="n">
+        <v>8</v>
+      </c>
+      <c r="V196" t="n">
+        <v>2</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1</v>
+      </c>
+      <c r="X196" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>309</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>483</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>233</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>407</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>122</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>96</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>54</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>37</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
@@ -42702,25 +42350,17 @@
       <c r="BF196" t="inlineStr"/>
       <c r="BG196" t="inlineStr"/>
       <c r="BH196" t="inlineStr"/>
-      <c r="BI196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BJ196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK196" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BL196" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="BI196" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="197">
@@ -42752,15 +42392,11 @@
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -42794,155 +42430,95 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AT197" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="Q197" t="n">
+        <v>9</v>
+      </c>
+      <c r="R197" t="n">
+        <v>11</v>
+      </c>
+      <c r="S197" t="n">
+        <v>4</v>
+      </c>
+      <c r="T197" t="n">
+        <v>5</v>
+      </c>
+      <c r="U197" t="n">
+        <v>4</v>
+      </c>
+      <c r="V197" t="n">
+        <v>5</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1</v>
+      </c>
+      <c r="X197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>571</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>495</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>199</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>136</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>37</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
@@ -42984,25 +42560,17 @@
       <c r="BF197" t="inlineStr"/>
       <c r="BG197" t="inlineStr"/>
       <c r="BH197" t="inlineStr"/>
-      <c r="BI197" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ197" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BK197" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BL197" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BI197" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="198">
@@ -43034,15 +42602,11 @@
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -43076,155 +42640,95 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="AN198" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="AP198" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AT198" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="Q198" t="n">
+        <v>14</v>
+      </c>
+      <c r="R198" t="n">
+        <v>9</v>
+      </c>
+      <c r="S198" t="n">
+        <v>5</v>
+      </c>
+      <c r="T198" t="n">
+        <v>6</v>
+      </c>
+      <c r="U198" t="n">
+        <v>6</v>
+      </c>
+      <c r="V198" t="n">
+        <v>1</v>
+      </c>
+      <c r="W198" t="n">
+        <v>3</v>
+      </c>
+      <c r="X198" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>582</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>259</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>522</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>197</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>122</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>81</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>45</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
@@ -43266,25 +42770,17 @@
       <c r="BF198" t="inlineStr"/>
       <c r="BG198" t="inlineStr"/>
       <c r="BH198" t="inlineStr"/>
-      <c r="BI198" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BJ198" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BK198" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL198" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="BI198" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="199">
@@ -43320,15 +42816,11 @@
           <t>13 974</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G199" t="n">
+        <v>2</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -43362,155 +42854,95 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="AN199" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AT199" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="Q199" t="n">
+        <v>12</v>
+      </c>
+      <c r="R199" t="n">
+        <v>10</v>
+      </c>
+      <c r="S199" t="n">
+        <v>4</v>
+      </c>
+      <c r="T199" t="n">
+        <v>4</v>
+      </c>
+      <c r="U199" t="n">
+        <v>6</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2</v>
+      </c>
+      <c r="W199" t="n">
+        <v>2</v>
+      </c>
+      <c r="X199" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>527</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>363</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>458</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>274</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>102</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>113</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>54</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
@@ -43548,36 +42980,3408 @@
       </c>
       <c r="BC199" t="inlineStr"/>
       <c r="BD199" t="inlineStr"/>
-      <c r="BE199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>1</v>
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
-      <c r="BI199" t="inlineStr">
+      <c r="BI199" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>16.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="AY200" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr"/>
+      <c r="BI200" t="inlineStr"/>
+      <c r="BJ200" t="inlineStr"/>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>16.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>17 586</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AY201" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr"/>
+      <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF201" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
+      <c r="BI201" t="inlineStr"/>
+      <c r="BJ201" t="inlineStr"/>
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>15.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>14 541</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BJ199" t="inlineStr">
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BK199" t="inlineStr">
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AY202" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr"/>
+      <c r="BD202" t="inlineStr"/>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr"/>
+      <c r="BI202" t="inlineStr"/>
+      <c r="BJ202" t="inlineStr"/>
+      <c r="BK202" t="inlineStr"/>
+      <c r="BL202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>15.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>15 733</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT203" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AY203" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr"/>
+      <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr"/>
+      <c r="BI203" t="inlineStr"/>
+      <c r="BJ203" t="inlineStr"/>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>22 705</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AY204" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="inlineStr"/>
+      <c r="BL204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>24 277</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AN205" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AY205" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>15.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>33 009</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>de rossi daniele</t>
+        </is>
+      </c>
+      <c r="AY206" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>14.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>71 273</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="AY207" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>15 083</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AY208" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ208" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BK208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL208" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2 777</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BL199" t="inlineStr">
-        <is>
-          <t>23</t>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AY209" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BK209" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BL209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>8 171</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AY210" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ210" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BK210" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BL210" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>8 665</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AT211" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AY211" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ211" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL211" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL230"/>
+  <dimension ref="A1:BL239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46014,15 +46014,11 @@
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>2</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -46044,15 +46040,11 @@
           <t>AC Milan</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="M214" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1.91</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -46064,135 +46056,83 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="AN214" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AP214" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+      <c r="Q214" t="n">
+        <v>13</v>
+      </c>
+      <c r="R214" t="n">
+        <v>16</v>
+      </c>
+      <c r="S214" t="n">
+        <v>4</v>
+      </c>
+      <c r="T214" t="n">
+        <v>8</v>
+      </c>
+      <c r="U214" t="n">
+        <v>4</v>
+      </c>
+      <c r="V214" t="n">
+        <v>5</v>
+      </c>
+      <c r="W214" t="n">
+        <v>5</v>
+      </c>
+      <c r="X214" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>544</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>441</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>487</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>371</v>
       </c>
       <c r="AQ214" t="inlineStr"/>
       <c r="AR214" t="inlineStr"/>
@@ -46272,15 +46212,11 @@
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G215" t="n">
+        <v>3</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -46302,15 +46238,11 @@
           <t>Udinese</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
+      <c r="M215" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0.39</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -46322,135 +46254,83 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="AN215" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AP215" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="Q215" t="n">
+        <v>16</v>
+      </c>
+      <c r="R215" t="n">
+        <v>9</v>
+      </c>
+      <c r="S215" t="n">
+        <v>8</v>
+      </c>
+      <c r="T215" t="n">
+        <v>2</v>
+      </c>
+      <c r="U215" t="n">
+        <v>4</v>
+      </c>
+      <c r="V215" t="n">
+        <v>4</v>
+      </c>
+      <c r="W215" t="n">
+        <v>4</v>
+      </c>
+      <c r="X215" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>609</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>369</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>495</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>277</v>
       </c>
       <c r="AQ215" t="inlineStr"/>
       <c r="AR215" t="inlineStr"/>
@@ -46490,15 +46370,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BD215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC215" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>0</v>
       </c>
       <c r="BE215" t="inlineStr"/>
       <c r="BF215" t="inlineStr"/>
@@ -46538,15 +46414,11 @@
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -46568,15 +46440,11 @@
           <t>Bologna</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="M216" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0.85</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -46588,135 +46456,83 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="AN216" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="AO216" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="AP216" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
+      <c r="Q216" t="n">
+        <v>6</v>
+      </c>
+      <c r="R216" t="n">
+        <v>15</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3</v>
+      </c>
+      <c r="T216" t="n">
+        <v>8</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3</v>
+      </c>
+      <c r="V216" t="n">
+        <v>3</v>
+      </c>
+      <c r="W216" t="n">
+        <v>0</v>
+      </c>
+      <c r="X216" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>544</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>312</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>467</v>
       </c>
       <c r="AQ216" t="inlineStr"/>
       <c r="AR216" t="inlineStr"/>
@@ -46796,15 +46612,11 @@
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -46826,15 +46638,11 @@
           <t>Lazio</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
+      <c r="M217" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1.44</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -46846,135 +46654,83 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AN217" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
+      <c r="Q217" t="n">
+        <v>14</v>
+      </c>
+      <c r="R217" t="n">
+        <v>20</v>
+      </c>
+      <c r="S217" t="n">
+        <v>5</v>
+      </c>
+      <c r="T217" t="n">
+        <v>6</v>
+      </c>
+      <c r="U217" t="n">
+        <v>9</v>
+      </c>
+      <c r="V217" t="n">
+        <v>7</v>
+      </c>
+      <c r="W217" t="n">
+        <v>0</v>
+      </c>
+      <c r="X217" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>355</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>405</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>305</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>360</v>
       </c>
       <c r="AQ217" t="inlineStr"/>
       <c r="AR217" t="inlineStr"/>
@@ -47058,15 +46814,11 @@
           <t>25 503</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -47088,15 +46840,11 @@
           <t>Parma</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
+      <c r="M218" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1.51</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -47108,135 +46856,83 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="AN218" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="AP218" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
+      <c r="Q218" t="n">
+        <v>14</v>
+      </c>
+      <c r="R218" t="n">
+        <v>24</v>
+      </c>
+      <c r="S218" t="n">
+        <v>3</v>
+      </c>
+      <c r="T218" t="n">
+        <v>10</v>
+      </c>
+      <c r="U218" t="n">
+        <v>6</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3</v>
+      </c>
+      <c r="W218" t="n">
+        <v>5</v>
+      </c>
+      <c r="X218" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>322</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>530</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>258</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>456</v>
       </c>
       <c r="AQ218" t="inlineStr"/>
       <c r="AR218" t="inlineStr"/>
@@ -47278,15 +46974,11 @@
       </c>
       <c r="BC218" t="inlineStr"/>
       <c r="BD218" t="inlineStr"/>
-      <c r="BE218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>1</v>
       </c>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
@@ -47328,15 +47020,11 @@
           <t>40 295</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -47358,15 +47046,11 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+      <c r="M219" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.43</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -47378,135 +47062,83 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="AN219" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="AP219" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+      <c r="Q219" t="n">
+        <v>9</v>
+      </c>
+      <c r="R219" t="n">
+        <v>8</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1</v>
+      </c>
+      <c r="U219" t="n">
+        <v>4</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2</v>
+      </c>
+      <c r="W219" t="n">
+        <v>4</v>
+      </c>
+      <c r="X219" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>728</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>379</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>621</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>312</v>
       </c>
       <c r="AQ219" t="inlineStr"/>
       <c r="AR219" t="inlineStr"/>
@@ -47590,15 +47222,11 @@
           <t>10 502</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -47620,15 +47248,11 @@
           <t>Genoa</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="M220" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0.35</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -47640,135 +47264,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="AN220" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="AP220" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
+      <c r="Q220" t="n">
+        <v>12</v>
+      </c>
+      <c r="R220" t="n">
+        <v>9</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="n">
+        <v>5</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3</v>
+      </c>
+      <c r="W220" t="n">
+        <v>3</v>
+      </c>
+      <c r="X220" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>373</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>399</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>291</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>323</v>
       </c>
       <c r="AQ220" t="inlineStr"/>
       <c r="AR220" t="inlineStr"/>
@@ -47808,15 +47380,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BC220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>5</v>
       </c>
       <c r="BE220" t="inlineStr"/>
       <c r="BF220" t="inlineStr"/>
@@ -47860,15 +47428,11 @@
           <t>23 000</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H221" t="n">
+        <v>3</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -47890,15 +47454,11 @@
           <t>Torino</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
+      <c r="M221" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N221" t="n">
+        <v>2.59</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -47910,135 +47470,83 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="AN221" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="AP221" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
+      <c r="Q221" t="n">
+        <v>8</v>
+      </c>
+      <c r="R221" t="n">
+        <v>16</v>
+      </c>
+      <c r="S221" t="n">
+        <v>2</v>
+      </c>
+      <c r="T221" t="n">
+        <v>3</v>
+      </c>
+      <c r="U221" t="n">
+        <v>4</v>
+      </c>
+      <c r="V221" t="n">
+        <v>6</v>
+      </c>
+      <c r="W221" t="n">
+        <v>2</v>
+      </c>
+      <c r="X221" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>314</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>749</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>229</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>673</v>
       </c>
       <c r="AQ221" t="inlineStr"/>
       <c r="AR221" t="inlineStr"/>
@@ -48080,15 +47588,11 @@
       </c>
       <c r="BC221" t="inlineStr"/>
       <c r="BD221" t="inlineStr"/>
-      <c r="BE221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE221" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>0</v>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
@@ -48130,15 +47634,11 @@
           <t>15 225</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -48160,15 +47660,11 @@
           <t>Empoli</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="M222" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0.95</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -48180,135 +47676,83 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="AN222" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="AP222" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+      <c r="Q222" t="n">
+        <v>21</v>
+      </c>
+      <c r="R222" t="n">
+        <v>9</v>
+      </c>
+      <c r="S222" t="n">
+        <v>2</v>
+      </c>
+      <c r="T222" t="n">
+        <v>4</v>
+      </c>
+      <c r="U222" t="n">
+        <v>12</v>
+      </c>
+      <c r="V222" t="n">
+        <v>3</v>
+      </c>
+      <c r="W222" t="n">
+        <v>7</v>
+      </c>
+      <c r="X222" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>453</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>291</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>353</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>198</v>
       </c>
       <c r="AQ222" t="inlineStr"/>
       <c r="AR222" t="inlineStr"/>
@@ -48392,15 +47836,11 @@
           <t>34 000</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G223" t="n">
+        <v>2</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -48422,15 +47862,11 @@
           <t>Verona</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
+      <c r="M223" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0.82</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -48442,155 +47878,95 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="AN223" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="AO223" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="AP223" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AT223" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="Q223" t="n">
+        <v>14</v>
+      </c>
+      <c r="R223" t="n">
+        <v>7</v>
+      </c>
+      <c r="S223" t="n">
+        <v>7</v>
+      </c>
+      <c r="T223" t="n">
+        <v>2</v>
+      </c>
+      <c r="U223" t="n">
+        <v>4</v>
+      </c>
+      <c r="V223" t="n">
+        <v>4</v>
+      </c>
+      <c r="W223" t="n">
+        <v>3</v>
+      </c>
+      <c r="X223" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>502</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>419</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>437</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>348</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>130</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>78</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>30</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
@@ -48670,15 +48046,11 @@
           <t>17 586</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" t="n">
+        <v>3</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -48700,15 +48072,11 @@
           <t>Udinese</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
+      <c r="M224" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2.52</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -48720,155 +48088,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL224" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="AN224" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="AP224" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AT224" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="Q224" t="n">
+        <v>9</v>
+      </c>
+      <c r="R224" t="n">
+        <v>18</v>
+      </c>
+      <c r="S224" t="n">
+        <v>3</v>
+      </c>
+      <c r="T224" t="n">
+        <v>6</v>
+      </c>
+      <c r="U224" t="n">
+        <v>5</v>
+      </c>
+      <c r="V224" t="n">
+        <v>8</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1</v>
+      </c>
+      <c r="X224" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>461</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>496</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>367</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>428</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>91</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>96</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>33</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>45</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
@@ -48906,15 +48214,11 @@
       </c>
       <c r="BC224" t="inlineStr"/>
       <c r="BD224" t="inlineStr"/>
-      <c r="BE224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>0</v>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
@@ -48956,15 +48260,11 @@
           <t>14 541</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -48986,15 +48286,11 @@
           <t>Inter</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
+      <c r="M225" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N225" t="n">
+        <v>1.89</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -49006,155 +48302,95 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R225" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="AN225" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AP225" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AT225" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="Q225" t="n">
+        <v>5</v>
+      </c>
+      <c r="R225" t="n">
+        <v>16</v>
+      </c>
+      <c r="S225" t="n">
+        <v>2</v>
+      </c>
+      <c r="T225" t="n">
+        <v>2</v>
+      </c>
+      <c r="U225" t="n">
+        <v>2</v>
+      </c>
+      <c r="V225" t="n">
+        <v>10</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1</v>
+      </c>
+      <c r="X225" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>398</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>637</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>338</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>529</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>97</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>146</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>70</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
@@ -49234,15 +48470,11 @@
           <t>15 733</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>4</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -49264,15 +48496,11 @@
           <t>Napoli</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="M226" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1.75</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -49284,155 +48512,95 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R226" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL226" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN226" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AT226" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="Q226" t="n">
+        <v>16</v>
+      </c>
+      <c r="R226" t="n">
+        <v>12</v>
+      </c>
+      <c r="S226" t="n">
+        <v>3</v>
+      </c>
+      <c r="T226" t="n">
+        <v>5</v>
+      </c>
+      <c r="U226" t="n">
+        <v>10</v>
+      </c>
+      <c r="V226" t="n">
+        <v>3</v>
+      </c>
+      <c r="W226" t="n">
+        <v>3</v>
+      </c>
+      <c r="X226" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>414</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>414</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>331</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>335</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>111</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>107</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>57</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
@@ -49512,15 +48680,11 @@
           <t>22 705</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G227" t="n">
+        <v>3</v>
+      </c>
+      <c r="H227" t="n">
+        <v>2</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -49542,15 +48706,11 @@
           <t>Fiorentina</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
+      <c r="M227" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1.87</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -49562,155 +48722,95 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL227" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AN227" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AP227" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AT227" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="Q227" t="n">
+        <v>13</v>
+      </c>
+      <c r="R227" t="n">
+        <v>13</v>
+      </c>
+      <c r="S227" t="n">
+        <v>7</v>
+      </c>
+      <c r="T227" t="n">
+        <v>5</v>
+      </c>
+      <c r="U227" t="n">
+        <v>5</v>
+      </c>
+      <c r="V227" t="n">
+        <v>5</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1</v>
+      </c>
+      <c r="X227" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>395</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>336</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>308</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>117</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>113</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>40</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
@@ -49790,15 +48890,11 @@
           <t>24 277</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -49820,15 +48916,11 @@
           <t>Lecce</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
+      <c r="M228" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0.61</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -49840,155 +48932,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL228" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="AN228" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AP228" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AT228" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="Q228" t="n">
+        <v>5</v>
+      </c>
+      <c r="R228" t="n">
+        <v>20</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>6</v>
+      </c>
+      <c r="U228" t="n">
+        <v>4</v>
+      </c>
+      <c r="V228" t="n">
+        <v>12</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1</v>
+      </c>
+      <c r="X228" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>452</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>399</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>380</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>323</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>101</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>47</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
@@ -50068,15 +49100,11 @@
           <t>33 009</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -50098,15 +49126,11 @@
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
+      <c r="M229" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>2.32</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -50118,155 +49142,95 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T229" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL229" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="AN229" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AP229" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AT229" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="Q229" t="n">
+        <v>20</v>
+      </c>
+      <c r="R229" t="n">
+        <v>16</v>
+      </c>
+      <c r="S229" t="n">
+        <v>8</v>
+      </c>
+      <c r="T229" t="n">
+        <v>6</v>
+      </c>
+      <c r="U229" t="n">
+        <v>6</v>
+      </c>
+      <c r="V229" t="n">
+        <v>8</v>
+      </c>
+      <c r="W229" t="n">
+        <v>6</v>
+      </c>
+      <c r="X229" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>381</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>420</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>324</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>349</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>102</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>63</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>44</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
@@ -50346,15 +49310,11 @@
           <t>71 273</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G230" t="n">
+        <v>4</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -50376,15 +49336,11 @@
           <t>Venezia</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+      <c r="M230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0.43</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -50396,155 +49352,95 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="AN230" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AO230" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="AP230" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AT230" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="Q230" t="n">
+        <v>12</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6</v>
+      </c>
+      <c r="S230" t="n">
+        <v>8</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2</v>
+      </c>
+      <c r="V230" t="n">
+        <v>4</v>
+      </c>
+      <c r="W230" t="n">
+        <v>2</v>
+      </c>
+      <c r="X230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>571</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>338</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>525</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>284</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>98</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>61</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>29</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
@@ -50582,15 +49478,11 @@
       </c>
       <c r="BC230" t="inlineStr"/>
       <c r="BD230" t="inlineStr"/>
-      <c r="BE230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>1</v>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
@@ -50599,6 +49491,2456 @@
       <c r="BK230" t="inlineStr"/>
       <c r="BL230" t="inlineStr"/>
     </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>22 977</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr"/>
+      <c r="AR231" t="inlineStr"/>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AY231" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr"/>
+      <c r="BD231" t="inlineStr"/>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr"/>
+      <c r="BI231" t="inlineStr"/>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>h8xCR9dC</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>26.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Napoli</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AN232" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr"/>
+      <c r="AR232" t="inlineStr"/>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AY232" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr"/>
+      <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>OE5MGhrf</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>26.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>3 782</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Monza</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="AN233" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr"/>
+      <c r="AR233" t="inlineStr"/>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AY233" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr"/>
+      <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
+      <c r="BI233" t="inlineStr"/>
+      <c r="BJ233" t="inlineStr"/>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>baMp22np</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>25.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>28 575</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Sampdoria
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AN234" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AT234" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AY234" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr"/>
+      <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>xCj1xWPj</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>25.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>4 940</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Udinese</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="AN235" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AT235" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AY235" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>h2uVDr1f</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>25.09.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Rutella D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>3 347</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Cesena
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AN236" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AT236" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AY236" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SG7bDmCr</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>24.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>12 334</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Empoli
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AN237" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AT237" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AY237" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>WjBv9U0S</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>24.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Cagliari</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="AN238" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AT238" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="AY238" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="inlineStr"/>
+      <c r="BH238" t="inlineStr"/>
+      <c r="BI238" t="inlineStr"/>
+      <c r="BJ238" t="inlineStr"/>
+      <c r="BK238" t="inlineStr"/>
+      <c r="BL238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>O2Xm0vko</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>24.09.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>13 951</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Sassuolo
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="AN239" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AT239" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AY239" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE239" t="inlineStr"/>
+      <c r="BF239" t="inlineStr"/>
+      <c r="BG239" t="inlineStr"/>
+      <c r="BH239" t="inlineStr"/>
+      <c r="BI239" t="inlineStr"/>
+      <c r="BJ239" t="inlineStr"/>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL239"/>
+  <dimension ref="A1:BL247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49524,15 +49524,11 @@
           <t>22 977</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G231" t="n">
+        <v>2</v>
+      </c>
+      <c r="H231" t="n">
+        <v>3</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -49554,15 +49550,11 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
+      <c r="M231" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1.34</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -49574,135 +49566,83 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="AN231" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AP231" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
+      <c r="Q231" t="n">
+        <v>8</v>
+      </c>
+      <c r="R231" t="n">
+        <v>14</v>
+      </c>
+      <c r="S231" t="n">
+        <v>5</v>
+      </c>
+      <c r="T231" t="n">
+        <v>7</v>
+      </c>
+      <c r="U231" t="n">
+        <v>3</v>
+      </c>
+      <c r="V231" t="n">
+        <v>4</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>560</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>308</v>
       </c>
       <c r="AQ231" t="inlineStr"/>
       <c r="AR231" t="inlineStr"/>
@@ -49782,15 +49722,11 @@
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G232" t="n">
+        <v>5</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -49825,135 +49761,83 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R232" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="AN232" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+      <c r="Q232" t="n">
+        <v>16</v>
+      </c>
+      <c r="R232" t="n">
+        <v>10</v>
+      </c>
+      <c r="S232" t="n">
+        <v>7</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1</v>
+      </c>
+      <c r="U232" t="n">
+        <v>5</v>
+      </c>
+      <c r="V232" t="n">
+        <v>8</v>
+      </c>
+      <c r="W232" t="n">
+        <v>4</v>
+      </c>
+      <c r="X232" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>649</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>334</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>549</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>243</v>
       </c>
       <c r="AQ232" t="inlineStr"/>
       <c r="AR232" t="inlineStr"/>
@@ -49995,15 +49879,11 @@
       </c>
       <c r="BC232" t="inlineStr"/>
       <c r="BD232" t="inlineStr"/>
-      <c r="BE232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>1</v>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
@@ -50045,15 +49925,11 @@
           <t>3 782</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G233" t="n">
+        <v>3</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -50088,135 +49964,83 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R233" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T233" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="AN233" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="AO233" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="AP233" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
+      <c r="Q233" t="n">
+        <v>19</v>
+      </c>
+      <c r="R233" t="n">
+        <v>13</v>
+      </c>
+      <c r="S233" t="n">
+        <v>8</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3</v>
+      </c>
+      <c r="U233" t="n">
+        <v>6</v>
+      </c>
+      <c r="V233" t="n">
+        <v>8</v>
+      </c>
+      <c r="W233" t="n">
+        <v>5</v>
+      </c>
+      <c r="X233" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>634</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>446</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>531</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>359</v>
       </c>
       <c r="AQ233" t="inlineStr"/>
       <c r="AR233" t="inlineStr"/>
@@ -50300,15 +50124,11 @@
           <t>28 575</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -50343,155 +50163,95 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R234" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL234" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN234" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="AO234" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AP234" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AT234" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="Q234" t="n">
+        <v>11</v>
+      </c>
+      <c r="R234" t="n">
+        <v>14</v>
+      </c>
+      <c r="S234" t="n">
+        <v>3</v>
+      </c>
+      <c r="T234" t="n">
+        <v>4</v>
+      </c>
+      <c r="U234" t="n">
+        <v>5</v>
+      </c>
+      <c r="V234" t="n">
+        <v>7</v>
+      </c>
+      <c r="W234" t="n">
+        <v>3</v>
+      </c>
+      <c r="X234" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>288</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>524</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>182</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>388</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>96</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>128</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>48</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
@@ -50529,15 +50289,11 @@
       </c>
       <c r="BC234" t="inlineStr"/>
       <c r="BD234" t="inlineStr"/>
-      <c r="BE234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE234" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>1</v>
       </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
@@ -50579,15 +50335,11 @@
           <t>4 940</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -50622,155 +50374,95 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W235" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE235" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG235" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ235" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK235" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM235" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="AN235" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AO235" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="AP235" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AT235" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="Q235" t="n">
+        <v>15</v>
+      </c>
+      <c r="R235" t="n">
+        <v>13</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4</v>
+      </c>
+      <c r="T235" t="n">
+        <v>3</v>
+      </c>
+      <c r="U235" t="n">
+        <v>7</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3</v>
+      </c>
+      <c r="W235" t="n">
+        <v>4</v>
+      </c>
+      <c r="X235" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>537</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>496</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>433</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>390</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>86</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>84</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>35</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
@@ -50808,15 +50500,11 @@
       </c>
       <c r="BC235" t="inlineStr"/>
       <c r="BD235" t="inlineStr"/>
-      <c r="BE235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BE235" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>1</v>
       </c>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
@@ -50858,15 +50546,11 @@
           <t>3 347</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -50901,155 +50585,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R236" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T236" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="AN236" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AP236" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AT236" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="Q236" t="n">
+        <v>12</v>
+      </c>
+      <c r="R236" t="n">
+        <v>15</v>
+      </c>
+      <c r="S236" t="n">
+        <v>4</v>
+      </c>
+      <c r="T236" t="n">
+        <v>6</v>
+      </c>
+      <c r="U236" t="n">
+        <v>5</v>
+      </c>
+      <c r="V236" t="n">
+        <v>8</v>
+      </c>
+      <c r="W236" t="n">
+        <v>3</v>
+      </c>
+      <c r="X236" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>495</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>474</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>354</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>324</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>110</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>105</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>49</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>34</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
@@ -51085,15 +50709,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>0</v>
       </c>
       <c r="BE236" t="inlineStr"/>
       <c r="BF236" t="inlineStr"/>
@@ -51137,15 +50757,11 @@
           <t>12 334</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>2</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -51180,155 +50796,95 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R237" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AN237" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="AP237" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AT237" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="Q237" t="n">
+        <v>15</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7</v>
+      </c>
+      <c r="S237" t="n">
+        <v>5</v>
+      </c>
+      <c r="T237" t="n">
+        <v>2</v>
+      </c>
+      <c r="U237" t="n">
+        <v>5</v>
+      </c>
+      <c r="V237" t="n">
+        <v>2</v>
+      </c>
+      <c r="W237" t="n">
+        <v>5</v>
+      </c>
+      <c r="X237" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>506</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>400</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>381</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>290</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>92</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>56</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>39</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
@@ -51364,15 +50920,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>0</v>
       </c>
       <c r="BE237" t="inlineStr"/>
       <c r="BF237" t="inlineStr"/>
@@ -51416,15 +50968,11 @@
           <t>11 017</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -51459,155 +51007,95 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL238" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="AN238" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="AP238" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AT238" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="Q238" t="n">
+        <v>13</v>
+      </c>
+      <c r="R238" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0</v>
+      </c>
+      <c r="U238" t="n">
+        <v>8</v>
+      </c>
+      <c r="V238" t="n">
+        <v>1</v>
+      </c>
+      <c r="W238" t="n">
+        <v>1</v>
+      </c>
+      <c r="X238" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>469</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>502</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>371</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>422</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>34</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
@@ -51643,15 +51131,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC238" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>0</v>
       </c>
       <c r="BE238" t="inlineStr"/>
       <c r="BF238" t="inlineStr"/>
@@ -51695,15 +51179,11 @@
           <t>13 951</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -51738,155 +51218,95 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R239" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="AN239" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="AP239" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AT239" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="Q239" t="n">
+        <v>14</v>
+      </c>
+      <c r="R239" t="n">
+        <v>13</v>
+      </c>
+      <c r="S239" t="n">
+        <v>7</v>
+      </c>
+      <c r="T239" t="n">
+        <v>5</v>
+      </c>
+      <c r="U239" t="n">
+        <v>6</v>
+      </c>
+      <c r="V239" t="n">
+        <v>6</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1</v>
+      </c>
+      <c r="X239" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>599</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>339</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>531</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>263</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>143</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>83</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>72</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>32</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
@@ -51922,15 +51342,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>0</v>
       </c>
       <c r="BE239" t="inlineStr"/>
       <c r="BF239" t="inlineStr"/>
@@ -51941,6 +51357,2122 @@
       <c r="BK239" t="inlineStr"/>
       <c r="BL239" t="inlineStr"/>
     </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>28.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>27 126</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AN240" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr"/>
+      <c r="AR240" t="inlineStr"/>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AY240" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr"/>
+      <c r="BD240" t="inlineStr"/>
+      <c r="BE240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG240" t="inlineStr"/>
+      <c r="BH240" t="inlineStr"/>
+      <c r="BI240" t="inlineStr"/>
+      <c r="BJ240" t="inlineStr"/>
+      <c r="BK240" t="inlineStr"/>
+      <c r="BL240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AN241" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr"/>
+      <c r="AR241" t="inlineStr"/>
+      <c r="AS241" t="inlineStr"/>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="AY241" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA241" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr"/>
+      <c r="BD241" t="inlineStr"/>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="inlineStr"/>
+      <c r="BH241" t="inlineStr"/>
+      <c r="BI241" t="inlineStr"/>
+      <c r="BJ241" t="inlineStr"/>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>24 611</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr"/>
+      <c r="AR242" t="inlineStr"/>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AY242" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr"/>
+      <c r="BD242" t="inlineStr"/>
+      <c r="BE242" t="inlineStr"/>
+      <c r="BF242" t="inlineStr"/>
+      <c r="BG242" t="inlineStr"/>
+      <c r="BH242" t="inlineStr"/>
+      <c r="BI242" t="inlineStr"/>
+      <c r="BJ242" t="inlineStr"/>
+      <c r="BK242" t="inlineStr"/>
+      <c r="BL242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>71 103</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AN243" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr"/>
+      <c r="AR243" t="inlineStr"/>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AY243" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA243" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr"/>
+      <c r="BD243" t="inlineStr"/>
+      <c r="BE243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG243" t="inlineStr"/>
+      <c r="BH243" t="inlineStr"/>
+      <c r="BI243" t="inlineStr"/>
+      <c r="BJ243" t="inlineStr"/>
+      <c r="BK243" t="inlineStr"/>
+      <c r="BL243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>jwmmlzio</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>17 538</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AN244" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr"/>
+      <c r="AR244" t="inlineStr"/>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AY244" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA244" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr"/>
+      <c r="BD244" t="inlineStr"/>
+      <c r="BE244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG244" t="inlineStr"/>
+      <c r="BH244" t="inlineStr"/>
+      <c r="BI244" t="inlineStr"/>
+      <c r="BJ244" t="inlineStr"/>
+      <c r="BK244" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL244" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>vaTsAHD4</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2 280</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr"/>
+      <c r="AR245" t="inlineStr"/>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AY245" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr"/>
+      <c r="BD245" t="inlineStr"/>
+      <c r="BE245" t="inlineStr"/>
+      <c r="BF245" t="inlineStr"/>
+      <c r="BG245" t="inlineStr"/>
+      <c r="BH245" t="inlineStr"/>
+      <c r="BI245" t="inlineStr"/>
+      <c r="BJ245" t="inlineStr"/>
+      <c r="BK245" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BL245" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>4USV4sgM</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>5 405</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr"/>
+      <c r="AR246" t="inlineStr"/>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AY246" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr"/>
+      <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="inlineStr"/>
+      <c r="BH246" t="inlineStr"/>
+      <c r="BI246" t="inlineStr"/>
+      <c r="BJ246" t="inlineStr"/>
+      <c r="BK246" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BL246" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>8vLb6ZCT</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>3 204</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr"/>
+      <c r="AR247" t="inlineStr"/>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="AY247" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA247" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr"/>
+      <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="inlineStr"/>
+      <c r="BH247" t="inlineStr"/>
+      <c r="BI247" t="inlineStr"/>
+      <c r="BJ247" t="inlineStr"/>
+      <c r="BK247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL247" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL247"/>
+  <dimension ref="A1:BL256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51390,15 +51390,11 @@
           <t>27 126</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -51420,15 +51416,11 @@
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="M240" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N240" t="n">
+        <v>1.5</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -51440,135 +51432,83 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T240" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AN240" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
+      <c r="Q240" t="n">
+        <v>5</v>
+      </c>
+      <c r="R240" t="n">
+        <v>23</v>
+      </c>
+      <c r="S240" t="n">
+        <v>1</v>
+      </c>
+      <c r="T240" t="n">
+        <v>5</v>
+      </c>
+      <c r="U240" t="n">
+        <v>1</v>
+      </c>
+      <c r="V240" t="n">
+        <v>11</v>
+      </c>
+      <c r="W240" t="n">
+        <v>3</v>
+      </c>
+      <c r="X240" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>296</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>522</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>225</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>454</v>
       </c>
       <c r="AQ240" t="inlineStr"/>
       <c r="AR240" t="inlineStr"/>
@@ -51610,15 +51550,11 @@
       </c>
       <c r="BC240" t="inlineStr"/>
       <c r="BD240" t="inlineStr"/>
-      <c r="BE240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF240" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>0</v>
       </c>
       <c r="BG240" t="inlineStr"/>
       <c r="BH240" t="inlineStr"/>
@@ -51656,15 +51592,11 @@
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -51686,15 +51618,11 @@
           <t>Juventus</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="M241" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N241" t="n">
+        <v>2.75</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -51706,135 +51634,83 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AN241" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="AP241" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
+      <c r="Q241" t="n">
+        <v>7</v>
+      </c>
+      <c r="R241" t="n">
+        <v>12</v>
+      </c>
+      <c r="S241" t="n">
+        <v>2</v>
+      </c>
+      <c r="T241" t="n">
+        <v>3</v>
+      </c>
+      <c r="U241" t="n">
+        <v>1</v>
+      </c>
+      <c r="V241" t="n">
+        <v>7</v>
+      </c>
+      <c r="W241" t="n">
+        <v>4</v>
+      </c>
+      <c r="X241" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>355</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>697</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>267</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>577</v>
       </c>
       <c r="AQ241" t="inlineStr"/>
       <c r="AR241" t="inlineStr"/>
@@ -51918,15 +51794,11 @@
           <t>24 611</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" t="n">
+        <v>3</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -51948,15 +51820,11 @@
           <t>Inter</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
+      <c r="M242" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N242" t="n">
+        <v>2.89</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -51968,135 +51836,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R242" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T242" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL242" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="AN242" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
+      <c r="Q242" t="n">
+        <v>10</v>
+      </c>
+      <c r="R242" t="n">
+        <v>16</v>
+      </c>
+      <c r="S242" t="n">
+        <v>3</v>
+      </c>
+      <c r="T242" t="n">
+        <v>7</v>
+      </c>
+      <c r="U242" t="n">
+        <v>2</v>
+      </c>
+      <c r="V242" t="n">
+        <v>6</v>
+      </c>
+      <c r="W242" t="n">
+        <v>5</v>
+      </c>
+      <c r="X242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>416</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>648</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>346</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>583</v>
       </c>
       <c r="AQ242" t="inlineStr"/>
       <c r="AR242" t="inlineStr"/>
@@ -52180,15 +51996,11 @@
           <t>71 103</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -52210,15 +52022,11 @@
           <t>Lecce</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="M243" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1.14</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -52230,135 +52038,83 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R243" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="AN243" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="Q243" t="n">
+        <v>15</v>
+      </c>
+      <c r="R243" t="n">
+        <v>16</v>
+      </c>
+      <c r="S243" t="n">
+        <v>6</v>
+      </c>
+      <c r="T243" t="n">
+        <v>7</v>
+      </c>
+      <c r="U243" t="n">
+        <v>7</v>
+      </c>
+      <c r="V243" t="n">
+        <v>6</v>
+      </c>
+      <c r="W243" t="n">
+        <v>2</v>
+      </c>
+      <c r="X243" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>497</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>368</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>458</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>328</v>
       </c>
       <c r="AQ243" t="inlineStr"/>
       <c r="AR243" t="inlineStr"/>
@@ -52400,15 +52156,11 @@
       </c>
       <c r="BC243" t="inlineStr"/>
       <c r="BD243" t="inlineStr"/>
-      <c r="BE243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE243" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>0</v>
       </c>
       <c r="BG243" t="inlineStr"/>
       <c r="BH243" t="inlineStr"/>
@@ -52450,15 +52202,11 @@
           <t>17 538</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -52492,135 +52240,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AN244" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
+      <c r="Q244" t="n">
+        <v>12</v>
+      </c>
+      <c r="R244" t="n">
+        <v>11</v>
+      </c>
+      <c r="S244" t="n">
+        <v>1</v>
+      </c>
+      <c r="T244" t="n">
+        <v>4</v>
+      </c>
+      <c r="U244" t="n">
+        <v>4</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3</v>
+      </c>
+      <c r="W244" t="n">
+        <v>7</v>
+      </c>
+      <c r="X244" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>328</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>329</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>266</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>267</v>
       </c>
       <c r="AQ244" t="inlineStr"/>
       <c r="AR244" t="inlineStr"/>
@@ -52662,29 +52358,21 @@
       </c>
       <c r="BC244" t="inlineStr"/>
       <c r="BD244" t="inlineStr"/>
-      <c r="BE244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE244" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>0</v>
       </c>
       <c r="BG244" t="inlineStr"/>
       <c r="BH244" t="inlineStr"/>
       <c r="BI244" t="inlineStr"/>
       <c r="BJ244" t="inlineStr"/>
-      <c r="BK244" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL244" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="BK244" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="245">
@@ -52720,15 +52408,11 @@
           <t>2 280</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -52762,135 +52446,83 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="AN245" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
+      <c r="Q245" t="n">
+        <v>17</v>
+      </c>
+      <c r="R245" t="n">
+        <v>10</v>
+      </c>
+      <c r="S245" t="n">
+        <v>6</v>
+      </c>
+      <c r="T245" t="n">
+        <v>4</v>
+      </c>
+      <c r="U245" t="n">
+        <v>4</v>
+      </c>
+      <c r="V245" t="n">
+        <v>4</v>
+      </c>
+      <c r="W245" t="n">
+        <v>7</v>
+      </c>
+      <c r="X245" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>357</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>357</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>265</v>
       </c>
       <c r="AQ245" t="inlineStr"/>
       <c r="AR245" t="inlineStr"/>
@@ -52938,15 +52570,11 @@
       <c r="BH245" t="inlineStr"/>
       <c r="BI245" t="inlineStr"/>
       <c r="BJ245" t="inlineStr"/>
-      <c r="BK245" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BL245" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="BK245" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="246">
@@ -52982,15 +52610,11 @@
           <t>5 405</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -53024,135 +52648,83 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="AN246" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+      <c r="Q246" t="n">
+        <v>12</v>
+      </c>
+      <c r="R246" t="n">
+        <v>13</v>
+      </c>
+      <c r="S246" t="n">
+        <v>3</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1</v>
+      </c>
+      <c r="U246" t="n">
+        <v>5</v>
+      </c>
+      <c r="V246" t="n">
+        <v>6</v>
+      </c>
+      <c r="W246" t="n">
+        <v>4</v>
+      </c>
+      <c r="X246" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>540</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>352</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>274</v>
       </c>
       <c r="AQ246" t="inlineStr"/>
       <c r="AR246" t="inlineStr"/>
@@ -53200,15 +52772,11 @@
       <c r="BH246" t="inlineStr"/>
       <c r="BI246" t="inlineStr"/>
       <c r="BJ246" t="inlineStr"/>
-      <c r="BK246" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BL246" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="BK246" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="247">
@@ -53244,15 +52812,11 @@
           <t>3 204</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>2</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -53286,135 +52850,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="AN247" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="AO247" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="AP247" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
+      <c r="Q247" t="n">
+        <v>12</v>
+      </c>
+      <c r="R247" t="n">
+        <v>17</v>
+      </c>
+      <c r="S247" t="n">
+        <v>4</v>
+      </c>
+      <c r="T247" t="n">
+        <v>5</v>
+      </c>
+      <c r="U247" t="n">
+        <v>7</v>
+      </c>
+      <c r="V247" t="n">
+        <v>6</v>
+      </c>
+      <c r="W247" t="n">
+        <v>1</v>
+      </c>
+      <c r="X247" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>372</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>396</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>268</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>307</v>
       </c>
       <c r="AQ247" t="inlineStr"/>
       <c r="AR247" t="inlineStr"/>
@@ -53462,14 +52974,2392 @@
       <c r="BH247" t="inlineStr"/>
       <c r="BI247" t="inlineStr"/>
       <c r="BJ247" t="inlineStr"/>
-      <c r="BK247" t="inlineStr">
+      <c r="BK247" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="BL247" t="inlineStr">
-        <is>
-          <t>41</t>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr"/>
+      <c r="AR248" t="inlineStr"/>
+      <c r="AS248" t="inlineStr"/>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AY248" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>13 053</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr"/>
+      <c r="AR249" t="inlineStr"/>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AY249" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA249" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD249" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
+      <c r="BI249" t="inlineStr"/>
+      <c r="BJ249" t="inlineStr"/>
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>62 165</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr"/>
+      <c r="AR250" t="inlineStr"/>
+      <c r="AS250" t="inlineStr"/>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="AY250" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr"/>
+      <c r="BD250" t="inlineStr"/>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr"/>
+      <c r="BH250" t="inlineStr"/>
+      <c r="BI250" t="inlineStr"/>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>9 000</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="AN251" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr"/>
+      <c r="AR251" t="inlineStr"/>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="AY251" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr"/>
+      <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
+      <c r="BI251" t="inlineStr"/>
+      <c r="BJ251" t="inlineStr"/>
+      <c r="BK251" t="inlineStr"/>
+      <c r="BL251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>29.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>23 130</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr"/>
+      <c r="AR252" t="inlineStr"/>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AY252" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA252" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr"/>
+      <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="inlineStr"/>
+      <c r="BI252" t="inlineStr"/>
+      <c r="BJ252" t="inlineStr"/>
+      <c r="BK252" t="inlineStr"/>
+      <c r="BL252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>nPWk8erH</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>23 860</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>12 326</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="AN253" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr"/>
+      <c r="AR253" t="inlineStr"/>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="AY253" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr"/>
+      <c r="BD253" t="inlineStr"/>
+      <c r="BE253" t="inlineStr"/>
+      <c r="BF253" t="inlineStr"/>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
+      <c r="BI253" t="inlineStr"/>
+      <c r="BJ253" t="inlineStr"/>
+      <c r="BK253" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BL253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>ID6U0Dzi</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Stadio Romeo Menti
+ (Castellammare di Stabia)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>13 000</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>6 500</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN254" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr"/>
+      <c r="AR254" t="inlineStr"/>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AY254" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA254" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr"/>
+      <c r="BD254" t="inlineStr"/>
+      <c r="BE254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG254" t="inlineStr"/>
+      <c r="BH254" t="inlineStr"/>
+      <c r="BI254" t="inlineStr"/>
+      <c r="BJ254" t="inlineStr"/>
+      <c r="BK254" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BL254" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>zkyF8Pgc</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>10 101</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AN255" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr"/>
+      <c r="AR255" t="inlineStr"/>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AY255" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr"/>
+      <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
+      <c r="BG255" t="inlineStr"/>
+      <c r="BH255" t="inlineStr"/>
+      <c r="BI255" t="inlineStr"/>
+      <c r="BJ255" t="inlineStr"/>
+      <c r="BK255" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BL255" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>14 932</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AN256" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr"/>
+      <c r="AR256" t="inlineStr"/>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="AY256" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr"/>
+      <c r="BD256" t="inlineStr"/>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="inlineStr"/>
+      <c r="BH256" t="inlineStr"/>
+      <c r="BI256" t="inlineStr"/>
+      <c r="BJ256" t="inlineStr"/>
+      <c r="BK256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL256" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL268"/>
+  <dimension ref="A1:BL279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55506,15 +55506,11 @@
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G260" t="n">
+        <v>5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -55536,15 +55532,11 @@
           <t>Genoa</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+      <c r="M260" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.59</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -55556,127 +55548,79 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q260" t="n">
+        <v>22</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7</v>
+      </c>
+      <c r="S260" t="n">
+        <v>10</v>
+      </c>
+      <c r="T260" t="n">
+        <v>3</v>
+      </c>
+      <c r="U260" t="n">
+        <v>8</v>
+      </c>
+      <c r="V260" t="n">
+        <v>1</v>
+      </c>
+      <c r="W260" t="n">
+        <v>4</v>
+      </c>
+      <c r="X260" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>10</v>
       </c>
       <c r="AK260" t="inlineStr"/>
       <c r="AL260" t="inlineStr"/>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="AN260" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="AP260" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="AM260" t="n">
+        <v>613</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>362</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>567</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>304</v>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
@@ -55760,15 +55704,11 @@
           <t>21 441</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -55790,15 +55730,11 @@
           <t>Lecce</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+      <c r="M261" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.26</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -55810,135 +55746,83 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="AN261" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="AO261" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AP261" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
+      <c r="Q261" t="n">
+        <v>13</v>
+      </c>
+      <c r="R261" t="n">
+        <v>9</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4</v>
+      </c>
+      <c r="T261" t="n">
+        <v>3</v>
+      </c>
+      <c r="U261" t="n">
+        <v>5</v>
+      </c>
+      <c r="V261" t="n">
+        <v>5</v>
+      </c>
+      <c r="W261" t="n">
+        <v>4</v>
+      </c>
+      <c r="X261" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>459</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>371</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>272</v>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
@@ -56022,15 +55906,11 @@
           <t>25 979</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -56052,15 +55932,11 @@
           <t>Venezia</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
+      <c r="M262" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N262" t="n">
+        <v>2.01</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -56072,135 +55948,83 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AN262" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
+      <c r="Q262" t="n">
+        <v>20</v>
+      </c>
+      <c r="R262" t="n">
+        <v>14</v>
+      </c>
+      <c r="S262" t="n">
+        <v>3</v>
+      </c>
+      <c r="T262" t="n">
+        <v>2</v>
+      </c>
+      <c r="U262" t="n">
+        <v>10</v>
+      </c>
+      <c r="V262" t="n">
+        <v>8</v>
+      </c>
+      <c r="W262" t="n">
+        <v>7</v>
+      </c>
+      <c r="X262" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>370</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>281</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>292</v>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
@@ -56284,15 +56108,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G263" t="n">
+        <v>3</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -56314,15 +56134,11 @@
           <t>Como</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="M263" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0.95</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -56334,135 +56150,83 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="AN263" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
+      <c r="Q263" t="n">
+        <v>9</v>
+      </c>
+      <c r="R263" t="n">
+        <v>11</v>
+      </c>
+      <c r="S263" t="n">
+        <v>6</v>
+      </c>
+      <c r="T263" t="n">
+        <v>2</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
+      <c r="V263" t="n">
+        <v>8</v>
+      </c>
+      <c r="W263" t="n">
+        <v>3</v>
+      </c>
+      <c r="X263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>469</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>681</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>394</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>620</v>
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
@@ -56542,15 +56306,11 @@
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -56584,135 +56344,83 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R264" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="AN264" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="AP264" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+      <c r="Q264" t="n">
+        <v>15</v>
+      </c>
+      <c r="R264" t="n">
+        <v>4</v>
+      </c>
+      <c r="S264" t="n">
+        <v>3</v>
+      </c>
+      <c r="T264" t="n">
+        <v>3</v>
+      </c>
+      <c r="U264" t="n">
+        <v>9</v>
+      </c>
+      <c r="V264" t="n">
+        <v>1</v>
+      </c>
+      <c r="W264" t="n">
+        <v>3</v>
+      </c>
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>437</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>314</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>365</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>229</v>
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
@@ -56758,15 +56466,11 @@
       <c r="BF264" t="inlineStr"/>
       <c r="BG264" t="inlineStr"/>
       <c r="BH264" t="inlineStr"/>
-      <c r="BI264" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ264" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="BI264" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>27</v>
       </c>
       <c r="BK264" t="inlineStr"/>
       <c r="BL264" t="inlineStr"/>
@@ -56800,15 +56504,11 @@
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G265" t="n">
+        <v>3</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -56842,135 +56542,83 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R265" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T265" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="AN265" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
+      <c r="Q265" t="n">
+        <v>14</v>
+      </c>
+      <c r="R265" t="n">
+        <v>6</v>
+      </c>
+      <c r="S265" t="n">
+        <v>7</v>
+      </c>
+      <c r="T265" t="n">
+        <v>2</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3</v>
+      </c>
+      <c r="V265" t="n">
+        <v>4</v>
+      </c>
+      <c r="W265" t="n">
+        <v>4</v>
+      </c>
+      <c r="X265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>196</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>303</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>143</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>253</v>
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
@@ -57016,15 +56664,11 @@
       <c r="BF265" t="inlineStr"/>
       <c r="BG265" t="inlineStr"/>
       <c r="BH265" t="inlineStr"/>
-      <c r="BI265" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BJ265" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="BI265" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>18</v>
       </c>
       <c r="BK265" t="inlineStr"/>
       <c r="BL265" t="inlineStr"/>
@@ -57058,15 +56702,11 @@
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G266" t="n">
+        <v>6</v>
+      </c>
+      <c r="H266" t="n">
+        <v>1</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -57100,135 +56740,83 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="AN266" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO266" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="AP266" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+      <c r="Q266" t="n">
+        <v>19</v>
+      </c>
+      <c r="R266" t="n">
+        <v>11</v>
+      </c>
+      <c r="S266" t="n">
+        <v>13</v>
+      </c>
+      <c r="T266" t="n">
+        <v>4</v>
+      </c>
+      <c r="U266" t="n">
+        <v>2</v>
+      </c>
+      <c r="V266" t="n">
+        <v>5</v>
+      </c>
+      <c r="W266" t="n">
+        <v>4</v>
+      </c>
+      <c r="X266" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>504</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>350</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>428</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>274</v>
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
@@ -57274,15 +56862,11 @@
       <c r="BF266" t="inlineStr"/>
       <c r="BG266" t="inlineStr"/>
       <c r="BH266" t="inlineStr"/>
-      <c r="BI266" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ266" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BI266" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>17</v>
       </c>
       <c r="BK266" t="inlineStr"/>
       <c r="BL266" t="inlineStr"/>
@@ -57316,15 +56900,11 @@
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -57358,135 +56938,83 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AN267" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
+      <c r="Q267" t="n">
+        <v>12</v>
+      </c>
+      <c r="R267" t="n">
+        <v>15</v>
+      </c>
+      <c r="S267" t="n">
+        <v>2</v>
+      </c>
+      <c r="T267" t="n">
+        <v>3</v>
+      </c>
+      <c r="U267" t="n">
+        <v>6</v>
+      </c>
+      <c r="V267" t="n">
+        <v>6</v>
+      </c>
+      <c r="W267" t="n">
+        <v>4</v>
+      </c>
+      <c r="X267" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>329</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>444</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>233</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>346</v>
       </c>
       <c r="AQ267" t="inlineStr">
         <is>
@@ -57532,15 +57060,11 @@
       <c r="BF267" t="inlineStr"/>
       <c r="BG267" t="inlineStr"/>
       <c r="BH267" t="inlineStr"/>
-      <c r="BI267" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BJ267" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="BI267" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>19</v>
       </c>
       <c r="BK267" t="inlineStr"/>
       <c r="BL267" t="inlineStr"/>
@@ -57574,15 +57098,11 @@
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -57616,135 +57136,83 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AN268" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AO268" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="Q268" t="n">
+        <v>16</v>
+      </c>
+      <c r="R268" t="n">
+        <v>7</v>
+      </c>
+      <c r="S268" t="n">
+        <v>4</v>
+      </c>
+      <c r="T268" t="n">
+        <v>3</v>
+      </c>
+      <c r="U268" t="n">
+        <v>9</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3</v>
+      </c>
+      <c r="W268" t="n">
+        <v>3</v>
+      </c>
+      <c r="X268" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>369</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>331</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>269</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>228</v>
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
@@ -57790,18 +57258,2968 @@
       <c r="BF268" t="inlineStr"/>
       <c r="BG268" t="inlineStr"/>
       <c r="BH268" t="inlineStr"/>
-      <c r="BI268" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BJ268" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="BI268" t="n">
+        <v>17</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>18</v>
       </c>
       <c r="BK268" t="inlineStr"/>
       <c r="BL268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>21 923</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AN269" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AT269" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AU269" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr"/>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr"/>
+      <c r="BD269" t="inlineStr"/>
+      <c r="BE269" t="inlineStr"/>
+      <c r="BF269" t="inlineStr"/>
+      <c r="BG269" t="inlineStr"/>
+      <c r="BH269" t="inlineStr"/>
+      <c r="BI269" t="inlineStr"/>
+      <c r="BJ269" t="inlineStr"/>
+      <c r="BK269" t="inlineStr"/>
+      <c r="BL269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>06.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>12 021</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AN270" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AT270" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="AU270" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr"/>
+      <c r="BB270" t="inlineStr"/>
+      <c r="BC270" t="inlineStr"/>
+      <c r="BD270" t="inlineStr"/>
+      <c r="BE270" t="inlineStr"/>
+      <c r="BF270" t="inlineStr"/>
+      <c r="BG270" t="inlineStr"/>
+      <c r="BH270" t="inlineStr"/>
+      <c r="BI270" t="inlineStr"/>
+      <c r="BJ270" t="inlineStr"/>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>28 400</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AN271" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AT271" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AU271" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr"/>
+      <c r="BD271" t="inlineStr"/>
+      <c r="BE271" t="inlineStr"/>
+      <c r="BF271" t="inlineStr"/>
+      <c r="BG271" t="inlineStr"/>
+      <c r="BH271" t="inlineStr"/>
+      <c r="BI271" t="inlineStr"/>
+      <c r="BJ271" t="inlineStr"/>
+      <c r="BK271" t="inlineStr"/>
+      <c r="BL271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>38 000</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="AN272" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AT272" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AU272" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="inlineStr"/>
+      <c r="BD272" t="inlineStr"/>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="inlineStr"/>
+      <c r="BH272" t="inlineStr"/>
+      <c r="BI272" t="inlineStr"/>
+      <c r="BJ272" t="inlineStr"/>
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>06.10.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>40 557</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="AN273" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AT273" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AU273" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr"/>
+      <c r="BD273" t="inlineStr"/>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="inlineStr"/>
+      <c r="BH273" t="inlineStr"/>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>05.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>73 348</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="AN274" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AT274" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AU274" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr"/>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr"/>
+      <c r="BD274" t="inlineStr"/>
+      <c r="BE274" t="inlineStr"/>
+      <c r="BF274" t="inlineStr"/>
+      <c r="BG274" t="inlineStr"/>
+      <c r="BH274" t="inlineStr"/>
+      <c r="BI274" t="inlineStr"/>
+      <c r="BJ274" t="inlineStr"/>
+      <c r="BK274" t="inlineStr"/>
+      <c r="BL274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>tAM9caod</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>8 394</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AN275" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AT275" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AU275" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr"/>
+      <c r="BA275" t="inlineStr"/>
+      <c r="BB275" t="inlineStr"/>
+      <c r="BC275" t="inlineStr"/>
+      <c r="BD275" t="inlineStr"/>
+      <c r="BE275" t="inlineStr"/>
+      <c r="BF275" t="inlineStr"/>
+      <c r="BG275" t="inlineStr"/>
+      <c r="BH275" t="inlineStr"/>
+      <c r="BI275" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BJ275" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>8GEeL2w3</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>6 771</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="AN276" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AT276" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AU276" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr"/>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr"/>
+      <c r="BD276" t="inlineStr"/>
+      <c r="BE276" t="inlineStr"/>
+      <c r="BF276" t="inlineStr"/>
+      <c r="BG276" t="inlineStr"/>
+      <c r="BH276" t="inlineStr"/>
+      <c r="BI276" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ276" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BK276" t="inlineStr"/>
+      <c r="BL276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>4r84Jt8F</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>9 942</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AN277" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AT277" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AU277" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr"/>
+      <c r="BA277" t="inlineStr"/>
+      <c r="BB277" t="inlineStr"/>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="inlineStr"/>
+      <c r="BF277" t="inlineStr"/>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
+      <c r="BI277" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ277" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>KG9yCb0k</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Stadio Danilo Martelli
+ (Mantova)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>10 317</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="AN278" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AT278" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AU278" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr"/>
+      <c r="BA278" t="inlineStr"/>
+      <c r="BB278" t="inlineStr"/>
+      <c r="BC278" t="inlineStr"/>
+      <c r="BD278" t="inlineStr"/>
+      <c r="BE278" t="inlineStr"/>
+      <c r="BF278" t="inlineStr"/>
+      <c r="BG278" t="inlineStr"/>
+      <c r="BH278" t="inlineStr"/>
+      <c r="BI278" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ278" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BK278" t="inlineStr"/>
+      <c r="BL278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>StDqAxV1</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Stadio Renzo Barbera
+ (Palermo)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>36 349</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>25 460</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL279" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AN279" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AT279" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AU279" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr"/>
+      <c r="BA279" t="inlineStr"/>
+      <c r="BB279" t="inlineStr"/>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="inlineStr"/>
+      <c r="BF279" t="inlineStr"/>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="inlineStr"/>
+      <c r="BI279" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ279" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL279"/>
+  <dimension ref="A1:BN288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,16 @@
       <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
         </is>
       </c>
     </row>
@@ -946,6 +956,8 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1148,6 +1160,8 @@
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1354,6 +1368,8 @@
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1556,6 +1572,8 @@
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1762,6 +1780,8 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1964,6 +1984,8 @@
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2170,6 +2192,8 @@
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2368,6 +2392,8 @@
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2570,6 +2596,8 @@
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2776,6 +2804,8 @@
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2978,6 +3008,8 @@
       <c r="BJ12" t="inlineStr"/>
       <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3180,6 +3212,8 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3386,6 +3420,8 @@
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3588,6 +3624,8 @@
       <c r="BJ15" t="inlineStr"/>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3790,6 +3828,8 @@
       <c r="BJ16" t="inlineStr"/>
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3996,6 +4036,8 @@
       <c r="BJ17" t="inlineStr"/>
       <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -4198,6 +4240,8 @@
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4404,6 +4448,8 @@
       <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4610,6 +4656,8 @@
       <c r="BJ20" t="inlineStr"/>
       <c r="BK20" t="inlineStr"/>
       <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -4812,6 +4860,8 @@
       <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
       <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -5022,6 +5072,8 @@
       <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
       <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5236,6 +5288,8 @@
       <c r="BJ23" t="inlineStr"/>
       <c r="BK23" t="inlineStr"/>
       <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5446,6 +5500,8 @@
       <c r="BJ24" t="inlineStr"/>
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5656,6 +5712,8 @@
       <c r="BJ25" t="inlineStr"/>
       <c r="BK25" t="inlineStr"/>
       <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -5866,6 +5924,8 @@
       <c r="BJ26" t="inlineStr"/>
       <c r="BK26" t="inlineStr"/>
       <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -6076,6 +6136,8 @@
       <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
       <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -6286,6 +6348,8 @@
       <c r="BJ28" t="inlineStr"/>
       <c r="BK28" t="inlineStr"/>
       <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6500,6 +6564,8 @@
       <c r="BJ29" t="inlineStr"/>
       <c r="BK29" t="inlineStr"/>
       <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6710,6 +6776,8 @@
       <c r="BJ30" t="inlineStr"/>
       <c r="BK30" t="inlineStr"/>
       <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -6920,6 +6988,8 @@
       <c r="BJ31" t="inlineStr"/>
       <c r="BK31" t="inlineStr"/>
       <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7130,6 +7200,8 @@
       <c r="BJ32" t="inlineStr"/>
       <c r="BK32" t="inlineStr"/>
       <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -7340,6 +7412,8 @@
       <c r="BJ33" t="inlineStr"/>
       <c r="BK33" t="inlineStr"/>
       <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -7550,6 +7624,8 @@
       <c r="BJ34" t="inlineStr"/>
       <c r="BK34" t="inlineStr"/>
       <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -7760,6 +7836,8 @@
       <c r="BJ35" t="inlineStr"/>
       <c r="BK35" t="inlineStr"/>
       <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -7974,6 +8052,8 @@
       <c r="BJ36" t="inlineStr"/>
       <c r="BK36" t="inlineStr"/>
       <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -8192,6 +8272,8 @@
       <c r="BJ37" t="inlineStr"/>
       <c r="BK37" t="inlineStr"/>
       <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8406,6 +8488,8 @@
       <c r="BJ38" t="inlineStr"/>
       <c r="BK38" t="inlineStr"/>
       <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8624,6 +8708,8 @@
       <c r="BJ39" t="inlineStr"/>
       <c r="BK39" t="inlineStr"/>
       <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -8834,6 +8920,8 @@
       <c r="BJ40" t="inlineStr"/>
       <c r="BK40" t="inlineStr"/>
       <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -9048,6 +9136,8 @@
       <c r="BJ41" t="inlineStr"/>
       <c r="BK41" t="inlineStr"/>
       <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -9258,6 +9348,8 @@
       <c r="BJ42" t="inlineStr"/>
       <c r="BK42" t="inlineStr"/>
       <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -9468,6 +9560,8 @@
       <c r="BJ43" t="inlineStr"/>
       <c r="BK43" t="inlineStr"/>
       <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -9678,6 +9772,8 @@
       <c r="BJ44" t="inlineStr"/>
       <c r="BK44" t="inlineStr"/>
       <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -9888,6 +9984,8 @@
       <c r="BJ45" t="inlineStr"/>
       <c r="BK45" t="inlineStr"/>
       <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -10098,6 +10196,8 @@
       <c r="BJ46" t="inlineStr"/>
       <c r="BK46" t="inlineStr"/>
       <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -10308,6 +10408,8 @@
       <c r="BJ47" t="inlineStr"/>
       <c r="BK47" t="inlineStr"/>
       <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -10518,6 +10620,8 @@
       <c r="BJ48" t="inlineStr"/>
       <c r="BK48" t="inlineStr"/>
       <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -10728,6 +10832,8 @@
       <c r="BJ49" t="inlineStr"/>
       <c r="BK49" t="inlineStr"/>
       <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -10938,6 +11044,8 @@
       <c r="BJ50" t="inlineStr"/>
       <c r="BK50" t="inlineStr"/>
       <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -11152,6 +11260,8 @@
       <c r="BJ51" t="inlineStr"/>
       <c r="BK51" t="inlineStr"/>
       <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -11362,6 +11472,8 @@
       <c r="BJ52" t="inlineStr"/>
       <c r="BK52" t="inlineStr"/>
       <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -11572,6 +11684,8 @@
       <c r="BJ53" t="inlineStr"/>
       <c r="BK53" t="inlineStr"/>
       <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -11782,6 +11896,8 @@
       <c r="BJ54" t="inlineStr"/>
       <c r="BK54" t="inlineStr"/>
       <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -11992,6 +12108,8 @@
       <c r="BJ55" t="inlineStr"/>
       <c r="BK55" t="inlineStr"/>
       <c r="BL55" t="inlineStr"/>
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -12202,6 +12320,8 @@
       <c r="BJ56" t="inlineStr"/>
       <c r="BK56" t="inlineStr"/>
       <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -12412,6 +12532,8 @@
       <c r="BJ57" t="inlineStr"/>
       <c r="BK57" t="inlineStr"/>
       <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -12622,6 +12744,8 @@
       <c r="BJ58" t="inlineStr"/>
       <c r="BK58" t="inlineStr"/>
       <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -12832,6 +12956,8 @@
       <c r="BJ59" t="inlineStr"/>
       <c r="BK59" t="inlineStr"/>
       <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="inlineStr"/>
+      <c r="BN59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -13042,6 +13168,8 @@
       <c r="BJ60" t="inlineStr"/>
       <c r="BK60" t="inlineStr"/>
       <c r="BL60" t="inlineStr"/>
+      <c r="BM60" t="inlineStr"/>
+      <c r="BN60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -13256,6 +13384,8 @@
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
       <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
+      <c r="BN61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -13474,6 +13604,8 @@
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
       <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
+      <c r="BN62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -13692,6 +13824,8 @@
       <c r="BJ63" t="inlineStr"/>
       <c r="BK63" t="inlineStr"/>
       <c r="BL63" t="inlineStr"/>
+      <c r="BM63" t="inlineStr"/>
+      <c r="BN63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -13910,6 +14044,8 @@
       <c r="BJ64" t="inlineStr"/>
       <c r="BK64" t="inlineStr"/>
       <c r="BL64" t="inlineStr"/>
+      <c r="BM64" t="inlineStr"/>
+      <c r="BN64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -14128,6 +14264,8 @@
       <c r="BJ65" t="inlineStr"/>
       <c r="BK65" t="inlineStr"/>
       <c r="BL65" t="inlineStr"/>
+      <c r="BM65" t="inlineStr"/>
+      <c r="BN65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -14346,6 +14484,8 @@
       <c r="BJ66" t="inlineStr"/>
       <c r="BK66" t="inlineStr"/>
       <c r="BL66" t="inlineStr"/>
+      <c r="BM66" t="inlineStr"/>
+      <c r="BN66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -14564,6 +14704,8 @@
       <c r="BJ67" t="inlineStr"/>
       <c r="BK67" t="inlineStr"/>
       <c r="BL67" t="inlineStr"/>
+      <c r="BM67" t="inlineStr"/>
+      <c r="BN67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -14778,6 +14920,8 @@
       <c r="BJ68" t="inlineStr"/>
       <c r="BK68" t="inlineStr"/>
       <c r="BL68" t="inlineStr"/>
+      <c r="BM68" t="inlineStr"/>
+      <c r="BN68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -14996,6 +15140,8 @@
       <c r="BJ69" t="inlineStr"/>
       <c r="BK69" t="inlineStr"/>
       <c r="BL69" t="inlineStr"/>
+      <c r="BM69" t="inlineStr"/>
+      <c r="BN69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -15218,6 +15364,8 @@
       <c r="BJ70" t="inlineStr"/>
       <c r="BK70" t="inlineStr"/>
       <c r="BL70" t="inlineStr"/>
+      <c r="BM70" t="inlineStr"/>
+      <c r="BN70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -15436,6 +15584,8 @@
       <c r="BJ71" t="inlineStr"/>
       <c r="BK71" t="inlineStr"/>
       <c r="BL71" t="inlineStr"/>
+      <c r="BM71" t="inlineStr"/>
+      <c r="BN71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -15654,6 +15804,8 @@
       <c r="BJ72" t="inlineStr"/>
       <c r="BK72" t="inlineStr"/>
       <c r="BL72" t="inlineStr"/>
+      <c r="BM72" t="inlineStr"/>
+      <c r="BN72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -15872,6 +16024,8 @@
       <c r="BJ73" t="inlineStr"/>
       <c r="BK73" t="inlineStr"/>
       <c r="BL73" t="inlineStr"/>
+      <c r="BM73" t="inlineStr"/>
+      <c r="BN73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -16086,6 +16240,8 @@
       <c r="BJ74" t="inlineStr"/>
       <c r="BK74" t="inlineStr"/>
       <c r="BL74" t="inlineStr"/>
+      <c r="BM74" t="inlineStr"/>
+      <c r="BN74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -16308,6 +16464,8 @@
       <c r="BJ75" t="inlineStr"/>
       <c r="BK75" t="inlineStr"/>
       <c r="BL75" t="inlineStr"/>
+      <c r="BM75" t="inlineStr"/>
+      <c r="BN75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -16526,6 +16684,8 @@
       <c r="BJ76" t="inlineStr"/>
       <c r="BK76" t="inlineStr"/>
       <c r="BL76" t="inlineStr"/>
+      <c r="BM76" t="inlineStr"/>
+      <c r="BN76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -16744,6 +16904,8 @@
       <c r="BJ77" t="inlineStr"/>
       <c r="BK77" t="inlineStr"/>
       <c r="BL77" t="inlineStr"/>
+      <c r="BM77" t="inlineStr"/>
+      <c r="BN77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -16966,6 +17128,8 @@
       <c r="BJ78" t="inlineStr"/>
       <c r="BK78" t="inlineStr"/>
       <c r="BL78" t="inlineStr"/>
+      <c r="BM78" t="inlineStr"/>
+      <c r="BN78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -17188,6 +17352,8 @@
       <c r="BJ79" t="inlineStr"/>
       <c r="BK79" t="inlineStr"/>
       <c r="BL79" t="inlineStr"/>
+      <c r="BM79" t="inlineStr"/>
+      <c r="BN79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -17406,6 +17572,8 @@
       <c r="BJ80" t="inlineStr"/>
       <c r="BK80" t="inlineStr"/>
       <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr"/>
+      <c r="BN80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -17624,6 +17792,8 @@
       <c r="BJ81" t="inlineStr"/>
       <c r="BK81" t="inlineStr"/>
       <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -17842,6 +18012,8 @@
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>
       <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -18060,6 +18232,8 @@
       <c r="BJ83" t="inlineStr"/>
       <c r="BK83" t="inlineStr"/>
       <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="inlineStr"/>
+      <c r="BN83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -18278,6 +18452,8 @@
       <c r="BJ84" t="inlineStr"/>
       <c r="BK84" t="inlineStr"/>
       <c r="BL84" t="inlineStr"/>
+      <c r="BM84" t="inlineStr"/>
+      <c r="BN84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -18496,6 +18672,8 @@
       <c r="BJ85" t="inlineStr"/>
       <c r="BK85" t="inlineStr"/>
       <c r="BL85" t="inlineStr"/>
+      <c r="BM85" t="inlineStr"/>
+      <c r="BN85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -18714,6 +18892,8 @@
       <c r="BJ86" t="inlineStr"/>
       <c r="BK86" t="inlineStr"/>
       <c r="BL86" t="inlineStr"/>
+      <c r="BM86" t="inlineStr"/>
+      <c r="BN86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -18932,6 +19112,8 @@
       <c r="BJ87" t="inlineStr"/>
       <c r="BK87" t="inlineStr"/>
       <c r="BL87" t="inlineStr"/>
+      <c r="BM87" t="inlineStr"/>
+      <c r="BN87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -19154,6 +19336,8 @@
       <c r="BJ88" t="inlineStr"/>
       <c r="BK88" t="inlineStr"/>
       <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -19372,6 +19556,8 @@
       <c r="BJ89" t="inlineStr"/>
       <c r="BK89" t="inlineStr"/>
       <c r="BL89" t="inlineStr"/>
+      <c r="BM89" t="inlineStr"/>
+      <c r="BN89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -19590,6 +19776,8 @@
       <c r="BJ90" t="inlineStr"/>
       <c r="BK90" t="inlineStr"/>
       <c r="BL90" t="inlineStr"/>
+      <c r="BM90" t="inlineStr"/>
+      <c r="BN90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -19808,6 +19996,8 @@
       <c r="BJ91" t="inlineStr"/>
       <c r="BK91" t="inlineStr"/>
       <c r="BL91" t="inlineStr"/>
+      <c r="BM91" t="inlineStr"/>
+      <c r="BN91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -20022,6 +20212,8 @@
       <c r="BJ92" t="inlineStr"/>
       <c r="BK92" t="inlineStr"/>
       <c r="BL92" t="inlineStr"/>
+      <c r="BM92" t="inlineStr"/>
+      <c r="BN92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -20236,6 +20428,8 @@
       <c r="BJ93" t="inlineStr"/>
       <c r="BK93" t="inlineStr"/>
       <c r="BL93" t="inlineStr"/>
+      <c r="BM93" t="inlineStr"/>
+      <c r="BN93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -20454,6 +20648,8 @@
       <c r="BJ94" t="inlineStr"/>
       <c r="BK94" t="inlineStr"/>
       <c r="BL94" t="inlineStr"/>
+      <c r="BM94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -20672,6 +20868,8 @@
       <c r="BJ95" t="inlineStr"/>
       <c r="BK95" t="inlineStr"/>
       <c r="BL95" t="inlineStr"/>
+      <c r="BM95" t="inlineStr"/>
+      <c r="BN95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -20890,6 +21088,8 @@
       <c r="BJ96" t="inlineStr"/>
       <c r="BK96" t="inlineStr"/>
       <c r="BL96" t="inlineStr"/>
+      <c r="BM96" t="inlineStr"/>
+      <c r="BN96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -21108,6 +21308,8 @@
       <c r="BJ97" t="inlineStr"/>
       <c r="BK97" t="inlineStr"/>
       <c r="BL97" t="inlineStr"/>
+      <c r="BM97" t="inlineStr"/>
+      <c r="BN97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -21326,6 +21528,8 @@
       <c r="BJ98" t="inlineStr"/>
       <c r="BK98" t="inlineStr"/>
       <c r="BL98" t="inlineStr"/>
+      <c r="BM98" t="inlineStr"/>
+      <c r="BN98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -21548,6 +21752,8 @@
       <c r="BJ99" t="inlineStr"/>
       <c r="BK99" t="inlineStr"/>
       <c r="BL99" t="inlineStr"/>
+      <c r="BM99" t="inlineStr"/>
+      <c r="BN99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -21766,6 +21972,8 @@
       <c r="BJ100" t="inlineStr"/>
       <c r="BK100" t="inlineStr"/>
       <c r="BL100" t="inlineStr"/>
+      <c r="BM100" t="inlineStr"/>
+      <c r="BN100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -21984,6 +22192,8 @@
       <c r="BJ101" t="inlineStr"/>
       <c r="BK101" t="inlineStr"/>
       <c r="BL101" t="inlineStr"/>
+      <c r="BM101" t="inlineStr"/>
+      <c r="BN101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -22202,6 +22412,8 @@
       <c r="BJ102" t="inlineStr"/>
       <c r="BK102" t="inlineStr"/>
       <c r="BL102" t="inlineStr"/>
+      <c r="BM102" t="inlineStr"/>
+      <c r="BN102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -22420,6 +22632,8 @@
       <c r="BJ103" t="inlineStr"/>
       <c r="BK103" t="inlineStr"/>
       <c r="BL103" t="inlineStr"/>
+      <c r="BM103" t="inlineStr"/>
+      <c r="BN103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -22638,6 +22852,8 @@
       <c r="BJ104" t="inlineStr"/>
       <c r="BK104" t="inlineStr"/>
       <c r="BL104" t="inlineStr"/>
+      <c r="BM104" t="inlineStr"/>
+      <c r="BN104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -22856,6 +23072,8 @@
       <c r="BJ105" t="inlineStr"/>
       <c r="BK105" t="inlineStr"/>
       <c r="BL105" t="inlineStr"/>
+      <c r="BM105" t="inlineStr"/>
+      <c r="BN105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -23074,6 +23292,8 @@
       <c r="BJ106" t="inlineStr"/>
       <c r="BK106" t="inlineStr"/>
       <c r="BL106" t="inlineStr"/>
+      <c r="BM106" t="inlineStr"/>
+      <c r="BN106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -23296,6 +23516,8 @@
       <c r="BJ107" t="inlineStr"/>
       <c r="BK107" t="inlineStr"/>
       <c r="BL107" t="inlineStr"/>
+      <c r="BM107" t="inlineStr"/>
+      <c r="BN107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -23514,6 +23736,8 @@
       <c r="BJ108" t="inlineStr"/>
       <c r="BK108" t="inlineStr"/>
       <c r="BL108" t="inlineStr"/>
+      <c r="BM108" t="inlineStr"/>
+      <c r="BN108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -23732,6 +23956,8 @@
       <c r="BJ109" t="inlineStr"/>
       <c r="BK109" t="inlineStr"/>
       <c r="BL109" t="inlineStr"/>
+      <c r="BM109" t="inlineStr"/>
+      <c r="BN109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -23950,6 +24176,8 @@
       <c r="BJ110" t="inlineStr"/>
       <c r="BK110" t="inlineStr"/>
       <c r="BL110" t="inlineStr"/>
+      <c r="BM110" t="inlineStr"/>
+      <c r="BN110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -24168,6 +24396,8 @@
       <c r="BJ111" t="inlineStr"/>
       <c r="BK111" t="inlineStr"/>
       <c r="BL111" t="inlineStr"/>
+      <c r="BM111" t="inlineStr"/>
+      <c r="BN111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -24386,6 +24616,8 @@
       <c r="BJ112" t="inlineStr"/>
       <c r="BK112" t="inlineStr"/>
       <c r="BL112" t="inlineStr"/>
+      <c r="BM112" t="inlineStr"/>
+      <c r="BN112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -24596,6 +24828,8 @@
       <c r="BJ113" t="inlineStr"/>
       <c r="BK113" t="inlineStr"/>
       <c r="BL113" t="inlineStr"/>
+      <c r="BM113" t="inlineStr"/>
+      <c r="BN113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -24818,6 +25052,8 @@
       <c r="BJ114" t="inlineStr"/>
       <c r="BK114" t="inlineStr"/>
       <c r="BL114" t="inlineStr"/>
+      <c r="BM114" t="inlineStr"/>
+      <c r="BN114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -25036,6 +25272,8 @@
       <c r="BJ115" t="inlineStr"/>
       <c r="BK115" t="inlineStr"/>
       <c r="BL115" t="inlineStr"/>
+      <c r="BM115" t="inlineStr"/>
+      <c r="BN115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -25250,6 +25488,8 @@
       <c r="BJ116" t="inlineStr"/>
       <c r="BK116" t="inlineStr"/>
       <c r="BL116" t="inlineStr"/>
+      <c r="BM116" t="inlineStr"/>
+      <c r="BN116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -25468,6 +25708,8 @@
       <c r="BJ117" t="inlineStr"/>
       <c r="BK117" t="inlineStr"/>
       <c r="BL117" t="inlineStr"/>
+      <c r="BM117" t="inlineStr"/>
+      <c r="BN117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -25686,6 +25928,8 @@
       <c r="BJ118" t="inlineStr"/>
       <c r="BK118" t="inlineStr"/>
       <c r="BL118" t="inlineStr"/>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -25904,6 +26148,8 @@
       <c r="BJ119" t="inlineStr"/>
       <c r="BK119" t="inlineStr"/>
       <c r="BL119" t="inlineStr"/>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -26122,6 +26368,8 @@
       <c r="BJ120" t="inlineStr"/>
       <c r="BK120" t="inlineStr"/>
       <c r="BL120" t="inlineStr"/>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -26340,6 +26588,8 @@
       <c r="BJ121" t="inlineStr"/>
       <c r="BK121" t="inlineStr"/>
       <c r="BL121" t="inlineStr"/>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -26558,6 +26808,8 @@
       <c r="BJ122" t="inlineStr"/>
       <c r="BK122" t="inlineStr"/>
       <c r="BL122" t="inlineStr"/>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -26776,6 +27028,8 @@
       <c r="BJ123" t="inlineStr"/>
       <c r="BK123" t="inlineStr"/>
       <c r="BL123" t="inlineStr"/>
+      <c r="BM123" t="inlineStr"/>
+      <c r="BN123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -26994,6 +27248,8 @@
       <c r="BJ124" t="inlineStr"/>
       <c r="BK124" t="inlineStr"/>
       <c r="BL124" t="inlineStr"/>
+      <c r="BM124" t="inlineStr"/>
+      <c r="BN124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -27212,6 +27468,8 @@
       <c r="BJ125" t="inlineStr"/>
       <c r="BK125" t="inlineStr"/>
       <c r="BL125" t="inlineStr"/>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -27430,6 +27688,8 @@
       <c r="BJ126" t="inlineStr"/>
       <c r="BK126" t="inlineStr"/>
       <c r="BL126" t="inlineStr"/>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -27648,6 +27908,8 @@
       <c r="BJ127" t="inlineStr"/>
       <c r="BK127" t="inlineStr"/>
       <c r="BL127" t="inlineStr"/>
+      <c r="BM127" t="inlineStr"/>
+      <c r="BN127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -27870,6 +28132,8 @@
       <c r="BJ128" t="inlineStr"/>
       <c r="BK128" t="inlineStr"/>
       <c r="BL128" t="inlineStr"/>
+      <c r="BM128" t="inlineStr"/>
+      <c r="BN128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -28088,6 +28352,8 @@
       <c r="BJ129" t="inlineStr"/>
       <c r="BK129" t="inlineStr"/>
       <c r="BL129" t="inlineStr"/>
+      <c r="BM129" t="inlineStr"/>
+      <c r="BN129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -28310,6 +28576,8 @@
       <c r="BJ130" t="inlineStr"/>
       <c r="BK130" t="inlineStr"/>
       <c r="BL130" t="inlineStr"/>
+      <c r="BM130" t="inlineStr"/>
+      <c r="BN130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -28528,6 +28796,8 @@
       <c r="BJ131" t="inlineStr"/>
       <c r="BK131" t="inlineStr"/>
       <c r="BL131" t="inlineStr"/>
+      <c r="BM131" t="inlineStr"/>
+      <c r="BN131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -28746,6 +29016,8 @@
       <c r="BJ132" t="inlineStr"/>
       <c r="BK132" t="inlineStr"/>
       <c r="BL132" t="inlineStr"/>
+      <c r="BM132" t="inlineStr"/>
+      <c r="BN132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -28964,6 +29236,8 @@
       <c r="BJ133" t="inlineStr"/>
       <c r="BK133" t="inlineStr"/>
       <c r="BL133" t="inlineStr"/>
+      <c r="BM133" t="inlineStr"/>
+      <c r="BN133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -29182,6 +29456,8 @@
       <c r="BJ134" t="inlineStr"/>
       <c r="BK134" t="inlineStr"/>
       <c r="BL134" t="inlineStr"/>
+      <c r="BM134" t="inlineStr"/>
+      <c r="BN134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -29400,6 +29676,8 @@
       <c r="BJ135" t="inlineStr"/>
       <c r="BK135" t="inlineStr"/>
       <c r="BL135" t="inlineStr"/>
+      <c r="BM135" t="inlineStr"/>
+      <c r="BN135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -29618,6 +29896,8 @@
       <c r="BJ136" t="inlineStr"/>
       <c r="BK136" t="inlineStr"/>
       <c r="BL136" t="inlineStr"/>
+      <c r="BM136" t="inlineStr"/>
+      <c r="BN136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -29836,6 +30116,8 @@
       <c r="BJ137" t="inlineStr"/>
       <c r="BK137" t="inlineStr"/>
       <c r="BL137" t="inlineStr"/>
+      <c r="BM137" t="inlineStr"/>
+      <c r="BN137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -30054,6 +30336,8 @@
       <c r="BJ138" t="inlineStr"/>
       <c r="BK138" t="inlineStr"/>
       <c r="BL138" t="inlineStr"/>
+      <c r="BM138" t="inlineStr"/>
+      <c r="BN138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -30272,6 +30556,8 @@
       <c r="BJ139" t="inlineStr"/>
       <c r="BK139" t="inlineStr"/>
       <c r="BL139" t="inlineStr"/>
+      <c r="BM139" t="inlineStr"/>
+      <c r="BN139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -30490,6 +30776,8 @@
       <c r="BJ140" t="inlineStr"/>
       <c r="BK140" t="inlineStr"/>
       <c r="BL140" t="inlineStr"/>
+      <c r="BM140" t="inlineStr"/>
+      <c r="BN140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -30712,6 +31000,8 @@
       <c r="BJ141" t="inlineStr"/>
       <c r="BK141" t="inlineStr"/>
       <c r="BL141" t="inlineStr"/>
+      <c r="BM141" t="inlineStr"/>
+      <c r="BN141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -30930,6 +31220,8 @@
       <c r="BJ142" t="inlineStr"/>
       <c r="BK142" t="inlineStr"/>
       <c r="BL142" t="inlineStr"/>
+      <c r="BM142" t="inlineStr"/>
+      <c r="BN142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -31148,6 +31440,8 @@
       <c r="BJ143" t="inlineStr"/>
       <c r="BK143" t="inlineStr"/>
       <c r="BL143" t="inlineStr"/>
+      <c r="BM143" t="inlineStr"/>
+      <c r="BN143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -31366,6 +31660,8 @@
       <c r="BJ144" t="inlineStr"/>
       <c r="BK144" t="inlineStr"/>
       <c r="BL144" t="inlineStr"/>
+      <c r="BM144" t="inlineStr"/>
+      <c r="BN144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -31584,6 +31880,8 @@
       <c r="BJ145" t="inlineStr"/>
       <c r="BK145" t="inlineStr"/>
       <c r="BL145" t="inlineStr"/>
+      <c r="BM145" t="inlineStr"/>
+      <c r="BN145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -31802,6 +32100,8 @@
       <c r="BJ146" t="inlineStr"/>
       <c r="BK146" t="inlineStr"/>
       <c r="BL146" t="inlineStr"/>
+      <c r="BM146" t="inlineStr"/>
+      <c r="BN146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -32020,6 +32320,8 @@
       <c r="BJ147" t="inlineStr"/>
       <c r="BK147" t="inlineStr"/>
       <c r="BL147" t="inlineStr"/>
+      <c r="BM147" t="inlineStr"/>
+      <c r="BN147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -32238,6 +32540,8 @@
       <c r="BJ148" t="inlineStr"/>
       <c r="BK148" t="inlineStr"/>
       <c r="BL148" t="inlineStr"/>
+      <c r="BM148" t="inlineStr"/>
+      <c r="BN148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -32456,6 +32760,8 @@
       <c r="BJ149" t="inlineStr"/>
       <c r="BK149" t="inlineStr"/>
       <c r="BL149" t="inlineStr"/>
+      <c r="BM149" t="inlineStr"/>
+      <c r="BN149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -32674,6 +32980,8 @@
       <c r="BJ150" t="inlineStr"/>
       <c r="BK150" t="inlineStr"/>
       <c r="BL150" t="inlineStr"/>
+      <c r="BM150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -32896,6 +33204,8 @@
       <c r="BJ151" t="inlineStr"/>
       <c r="BK151" t="inlineStr"/>
       <c r="BL151" t="inlineStr"/>
+      <c r="BM151" t="inlineStr"/>
+      <c r="BN151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -33114,6 +33424,8 @@
       <c r="BJ152" t="inlineStr"/>
       <c r="BK152" t="inlineStr"/>
       <c r="BL152" t="inlineStr"/>
+      <c r="BM152" t="inlineStr"/>
+      <c r="BN152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -33332,6 +33644,8 @@
       <c r="BJ153" t="inlineStr"/>
       <c r="BK153" t="inlineStr"/>
       <c r="BL153" t="inlineStr"/>
+      <c r="BM153" t="inlineStr"/>
+      <c r="BN153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -33550,6 +33864,8 @@
       <c r="BJ154" t="inlineStr"/>
       <c r="BK154" t="inlineStr"/>
       <c r="BL154" t="inlineStr"/>
+      <c r="BM154" t="inlineStr"/>
+      <c r="BN154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -33768,6 +34084,8 @@
       <c r="BJ155" t="inlineStr"/>
       <c r="BK155" t="inlineStr"/>
       <c r="BL155" t="inlineStr"/>
+      <c r="BM155" t="inlineStr"/>
+      <c r="BN155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -33990,6 +34308,8 @@
       <c r="BJ156" t="inlineStr"/>
       <c r="BK156" t="inlineStr"/>
       <c r="BL156" t="inlineStr"/>
+      <c r="BM156" t="inlineStr"/>
+      <c r="BN156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -34208,6 +34528,8 @@
       <c r="BJ157" t="inlineStr"/>
       <c r="BK157" t="inlineStr"/>
       <c r="BL157" t="inlineStr"/>
+      <c r="BM157" t="inlineStr"/>
+      <c r="BN157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -34426,6 +34748,8 @@
       <c r="BJ158" t="inlineStr"/>
       <c r="BK158" t="inlineStr"/>
       <c r="BL158" t="inlineStr"/>
+      <c r="BM158" t="inlineStr"/>
+      <c r="BN158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -34644,6 +34968,8 @@
       <c r="BJ159" t="inlineStr"/>
       <c r="BK159" t="inlineStr"/>
       <c r="BL159" t="inlineStr"/>
+      <c r="BM159" t="inlineStr"/>
+      <c r="BN159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -34862,6 +35188,8 @@
       <c r="BJ160" t="inlineStr"/>
       <c r="BK160" t="inlineStr"/>
       <c r="BL160" t="inlineStr"/>
+      <c r="BM160" t="inlineStr"/>
+      <c r="BN160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -35080,6 +35408,8 @@
       <c r="BJ161" t="inlineStr"/>
       <c r="BK161" t="inlineStr"/>
       <c r="BL161" t="inlineStr"/>
+      <c r="BM161" t="inlineStr"/>
+      <c r="BN161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -35283,6 +35613,8 @@
       <c r="BJ162" t="inlineStr"/>
       <c r="BK162" t="inlineStr"/>
       <c r="BL162" t="inlineStr"/>
+      <c r="BM162" t="inlineStr"/>
+      <c r="BN162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -35482,6 +35814,8 @@
       <c r="BJ163" t="inlineStr"/>
       <c r="BK163" t="inlineStr"/>
       <c r="BL163" t="inlineStr"/>
+      <c r="BM163" t="inlineStr"/>
+      <c r="BN163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -35693,6 +36027,8 @@
       <c r="BJ164" t="inlineStr"/>
       <c r="BK164" t="inlineStr"/>
       <c r="BL164" t="inlineStr"/>
+      <c r="BM164" t="inlineStr"/>
+      <c r="BN164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -35904,6 +36240,8 @@
       <c r="BJ165" t="inlineStr"/>
       <c r="BK165" t="inlineStr"/>
       <c r="BL165" t="inlineStr"/>
+      <c r="BM165" t="inlineStr"/>
+      <c r="BN165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -36115,6 +36453,8 @@
       <c r="BJ166" t="inlineStr"/>
       <c r="BK166" t="inlineStr"/>
       <c r="BL166" t="inlineStr"/>
+      <c r="BM166" t="inlineStr"/>
+      <c r="BN166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -36326,6 +36666,8 @@
       <c r="BJ167" t="inlineStr"/>
       <c r="BK167" t="inlineStr"/>
       <c r="BL167" t="inlineStr"/>
+      <c r="BM167" t="inlineStr"/>
+      <c r="BN167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -36537,6 +36879,8 @@
       <c r="BJ168" t="inlineStr"/>
       <c r="BK168" t="inlineStr"/>
       <c r="BL168" t="inlineStr"/>
+      <c r="BM168" t="inlineStr"/>
+      <c r="BN168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -36748,6 +37092,8 @@
       <c r="BJ169" t="inlineStr"/>
       <c r="BK169" t="inlineStr"/>
       <c r="BL169" t="inlineStr"/>
+      <c r="BM169" t="inlineStr"/>
+      <c r="BN169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -36959,6 +37305,8 @@
       <c r="BJ170" t="inlineStr"/>
       <c r="BK170" t="inlineStr"/>
       <c r="BL170" t="inlineStr"/>
+      <c r="BM170" t="inlineStr"/>
+      <c r="BN170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -37174,6 +37522,8 @@
       <c r="BJ171" t="inlineStr"/>
       <c r="BK171" t="inlineStr"/>
       <c r="BL171" t="inlineStr"/>
+      <c r="BM171" t="inlineStr"/>
+      <c r="BN171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -37385,6 +37735,8 @@
       <c r="BJ172" t="inlineStr"/>
       <c r="BK172" t="inlineStr"/>
       <c r="BL172" t="inlineStr"/>
+      <c r="BM172" t="inlineStr"/>
+      <c r="BN172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -37600,6 +37952,8 @@
       <c r="BJ173" t="inlineStr"/>
       <c r="BK173" t="inlineStr"/>
       <c r="BL173" t="inlineStr"/>
+      <c r="BM173" t="inlineStr"/>
+      <c r="BN173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -37815,6 +38169,8 @@
       <c r="BJ174" t="inlineStr"/>
       <c r="BK174" t="inlineStr"/>
       <c r="BL174" t="inlineStr"/>
+      <c r="BM174" t="inlineStr"/>
+      <c r="BN174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -38030,6 +38386,8 @@
       <c r="BJ175" t="inlineStr"/>
       <c r="BK175" t="inlineStr"/>
       <c r="BL175" t="inlineStr"/>
+      <c r="BM175" t="inlineStr"/>
+      <c r="BN175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -38241,6 +38599,8 @@
       <c r="BJ176" t="inlineStr"/>
       <c r="BK176" t="inlineStr"/>
       <c r="BL176" t="inlineStr"/>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -38452,6 +38812,8 @@
       <c r="BJ177" t="inlineStr"/>
       <c r="BK177" t="inlineStr"/>
       <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -38663,6 +39025,8 @@
       <c r="BJ178" t="inlineStr"/>
       <c r="BK178" t="inlineStr"/>
       <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -38874,6 +39238,8 @@
       <c r="BJ179" t="inlineStr"/>
       <c r="BK179" t="inlineStr"/>
       <c r="BL179" t="inlineStr"/>
+      <c r="BM179" t="inlineStr"/>
+      <c r="BN179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -39085,6 +39451,8 @@
       <c r="BJ180" t="inlineStr"/>
       <c r="BK180" t="inlineStr"/>
       <c r="BL180" t="inlineStr"/>
+      <c r="BM180" t="inlineStr"/>
+      <c r="BN180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -39296,6 +39664,8 @@
       <c r="BJ181" t="inlineStr"/>
       <c r="BK181" t="inlineStr"/>
       <c r="BL181" t="inlineStr"/>
+      <c r="BM181" t="inlineStr"/>
+      <c r="BN181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -39507,6 +39877,8 @@
       <c r="BJ182" t="inlineStr"/>
       <c r="BK182" t="inlineStr"/>
       <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="inlineStr"/>
+      <c r="BN182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -39710,6 +40082,8 @@
       <c r="BJ183" t="inlineStr"/>
       <c r="BK183" t="inlineStr"/>
       <c r="BL183" t="inlineStr"/>
+      <c r="BM183" t="inlineStr"/>
+      <c r="BN183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -39909,6 +40283,8 @@
       <c r="BJ184" t="inlineStr"/>
       <c r="BK184" t="inlineStr"/>
       <c r="BL184" t="inlineStr"/>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -40104,6 +40480,8 @@
       <c r="BJ185" t="inlineStr"/>
       <c r="BK185" t="inlineStr"/>
       <c r="BL185" t="inlineStr"/>
+      <c r="BM185" t="inlineStr"/>
+      <c r="BN185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -40222,6 +40600,8 @@
       <c r="BJ186" t="inlineStr"/>
       <c r="BK186" t="inlineStr"/>
       <c r="BL186" t="inlineStr"/>
+      <c r="BM186" t="inlineStr"/>
+      <c r="BN186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -40340,6 +40720,8 @@
       <c r="BJ187" t="inlineStr"/>
       <c r="BK187" t="inlineStr"/>
       <c r="BL187" t="inlineStr"/>
+      <c r="BM187" t="inlineStr"/>
+      <c r="BN187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -40458,6 +40840,8 @@
       <c r="BJ188" t="inlineStr"/>
       <c r="BK188" t="inlineStr"/>
       <c r="BL188" t="inlineStr"/>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -40576,6 +40960,8 @@
       <c r="BJ189" t="inlineStr"/>
       <c r="BK189" t="inlineStr"/>
       <c r="BL189" t="inlineStr"/>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -40778,6 +41164,8 @@
       </c>
       <c r="BK190" t="inlineStr"/>
       <c r="BL190" t="inlineStr"/>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -40980,6 +41368,8 @@
       </c>
       <c r="BK191" t="inlineStr"/>
       <c r="BL191" t="inlineStr"/>
+      <c r="BM191" t="inlineStr"/>
+      <c r="BN191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -41182,6 +41572,8 @@
       </c>
       <c r="BK192" t="inlineStr"/>
       <c r="BL192" t="inlineStr"/>
+      <c r="BM192" t="inlineStr"/>
+      <c r="BN192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -41388,6 +41780,8 @@
       </c>
       <c r="BK193" t="inlineStr"/>
       <c r="BL193" t="inlineStr"/>
+      <c r="BM193" t="inlineStr"/>
+      <c r="BN193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -41590,6 +41984,8 @@
       </c>
       <c r="BK194" t="inlineStr"/>
       <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="inlineStr"/>
+      <c r="BN194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -41792,6 +42188,8 @@
       </c>
       <c r="BK195" t="inlineStr"/>
       <c r="BL195" t="inlineStr"/>
+      <c r="BM195" t="inlineStr"/>
+      <c r="BN195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -41998,6 +42396,8 @@
       </c>
       <c r="BK196" t="inlineStr"/>
       <c r="BL196" t="inlineStr"/>
+      <c r="BM196" t="inlineStr"/>
+      <c r="BN196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -42200,6 +42600,8 @@
       </c>
       <c r="BK197" t="inlineStr"/>
       <c r="BL197" t="inlineStr"/>
+      <c r="BM197" t="inlineStr"/>
+      <c r="BN197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -42402,6 +42804,8 @@
       </c>
       <c r="BK198" t="inlineStr"/>
       <c r="BL198" t="inlineStr"/>
+      <c r="BM198" t="inlineStr"/>
+      <c r="BN198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -42604,6 +43008,8 @@
       </c>
       <c r="BK199" t="inlineStr"/>
       <c r="BL199" t="inlineStr"/>
+      <c r="BM199" t="inlineStr"/>
+      <c r="BN199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -42818,6 +43224,8 @@
       <c r="BL200" t="n">
         <v>8</v>
       </c>
+      <c r="BM200" t="inlineStr"/>
+      <c r="BN200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -43032,6 +43440,8 @@
       <c r="BL201" t="n">
         <v>18</v>
       </c>
+      <c r="BM201" t="inlineStr"/>
+      <c r="BN201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -43246,6 +43656,8 @@
       <c r="BL202" t="n">
         <v>20</v>
       </c>
+      <c r="BM202" t="inlineStr"/>
+      <c r="BN202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -43460,6 +43872,8 @@
       <c r="BL203" t="n">
         <v>14</v>
       </c>
+      <c r="BM203" t="inlineStr"/>
+      <c r="BN203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -43674,6 +44088,8 @@
       <c r="BL204" t="n">
         <v>16</v>
       </c>
+      <c r="BM204" t="inlineStr"/>
+      <c r="BN204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -43888,6 +44304,8 @@
       <c r="BL205" t="n">
         <v>21</v>
       </c>
+      <c r="BM205" t="inlineStr"/>
+      <c r="BN205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -44102,6 +44520,8 @@
       <c r="BL206" t="n">
         <v>20</v>
       </c>
+      <c r="BM206" t="inlineStr"/>
+      <c r="BN206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -44316,6 +44736,8 @@
       <c r="BL207" t="n">
         <v>23</v>
       </c>
+      <c r="BM207" t="inlineStr"/>
+      <c r="BN207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -44530,6 +44952,8 @@
       <c r="BL208" t="n">
         <v>9</v>
       </c>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -44744,6 +45168,8 @@
       <c r="BL209" t="n">
         <v>6</v>
       </c>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -44958,6 +45384,8 @@
       <c r="BL210" t="n">
         <v>21</v>
       </c>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -45172,6 +45600,8 @@
       <c r="BL211" t="n">
         <v>18</v>
       </c>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -45386,6 +45816,8 @@
       <c r="BL212" t="n">
         <v>14</v>
       </c>
+      <c r="BM212" t="inlineStr"/>
+      <c r="BN212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -45600,6 +46032,8 @@
       <c r="BL213" t="n">
         <v>11</v>
       </c>
+      <c r="BM213" t="inlineStr"/>
+      <c r="BN213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -45818,6 +46252,8 @@
       <c r="BL214" t="n">
         <v>18</v>
       </c>
+      <c r="BM214" t="inlineStr"/>
+      <c r="BN214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -46036,6 +46472,8 @@
       <c r="BL215" t="n">
         <v>12</v>
       </c>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -46250,6 +46688,8 @@
       <c r="BL216" t="n">
         <v>12</v>
       </c>
+      <c r="BM216" t="inlineStr"/>
+      <c r="BN216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -46464,6 +46904,8 @@
       <c r="BL217" t="n">
         <v>19</v>
       </c>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -46678,6 +47120,8 @@
       <c r="BL218" t="n">
         <v>15</v>
       </c>
+      <c r="BM218" t="inlineStr"/>
+      <c r="BN218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -46896,6 +47340,8 @@
       <c r="BL219" t="n">
         <v>19</v>
       </c>
+      <c r="BM219" t="inlineStr"/>
+      <c r="BN219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -47110,6 +47556,8 @@
       <c r="BL220" t="n">
         <v>11</v>
       </c>
+      <c r="BM220" t="inlineStr"/>
+      <c r="BN220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -47328,6 +47776,8 @@
       <c r="BL221" t="n">
         <v>15</v>
       </c>
+      <c r="BM221" t="inlineStr"/>
+      <c r="BN221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -47542,6 +47992,8 @@
       <c r="BL222" t="n">
         <v>11</v>
       </c>
+      <c r="BM222" t="inlineStr"/>
+      <c r="BN222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -47756,6 +48208,8 @@
       <c r="BL223" t="n">
         <v>10</v>
       </c>
+      <c r="BM223" t="inlineStr"/>
+      <c r="BN223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -47970,6 +48424,8 @@
       <c r="BL224" t="n">
         <v>15</v>
       </c>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -48184,6 +48640,8 @@
       <c r="BL225" t="n">
         <v>8</v>
       </c>
+      <c r="BM225" t="inlineStr"/>
+      <c r="BN225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -48398,6 +48856,8 @@
       <c r="BL226" t="n">
         <v>8</v>
       </c>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -48612,6 +49072,8 @@
       <c r="BL227" t="n">
         <v>15</v>
       </c>
+      <c r="BM227" t="inlineStr"/>
+      <c r="BN227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -48826,6 +49288,8 @@
       <c r="BL228" t="n">
         <v>19</v>
       </c>
+      <c r="BM228" t="inlineStr"/>
+      <c r="BN228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -49044,6 +49508,8 @@
       <c r="BL229" t="n">
         <v>10</v>
       </c>
+      <c r="BM229" t="inlineStr"/>
+      <c r="BN229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -49258,6 +49724,8 @@
       <c r="BL230" t="n">
         <v>7</v>
       </c>
+      <c r="BM230" t="inlineStr"/>
+      <c r="BN230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -49472,6 +49940,8 @@
       <c r="BL231" t="n">
         <v>15</v>
       </c>
+      <c r="BM231" t="inlineStr"/>
+      <c r="BN231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -49686,6 +50156,8 @@
       <c r="BL232" t="n">
         <v>13</v>
       </c>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -49904,6 +50376,8 @@
       <c r="BL233" t="n">
         <v>12</v>
       </c>
+      <c r="BM233" t="inlineStr"/>
+      <c r="BN233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -50118,6 +50592,8 @@
       <c r="BL234" t="n">
         <v>10</v>
       </c>
+      <c r="BM234" t="inlineStr"/>
+      <c r="BN234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -50332,6 +50808,8 @@
       <c r="BL235" t="n">
         <v>20</v>
       </c>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -50546,6 +51024,8 @@
       <c r="BL236" t="n">
         <v>11</v>
       </c>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -50760,6 +51240,8 @@
       <c r="BL237" t="n">
         <v>18</v>
       </c>
+      <c r="BM237" t="inlineStr"/>
+      <c r="BN237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -50974,6 +51456,8 @@
       <c r="BL238" t="n">
         <v>14</v>
       </c>
+      <c r="BM238" t="inlineStr"/>
+      <c r="BN238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -51192,6 +51676,8 @@
       <c r="BL239" t="n">
         <v>17</v>
       </c>
+      <c r="BM239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -51406,6 +51892,8 @@
       <c r="BL240" t="n">
         <v>5</v>
       </c>
+      <c r="BM240" t="inlineStr"/>
+      <c r="BN240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -51620,6 +52108,8 @@
       <c r="BL241" t="n">
         <v>8</v>
       </c>
+      <c r="BM241" t="inlineStr"/>
+      <c r="BN241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -51838,6 +52328,8 @@
       <c r="BL242" t="n">
         <v>17</v>
       </c>
+      <c r="BM242" t="inlineStr"/>
+      <c r="BN242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -52056,6 +52548,8 @@
       <c r="BL243" t="n">
         <v>12</v>
       </c>
+      <c r="BM243" t="inlineStr"/>
+      <c r="BN243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -52270,6 +52764,8 @@
       <c r="BL244" t="n">
         <v>7</v>
       </c>
+      <c r="BM244" t="inlineStr"/>
+      <c r="BN244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -52484,6 +52980,8 @@
       <c r="BL245" t="n">
         <v>23</v>
       </c>
+      <c r="BM245" t="inlineStr"/>
+      <c r="BN245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -52690,6 +53188,8 @@
       <c r="BL246" t="n">
         <v>14</v>
       </c>
+      <c r="BM246" t="inlineStr"/>
+      <c r="BN246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -52904,6 +53404,8 @@
       <c r="BL247" t="n">
         <v>15</v>
       </c>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -53118,6 +53620,8 @@
       <c r="BL248" t="n">
         <v>10</v>
       </c>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -53332,6 +53836,8 @@
       <c r="BL249" t="n">
         <v>16</v>
       </c>
+      <c r="BM249" t="inlineStr"/>
+      <c r="BN249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -53546,6 +54052,8 @@
       <c r="BL250" t="n">
         <v>10</v>
       </c>
+      <c r="BM250" t="inlineStr"/>
+      <c r="BN250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -53760,6 +54268,8 @@
       <c r="BL251" t="n">
         <v>21</v>
       </c>
+      <c r="BM251" t="inlineStr"/>
+      <c r="BN251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -53974,6 +54484,8 @@
       <c r="BL252" t="n">
         <v>15</v>
       </c>
+      <c r="BM252" t="inlineStr"/>
+      <c r="BN252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -54192,6 +54704,8 @@
       <c r="BL253" t="n">
         <v>13</v>
       </c>
+      <c r="BM253" t="inlineStr"/>
+      <c r="BN253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -54406,6 +54920,8 @@
       <c r="BL254" t="n">
         <v>12</v>
       </c>
+      <c r="BM254" t="inlineStr"/>
+      <c r="BN254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -54620,6 +55136,8 @@
       <c r="BL255" t="n">
         <v>15</v>
       </c>
+      <c r="BM255" t="inlineStr"/>
+      <c r="BN255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -54834,6 +55352,8 @@
       <c r="BL256" t="n">
         <v>14</v>
       </c>
+      <c r="BM256" t="inlineStr"/>
+      <c r="BN256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -55048,6 +55568,8 @@
       <c r="BL257" t="n">
         <v>24</v>
       </c>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -55262,6 +55784,8 @@
       <c r="BL258" t="n">
         <v>9</v>
       </c>
+      <c r="BM258" t="inlineStr"/>
+      <c r="BN258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -55476,6 +56000,8 @@
       <c r="BL259" t="n">
         <v>9</v>
       </c>
+      <c r="BM259" t="inlineStr"/>
+      <c r="BN259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -55670,6 +56196,8 @@
       <c r="BJ260" t="inlineStr"/>
       <c r="BK260" t="inlineStr"/>
       <c r="BL260" t="inlineStr"/>
+      <c r="BM260" t="inlineStr"/>
+      <c r="BN260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -55872,6 +56400,8 @@
       <c r="BJ261" t="inlineStr"/>
       <c r="BK261" t="inlineStr"/>
       <c r="BL261" t="inlineStr"/>
+      <c r="BM261" t="inlineStr"/>
+      <c r="BN261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -56074,6 +56604,8 @@
       <c r="BJ262" t="inlineStr"/>
       <c r="BK262" t="inlineStr"/>
       <c r="BL262" t="inlineStr"/>
+      <c r="BM262" t="inlineStr"/>
+      <c r="BN262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -56276,6 +56808,8 @@
       <c r="BJ263" t="inlineStr"/>
       <c r="BK263" t="inlineStr"/>
       <c r="BL263" t="inlineStr"/>
+      <c r="BM263" t="inlineStr"/>
+      <c r="BN263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -56474,6 +57008,8 @@
       </c>
       <c r="BK264" t="inlineStr"/>
       <c r="BL264" t="inlineStr"/>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -56672,6 +57208,8 @@
       </c>
       <c r="BK265" t="inlineStr"/>
       <c r="BL265" t="inlineStr"/>
+      <c r="BM265" t="inlineStr"/>
+      <c r="BN265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -56870,6 +57408,8 @@
       </c>
       <c r="BK266" t="inlineStr"/>
       <c r="BL266" t="inlineStr"/>
+      <c r="BM266" t="inlineStr"/>
+      <c r="BN266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -57068,6 +57608,8 @@
       </c>
       <c r="BK267" t="inlineStr"/>
       <c r="BL267" t="inlineStr"/>
+      <c r="BM267" t="inlineStr"/>
+      <c r="BN267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -57266,6 +57808,8 @@
       </c>
       <c r="BK268" t="inlineStr"/>
       <c r="BL268" t="inlineStr"/>
+      <c r="BM268" t="inlineStr"/>
+      <c r="BN268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -57300,15 +57844,11 @@
           <t>21 923</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -57330,15 +57870,11 @@
           <t>AC Milan</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
+      <c r="M269" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N269" t="n">
+        <v>2.34</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -57350,135 +57886,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T269" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AN269" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="AO269" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="Q269" t="n">
+        <v>12</v>
+      </c>
+      <c r="R269" t="n">
+        <v>16</v>
+      </c>
+      <c r="S269" t="n">
+        <v>3</v>
+      </c>
+      <c r="T269" t="n">
+        <v>8</v>
+      </c>
+      <c r="U269" t="n">
+        <v>8</v>
+      </c>
+      <c r="V269" t="n">
+        <v>5</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1</v>
+      </c>
+      <c r="X269" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>328</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>477</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>236</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>379</v>
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
@@ -57516,15 +58000,11 @@
       </c>
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr"/>
-      <c r="BA269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>1</v>
       </c>
       <c r="BC269" t="inlineStr"/>
       <c r="BD269" t="inlineStr"/>
@@ -57536,6 +58016,8 @@
       <c r="BJ269" t="inlineStr"/>
       <c r="BK269" t="inlineStr"/>
       <c r="BL269" t="inlineStr"/>
+      <c r="BM269" t="inlineStr"/>
+      <c r="BN269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -57570,15 +58052,11 @@
           <t>12 021</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -57600,15 +58078,11 @@
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
+      <c r="M270" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1.16</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -57620,135 +58094,83 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AN270" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
+      <c r="Q270" t="n">
+        <v>3</v>
+      </c>
+      <c r="R270" t="n">
+        <v>15</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3</v>
+      </c>
+      <c r="T270" t="n">
+        <v>4</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" t="n">
+        <v>7</v>
+      </c>
+      <c r="W270" t="n">
+        <v>0</v>
+      </c>
+      <c r="X270" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>337</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>654</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>234</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>518</v>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
@@ -57784,15 +58206,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY270" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AZ270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AY270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>4</v>
       </c>
       <c r="BA270" t="inlineStr"/>
       <c r="BB270" t="inlineStr"/>
@@ -57806,6 +58224,8 @@
       <c r="BJ270" t="inlineStr"/>
       <c r="BK270" t="inlineStr"/>
       <c r="BL270" t="inlineStr"/>
+      <c r="BM270" t="inlineStr"/>
+      <c r="BN270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -57840,15 +58260,11 @@
           <t>28 400</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -57870,15 +58286,11 @@
           <t>Parma</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="M271" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0.55</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -57890,135 +58302,83 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="AN271" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="Q271" t="n">
+        <v>19</v>
+      </c>
+      <c r="R271" t="n">
+        <v>13</v>
+      </c>
+      <c r="S271" t="n">
+        <v>3</v>
+      </c>
+      <c r="T271" t="n">
+        <v>2</v>
+      </c>
+      <c r="U271" t="n">
+        <v>9</v>
+      </c>
+      <c r="V271" t="n">
+        <v>5</v>
+      </c>
+      <c r="W271" t="n">
+        <v>7</v>
+      </c>
+      <c r="X271" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>630</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>246</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>493</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>161</v>
       </c>
       <c r="AQ271" t="inlineStr">
         <is>
@@ -58054,25 +58414,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY271" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AZ271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BA271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY271" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>1</v>
       </c>
       <c r="BC271" t="inlineStr"/>
       <c r="BD271" t="inlineStr"/>
@@ -58084,6 +58436,8 @@
       <c r="BJ271" t="inlineStr"/>
       <c r="BK271" t="inlineStr"/>
       <c r="BL271" t="inlineStr"/>
+      <c r="BM271" t="inlineStr"/>
+      <c r="BN271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -58118,15 +58472,11 @@
           <t>38 000</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G272" t="n">
+        <v>2</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -58148,15 +58498,11 @@
           <t>Empoli</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+      <c r="M272" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0.54</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -58168,135 +58514,83 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="AN272" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
+      <c r="Q272" t="n">
+        <v>16</v>
+      </c>
+      <c r="R272" t="n">
+        <v>7</v>
+      </c>
+      <c r="S272" t="n">
+        <v>6</v>
+      </c>
+      <c r="T272" t="n">
+        <v>2</v>
+      </c>
+      <c r="U272" t="n">
+        <v>8</v>
+      </c>
+      <c r="V272" t="n">
+        <v>3</v>
+      </c>
+      <c r="W272" t="n">
+        <v>2</v>
+      </c>
+      <c r="X272" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>453</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>317</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>218</v>
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
@@ -58332,15 +58626,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY272" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AZ272" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AY272" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>6</v>
       </c>
       <c r="BA272" t="inlineStr"/>
       <c r="BB272" t="inlineStr"/>
@@ -58354,6 +58644,8 @@
       <c r="BJ272" t="inlineStr"/>
       <c r="BK272" t="inlineStr"/>
       <c r="BL272" t="inlineStr"/>
+      <c r="BM272" t="inlineStr"/>
+      <c r="BN272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -58388,15 +58680,11 @@
           <t>40 557</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -58418,15 +58706,11 @@
           <t>Cagliari</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="M273" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N273" t="n">
+        <v>1.55</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -58438,135 +58722,83 @@
           <t>26%</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R273" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="AN273" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="Q273" t="n">
+        <v>21</v>
+      </c>
+      <c r="R273" t="n">
+        <v>9</v>
+      </c>
+      <c r="S273" t="n">
+        <v>9</v>
+      </c>
+      <c r="T273" t="n">
+        <v>2</v>
+      </c>
+      <c r="U273" t="n">
+        <v>7</v>
+      </c>
+      <c r="V273" t="n">
+        <v>4</v>
+      </c>
+      <c r="W273" t="n">
+        <v>5</v>
+      </c>
+      <c r="X273" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>752</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>259</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>652</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>189</v>
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
@@ -58602,25 +58834,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AZ273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BA273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BB273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>0</v>
       </c>
       <c r="BC273" t="inlineStr"/>
       <c r="BD273" t="inlineStr"/>
@@ -58632,6 +58856,8 @@
       <c r="BJ273" t="inlineStr"/>
       <c r="BK273" t="inlineStr"/>
       <c r="BL273" t="inlineStr"/>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -58666,15 +58892,11 @@
           <t>73 348</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -58696,15 +58918,11 @@
           <t>Torino</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
+      <c r="M274" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N274" t="n">
+        <v>1.34</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -58716,135 +58934,83 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T274" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="AN274" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="Q274" t="n">
+        <v>29</v>
+      </c>
+      <c r="R274" t="n">
+        <v>7</v>
+      </c>
+      <c r="S274" t="n">
+        <v>8</v>
+      </c>
+      <c r="T274" t="n">
+        <v>5</v>
+      </c>
+      <c r="U274" t="n">
+        <v>13</v>
+      </c>
+      <c r="V274" t="n">
+        <v>1</v>
+      </c>
+      <c r="W274" t="n">
+        <v>8</v>
+      </c>
+      <c r="X274" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>740</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>192</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>688</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>127</v>
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
@@ -58882,15 +59048,11 @@
       </c>
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr"/>
-      <c r="BA274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BA274" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>1</v>
       </c>
       <c r="BC274" t="inlineStr"/>
       <c r="BD274" t="inlineStr"/>
@@ -58902,6 +59064,8 @@
       <c r="BJ274" t="inlineStr"/>
       <c r="BK274" t="inlineStr"/>
       <c r="BL274" t="inlineStr"/>
+      <c r="BM274" t="inlineStr"/>
+      <c r="BN274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -58936,15 +59100,11 @@
           <t>8 394</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G275" t="n">
+        <v>2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -58978,135 +59138,83 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AN275" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AP275" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
+      <c r="Q275" t="n">
+        <v>9</v>
+      </c>
+      <c r="R275" t="n">
+        <v>7</v>
+      </c>
+      <c r="S275" t="n">
+        <v>5</v>
+      </c>
+      <c r="T275" t="n">
+        <v>3</v>
+      </c>
+      <c r="U275" t="n">
+        <v>3</v>
+      </c>
+      <c r="V275" t="n">
+        <v>3</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1</v>
+      </c>
+      <c r="X275" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>385</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>290</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>303</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>204</v>
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
@@ -59152,18 +59260,16 @@
       <c r="BF275" t="inlineStr"/>
       <c r="BG275" t="inlineStr"/>
       <c r="BH275" t="inlineStr"/>
-      <c r="BI275" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BJ275" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="BI275" t="n">
+        <v>17</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>36</v>
       </c>
       <c r="BK275" t="inlineStr"/>
       <c r="BL275" t="inlineStr"/>
+      <c r="BM275" t="inlineStr"/>
+      <c r="BN275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -59198,15 +59304,11 @@
           <t>6 771</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>2</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -59240,135 +59342,83 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="AN276" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="AO276" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AP276" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="Q276" t="n">
+        <v>32</v>
+      </c>
+      <c r="R276" t="n">
+        <v>10</v>
+      </c>
+      <c r="S276" t="n">
+        <v>6</v>
+      </c>
+      <c r="T276" t="n">
+        <v>4</v>
+      </c>
+      <c r="U276" t="n">
+        <v>18</v>
+      </c>
+      <c r="V276" t="n">
+        <v>5</v>
+      </c>
+      <c r="W276" t="n">
+        <v>8</v>
+      </c>
+      <c r="X276" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>488</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>286</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>414</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>188</v>
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
@@ -59406,15 +59456,11 @@
       </c>
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr"/>
-      <c r="BA276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BA276" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>1</v>
       </c>
       <c r="BC276" t="inlineStr"/>
       <c r="BD276" t="inlineStr"/>
@@ -59422,18 +59468,16 @@
       <c r="BF276" t="inlineStr"/>
       <c r="BG276" t="inlineStr"/>
       <c r="BH276" t="inlineStr"/>
-      <c r="BI276" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ276" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BI276" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>24</v>
       </c>
       <c r="BK276" t="inlineStr"/>
       <c r="BL276" t="inlineStr"/>
+      <c r="BM276" t="inlineStr"/>
+      <c r="BN276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -59468,15 +59512,11 @@
           <t>9 942</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>1</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -59510,135 +59550,83 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AN277" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AO277" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AP277" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
+      <c r="Q277" t="n">
+        <v>19</v>
+      </c>
+      <c r="R277" t="n">
+        <v>14</v>
+      </c>
+      <c r="S277" t="n">
+        <v>6</v>
+      </c>
+      <c r="T277" t="n">
+        <v>4</v>
+      </c>
+      <c r="U277" t="n">
+        <v>11</v>
+      </c>
+      <c r="V277" t="n">
+        <v>7</v>
+      </c>
+      <c r="W277" t="n">
+        <v>2</v>
+      </c>
+      <c r="X277" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>445</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>338</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>375</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>264</v>
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
@@ -59684,18 +59672,16 @@
       <c r="BF277" t="inlineStr"/>
       <c r="BG277" t="inlineStr"/>
       <c r="BH277" t="inlineStr"/>
-      <c r="BI277" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ277" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="BI277" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ277" t="n">
+        <v>21</v>
       </c>
       <c r="BK277" t="inlineStr"/>
       <c r="BL277" t="inlineStr"/>
+      <c r="BM277" t="inlineStr"/>
+      <c r="BN277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -59730,15 +59716,11 @@
           <t>10 317</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -59772,135 +59754,83 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T278" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W278" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y278" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE278" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF278" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG278" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ278" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK278" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL278" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM278" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="AN278" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AO278" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="AP278" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="Q278" t="n">
+        <v>21</v>
+      </c>
+      <c r="R278" t="n">
+        <v>10</v>
+      </c>
+      <c r="S278" t="n">
+        <v>7</v>
+      </c>
+      <c r="T278" t="n">
+        <v>4</v>
+      </c>
+      <c r="U278" t="n">
+        <v>7</v>
+      </c>
+      <c r="V278" t="n">
+        <v>5</v>
+      </c>
+      <c r="W278" t="n">
+        <v>7</v>
+      </c>
+      <c r="X278" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>570</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>231</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>523</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>177</v>
       </c>
       <c r="AQ278" t="inlineStr">
         <is>
@@ -59946,18 +59876,16 @@
       <c r="BF278" t="inlineStr"/>
       <c r="BG278" t="inlineStr"/>
       <c r="BH278" t="inlineStr"/>
-      <c r="BI278" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ278" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="BI278" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>22</v>
       </c>
       <c r="BK278" t="inlineStr"/>
       <c r="BL278" t="inlineStr"/>
+      <c r="BM278" t="inlineStr"/>
+      <c r="BN278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -59992,15 +59920,11 @@
           <t>25 460</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -60034,135 +59958,83 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA279" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL279" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="AN279" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="AO279" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="AP279" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="Q279" t="n">
+        <v>16</v>
+      </c>
+      <c r="R279" t="n">
+        <v>9</v>
+      </c>
+      <c r="S279" t="n">
+        <v>5</v>
+      </c>
+      <c r="T279" t="n">
+        <v>4</v>
+      </c>
+      <c r="U279" t="n">
+        <v>5</v>
+      </c>
+      <c r="V279" t="n">
+        <v>3</v>
+      </c>
+      <c r="W279" t="n">
+        <v>6</v>
+      </c>
+      <c r="X279" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>439</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>438</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>374</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>367</v>
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
@@ -60208,18 +60080,2432 @@
       <c r="BF279" t="inlineStr"/>
       <c r="BG279" t="inlineStr"/>
       <c r="BH279" t="inlineStr"/>
-      <c r="BI279" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ279" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BI279" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ279" t="n">
+        <v>24</v>
       </c>
       <c r="BK279" t="inlineStr"/>
       <c r="BL279" t="inlineStr"/>
+      <c r="BM279" t="inlineStr"/>
+      <c r="BN279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AN280" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AT280" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AU280" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr"/>
+      <c r="BD280" t="inlineStr"/>
+      <c r="BE280" t="inlineStr"/>
+      <c r="BF280" t="inlineStr"/>
+      <c r="BG280" t="inlineStr"/>
+      <c r="BH280" t="inlineStr"/>
+      <c r="BI280" t="inlineStr"/>
+      <c r="BJ280" t="inlineStr"/>
+      <c r="BK280" t="inlineStr"/>
+      <c r="BL280" t="inlineStr"/>
+      <c r="BM280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BN280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="AN281" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AT281" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AU281" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr"/>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="inlineStr"/>
+      <c r="BI281" t="inlineStr"/>
+      <c r="BJ281" t="inlineStr"/>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="inlineStr"/>
+      <c r="BM281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BN281" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AN282" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AT282" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="AU282" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr"/>
+      <c r="BB282" t="inlineStr"/>
+      <c r="BC282" t="inlineStr"/>
+      <c r="BD282" t="inlineStr"/>
+      <c r="BE282" t="inlineStr"/>
+      <c r="BF282" t="inlineStr"/>
+      <c r="BG282" t="inlineStr"/>
+      <c r="BH282" t="inlineStr"/>
+      <c r="BI282" t="inlineStr"/>
+      <c r="BJ282" t="inlineStr"/>
+      <c r="BK282" t="inlineStr"/>
+      <c r="BL282" t="inlineStr"/>
+      <c r="BM282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BN282" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>4MfFXWSP</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>19.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AN283" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AT283" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AU283" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr"/>
+      <c r="BA283" t="inlineStr"/>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="inlineStr"/>
+      <c r="BF283" t="inlineStr"/>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="inlineStr"/>
+      <c r="BI283" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BJ283" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BK283" t="inlineStr"/>
+      <c r="BL283" t="inlineStr"/>
+      <c r="BM283" t="inlineStr"/>
+      <c r="BN283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Imw2OSkC</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Pezzuto I.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>dal canto alessandro</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AT284" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AU284" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr"/>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr"/>
+      <c r="BD284" t="inlineStr"/>
+      <c r="BE284" t="inlineStr"/>
+      <c r="BF284" t="inlineStr"/>
+      <c r="BG284" t="inlineStr"/>
+      <c r="BH284" t="inlineStr"/>
+      <c r="BI284" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BJ284" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BK284" t="inlineStr"/>
+      <c r="BL284" t="inlineStr"/>
+      <c r="BM284" t="inlineStr"/>
+      <c r="BN284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>UR6KtA5t</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AN285" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AT285" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AU285" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr"/>
+      <c r="BA285" t="inlineStr"/>
+      <c r="BB285" t="inlineStr"/>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="inlineStr"/>
+      <c r="BF285" t="inlineStr"/>
+      <c r="BG285" t="inlineStr"/>
+      <c r="BH285" t="inlineStr"/>
+      <c r="BI285" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ285" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BK285" t="inlineStr"/>
+      <c r="BL285" t="inlineStr"/>
+      <c r="BM285" t="inlineStr"/>
+      <c r="BN285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>dvbywS45</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="AN286" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AT286" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AU286" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr"/>
+      <c r="BA286" t="inlineStr"/>
+      <c r="BB286" t="inlineStr"/>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="inlineStr"/>
+      <c r="BF286" t="inlineStr"/>
+      <c r="BG286" t="inlineStr"/>
+      <c r="BH286" t="inlineStr"/>
+      <c r="BI286" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ286" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BK286" t="inlineStr"/>
+      <c r="BL286" t="inlineStr"/>
+      <c r="BM286" t="inlineStr"/>
+      <c r="BN286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>441qy6ZH</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AN287" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AT287" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AU287" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr"/>
+      <c r="BA287" t="inlineStr"/>
+      <c r="BB287" t="inlineStr"/>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="inlineStr"/>
+      <c r="BF287" t="inlineStr"/>
+      <c r="BG287" t="inlineStr"/>
+      <c r="BH287" t="inlineStr"/>
+      <c r="BI287" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BJ287" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BK287" t="inlineStr"/>
+      <c r="BL287" t="inlineStr"/>
+      <c r="BM287" t="inlineStr"/>
+      <c r="BN287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>xG2T9TzJ</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>18 615</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AN288" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AT288" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="AU288" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr"/>
+      <c r="BA288" t="inlineStr"/>
+      <c r="BB288" t="inlineStr"/>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="inlineStr"/>
+      <c r="BF288" t="inlineStr"/>
+      <c r="BG288" t="inlineStr"/>
+      <c r="BH288" t="inlineStr"/>
+      <c r="BI288" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BJ288" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK288" t="inlineStr"/>
+      <c r="BL288" t="inlineStr"/>
+      <c r="BM288" t="inlineStr"/>
+      <c r="BN288" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN288"/>
+  <dimension ref="A1:BN299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60120,15 +60120,11 @@
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -60150,15 +60146,11 @@
           <t>Udinese</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+      <c r="M280" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0.53</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -60170,135 +60162,83 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AN280" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="AO280" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="AP280" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="Q280" t="n">
+        <v>10</v>
+      </c>
+      <c r="R280" t="n">
+        <v>13</v>
+      </c>
+      <c r="S280" t="n">
+        <v>5</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1</v>
+      </c>
+      <c r="U280" t="n">
+        <v>1</v>
+      </c>
+      <c r="V280" t="n">
+        <v>11</v>
+      </c>
+      <c r="W280" t="n">
+        <v>4</v>
+      </c>
+      <c r="X280" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>335</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>411</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>367</v>
       </c>
       <c r="AQ280" t="inlineStr">
         <is>
@@ -60334,25 +60274,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AZ280" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BA280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BB280" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>0</v>
       </c>
       <c r="BC280" t="inlineStr"/>
       <c r="BD280" t="inlineStr"/>
@@ -60364,15 +60296,11 @@
       <c r="BJ280" t="inlineStr"/>
       <c r="BK280" t="inlineStr"/>
       <c r="BL280" t="inlineStr"/>
-      <c r="BM280" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BN280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BM280" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -60408,15 +60336,11 @@
           <t>7 000</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="n">
+        <v>1</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -60438,15 +60362,11 @@
           <t>Parma</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M281" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0.51</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -60458,135 +60378,83 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q281" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T281" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA281" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="AN281" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AO281" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="AP281" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
+      <c r="Q281" t="n">
+        <v>11</v>
+      </c>
+      <c r="R281" t="n">
+        <v>9</v>
+      </c>
+      <c r="S281" t="n">
+        <v>3</v>
+      </c>
+      <c r="T281" t="n">
+        <v>3</v>
+      </c>
+      <c r="U281" t="n">
+        <v>4</v>
+      </c>
+      <c r="V281" t="n">
+        <v>6</v>
+      </c>
+      <c r="W281" t="n">
+        <v>4</v>
+      </c>
+      <c r="X281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>586</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>362</v>
+      </c>
+      <c r="AO281" t="n">
+        <v>511</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>298</v>
       </c>
       <c r="AQ281" t="inlineStr">
         <is>
@@ -60622,15 +60490,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY281" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AZ281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ281" t="n">
+        <v>1</v>
       </c>
       <c r="BA281" t="inlineStr"/>
       <c r="BB281" t="inlineStr"/>
@@ -60644,15 +60508,11 @@
       <c r="BJ281" t="inlineStr"/>
       <c r="BK281" t="inlineStr"/>
       <c r="BL281" t="inlineStr"/>
-      <c r="BM281" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BN281" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BM281" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN281" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -60688,15 +60548,11 @@
           <t>30 000</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -60718,15 +60574,11 @@
           <t>Bologna</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="M282" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0.75</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -60738,135 +60590,83 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T282" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X282" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y282" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE282" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF282" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG282" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI282" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ282" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL282" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM282" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AN282" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="AO282" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="AP282" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
+      <c r="Q282" t="n">
+        <v>10</v>
+      </c>
+      <c r="R282" t="n">
+        <v>12</v>
+      </c>
+      <c r="S282" t="n">
+        <v>4</v>
+      </c>
+      <c r="T282" t="n">
+        <v>7</v>
+      </c>
+      <c r="U282" t="n">
+        <v>2</v>
+      </c>
+      <c r="V282" t="n">
+        <v>1</v>
+      </c>
+      <c r="W282" t="n">
+        <v>4</v>
+      </c>
+      <c r="X282" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI282" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>450</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>186</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>366</v>
       </c>
       <c r="AQ282" t="inlineStr">
         <is>
@@ -60902,15 +60702,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AZ282" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AY282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ282" t="n">
+        <v>4</v>
       </c>
       <c r="BA282" t="inlineStr"/>
       <c r="BB282" t="inlineStr"/>
@@ -60924,15 +60720,11 @@
       <c r="BJ282" t="inlineStr"/>
       <c r="BK282" t="inlineStr"/>
       <c r="BL282" t="inlineStr"/>
-      <c r="BM282" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BN282" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BM282" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -60964,15 +60756,11 @@
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G283" t="n">
+        <v>2</v>
+      </c>
+      <c r="H283" t="n">
+        <v>5</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -61006,135 +60794,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X283" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y283" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD283" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE283" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF283" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ283" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM283" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AN283" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="AO283" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="AP283" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
+      <c r="Q283" t="n">
+        <v>20</v>
+      </c>
+      <c r="R283" t="n">
+        <v>21</v>
+      </c>
+      <c r="S283" t="n">
+        <v>8</v>
+      </c>
+      <c r="T283" t="n">
+        <v>8</v>
+      </c>
+      <c r="U283" t="n">
+        <v>10</v>
+      </c>
+      <c r="V283" t="n">
+        <v>8</v>
+      </c>
+      <c r="W283" t="n">
+        <v>2</v>
+      </c>
+      <c r="X283" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>445</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>466</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>371</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>407</v>
       </c>
       <c r="AQ283" t="inlineStr">
         <is>
@@ -61180,15 +60916,11 @@
       <c r="BF283" t="inlineStr"/>
       <c r="BG283" t="inlineStr"/>
       <c r="BH283" t="inlineStr"/>
-      <c r="BI283" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BJ283" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="BI283" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>19</v>
       </c>
       <c r="BK283" t="inlineStr"/>
       <c r="BL283" t="inlineStr"/>
@@ -61224,15 +60956,11 @@
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -61266,135 +60994,83 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA284" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE284" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ284" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL284" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="AN284" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="AO284" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="AP284" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+      <c r="Q284" t="n">
+        <v>21</v>
+      </c>
+      <c r="R284" t="n">
+        <v>10</v>
+      </c>
+      <c r="S284" t="n">
+        <v>5</v>
+      </c>
+      <c r="T284" t="n">
+        <v>2</v>
+      </c>
+      <c r="U284" t="n">
+        <v>8</v>
+      </c>
+      <c r="V284" t="n">
+        <v>3</v>
+      </c>
+      <c r="W284" t="n">
+        <v>8</v>
+      </c>
+      <c r="X284" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>426</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>276</v>
+      </c>
+      <c r="AO284" t="n">
+        <v>358</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>202</v>
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
@@ -61432,15 +61108,11 @@
       </c>
       <c r="AY284" t="inlineStr"/>
       <c r="AZ284" t="inlineStr"/>
-      <c r="BA284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB284" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BA284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB284" t="n">
+        <v>1</v>
       </c>
       <c r="BC284" t="inlineStr"/>
       <c r="BD284" t="inlineStr"/>
@@ -61448,15 +61120,11 @@
       <c r="BF284" t="inlineStr"/>
       <c r="BG284" t="inlineStr"/>
       <c r="BH284" t="inlineStr"/>
-      <c r="BI284" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BJ284" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="BI284" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>28</v>
       </c>
       <c r="BK284" t="inlineStr"/>
       <c r="BL284" t="inlineStr"/>
@@ -61492,15 +61160,11 @@
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -61534,135 +61198,83 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R285" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T285" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y285" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD285" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE285" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF285" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AG285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI285" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ285" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM285" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AN285" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="AO285" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="AP285" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="Q285" t="n">
+        <v>16</v>
+      </c>
+      <c r="R285" t="n">
+        <v>12</v>
+      </c>
+      <c r="S285" t="n">
+        <v>4</v>
+      </c>
+      <c r="T285" t="n">
+        <v>5</v>
+      </c>
+      <c r="U285" t="n">
+        <v>8</v>
+      </c>
+      <c r="V285" t="n">
+        <v>5</v>
+      </c>
+      <c r="W285" t="n">
+        <v>4</v>
+      </c>
+      <c r="X285" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>337</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>474</v>
+      </c>
+      <c r="AO285" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>385</v>
       </c>
       <c r="AQ285" t="inlineStr">
         <is>
@@ -61708,15 +61320,11 @@
       <c r="BF285" t="inlineStr"/>
       <c r="BG285" t="inlineStr"/>
       <c r="BH285" t="inlineStr"/>
-      <c r="BI285" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ285" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BI285" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>24</v>
       </c>
       <c r="BK285" t="inlineStr"/>
       <c r="BL285" t="inlineStr"/>
@@ -61752,15 +61360,11 @@
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -61794,135 +61398,83 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R286" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T286" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y286" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE286" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ286" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK286" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM286" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="AN286" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AO286" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="AP286" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
+      <c r="Q286" t="n">
+        <v>18</v>
+      </c>
+      <c r="R286" t="n">
+        <v>14</v>
+      </c>
+      <c r="S286" t="n">
+        <v>5</v>
+      </c>
+      <c r="T286" t="n">
+        <v>4</v>
+      </c>
+      <c r="U286" t="n">
+        <v>8</v>
+      </c>
+      <c r="V286" t="n">
+        <v>7</v>
+      </c>
+      <c r="W286" t="n">
+        <v>5</v>
+      </c>
+      <c r="X286" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>517</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>448</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>242</v>
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
@@ -61968,15 +61520,11 @@
       <c r="BF286" t="inlineStr"/>
       <c r="BG286" t="inlineStr"/>
       <c r="BH286" t="inlineStr"/>
-      <c r="BI286" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ286" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="BI286" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>26</v>
       </c>
       <c r="BK286" t="inlineStr"/>
       <c r="BL286" t="inlineStr"/>
@@ -62012,15 +61560,11 @@
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -62054,135 +61598,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R287" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X287" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y287" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC287" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE287" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF287" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG287" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI287" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ287" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM287" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AN287" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AO287" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="AP287" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
+      <c r="Q287" t="n">
+        <v>7</v>
+      </c>
+      <c r="R287" t="n">
+        <v>11</v>
+      </c>
+      <c r="S287" t="n">
+        <v>3</v>
+      </c>
+      <c r="T287" t="n">
+        <v>2</v>
+      </c>
+      <c r="U287" t="n">
+        <v>3</v>
+      </c>
+      <c r="V287" t="n">
+        <v>3</v>
+      </c>
+      <c r="W287" t="n">
+        <v>1</v>
+      </c>
+      <c r="X287" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>337</v>
+      </c>
+      <c r="AO287" t="n">
+        <v>321</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>246</v>
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
@@ -62228,15 +61720,11 @@
       <c r="BF287" t="inlineStr"/>
       <c r="BG287" t="inlineStr"/>
       <c r="BH287" t="inlineStr"/>
-      <c r="BI287" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BJ287" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="BI287" t="n">
+        <v>29</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>25</v>
       </c>
       <c r="BK287" t="inlineStr"/>
       <c r="BL287" t="inlineStr"/>
@@ -62276,15 +61764,11 @@
           <t>18 615</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -62318,135 +61802,83 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T288" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y288" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE288" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AF288" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG288" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI288" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ288" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM288" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="AN288" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="AO288" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="AP288" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
+      <c r="Q288" t="n">
+        <v>16</v>
+      </c>
+      <c r="R288" t="n">
+        <v>18</v>
+      </c>
+      <c r="S288" t="n">
+        <v>5</v>
+      </c>
+      <c r="T288" t="n">
+        <v>7</v>
+      </c>
+      <c r="U288" t="n">
+        <v>6</v>
+      </c>
+      <c r="V288" t="n">
+        <v>8</v>
+      </c>
+      <c r="W288" t="n">
+        <v>5</v>
+      </c>
+      <c r="X288" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>368</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>486</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>306</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>435</v>
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
@@ -62492,21 +61924,2381 @@
       <c r="BF288" t="inlineStr"/>
       <c r="BG288" t="inlineStr"/>
       <c r="BH288" t="inlineStr"/>
-      <c r="BI288" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BJ288" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BI288" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>8</v>
       </c>
       <c r="BK288" t="inlineStr"/>
       <c r="BL288" t="inlineStr"/>
       <c r="BM288" t="inlineStr"/>
       <c r="BN288" t="inlineStr"/>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>20.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>14</v>
+      </c>
+      <c r="R289" t="n">
+        <v>11</v>
+      </c>
+      <c r="S289" t="n">
+        <v>3</v>
+      </c>
+      <c r="T289" t="n">
+        <v>6</v>
+      </c>
+      <c r="U289" t="n">
+        <v>5</v>
+      </c>
+      <c r="V289" t="n">
+        <v>4</v>
+      </c>
+      <c r="W289" t="n">
+        <v>6</v>
+      </c>
+      <c r="X289" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>487</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>400</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>420</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>336</v>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AT289" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AU289" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY289" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA289" t="inlineStr"/>
+      <c r="BB289" t="inlineStr"/>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr"/>
+      <c r="BH289" t="inlineStr"/>
+      <c r="BI289" t="inlineStr"/>
+      <c r="BJ289" t="inlineStr"/>
+      <c r="BK289" t="inlineStr"/>
+      <c r="BL289" t="inlineStr"/>
+      <c r="BM289" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>20.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>16 000</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>18</v>
+      </c>
+      <c r="R290" t="n">
+        <v>17</v>
+      </c>
+      <c r="S290" t="n">
+        <v>5</v>
+      </c>
+      <c r="T290" t="n">
+        <v>5</v>
+      </c>
+      <c r="U290" t="n">
+        <v>7</v>
+      </c>
+      <c r="V290" t="n">
+        <v>8</v>
+      </c>
+      <c r="W290" t="n">
+        <v>6</v>
+      </c>
+      <c r="X290" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>335</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>471</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>286</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>415</v>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AT290" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AU290" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY290" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA290" t="inlineStr"/>
+      <c r="BB290" t="inlineStr"/>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr"/>
+      <c r="BH290" t="inlineStr"/>
+      <c r="BI290" t="inlineStr"/>
+      <c r="BJ290" t="inlineStr"/>
+      <c r="BK290" t="inlineStr"/>
+      <c r="BL290" t="inlineStr"/>
+      <c r="BM290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>AJ5eIkmR</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>25 124</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>6</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N291" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>5</v>
+      </c>
+      <c r="R291" t="n">
+        <v>19</v>
+      </c>
+      <c r="S291" t="n">
+        <v>2</v>
+      </c>
+      <c r="T291" t="n">
+        <v>11</v>
+      </c>
+      <c r="U291" t="n">
+        <v>2</v>
+      </c>
+      <c r="V291" t="n">
+        <v>4</v>
+      </c>
+      <c r="W291" t="n">
+        <v>1</v>
+      </c>
+      <c r="X291" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>353</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>567</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>279</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>511</v>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AT291" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AU291" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ291" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA291" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB291" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC291" t="inlineStr"/>
+      <c r="BD291" t="inlineStr"/>
+      <c r="BE291" t="inlineStr"/>
+      <c r="BF291" t="inlineStr"/>
+      <c r="BG291" t="inlineStr"/>
+      <c r="BH291" t="inlineStr"/>
+      <c r="BI291" t="inlineStr"/>
+      <c r="BJ291" t="inlineStr"/>
+      <c r="BK291" t="inlineStr"/>
+      <c r="BL291" t="inlineStr"/>
+      <c r="BM291" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>dGwq9oAD</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>11 979</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N292" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>12</v>
+      </c>
+      <c r="R292" t="n">
+        <v>16</v>
+      </c>
+      <c r="S292" t="n">
+        <v>4</v>
+      </c>
+      <c r="T292" t="n">
+        <v>7</v>
+      </c>
+      <c r="U292" t="n">
+        <v>7</v>
+      </c>
+      <c r="V292" t="n">
+        <v>8</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1</v>
+      </c>
+      <c r="X292" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>503</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>292</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>413</v>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AT292" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AU292" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ292" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA292" t="inlineStr"/>
+      <c r="BB292" t="inlineStr"/>
+      <c r="BC292" t="inlineStr"/>
+      <c r="BD292" t="inlineStr"/>
+      <c r="BE292" t="inlineStr"/>
+      <c r="BF292" t="inlineStr"/>
+      <c r="BG292" t="inlineStr"/>
+      <c r="BH292" t="inlineStr"/>
+      <c r="BI292" t="inlineStr"/>
+      <c r="BJ292" t="inlineStr"/>
+      <c r="BK292" t="inlineStr"/>
+      <c r="BL292" t="inlineStr"/>
+      <c r="BM292" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>8Kjh0jRr</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>20.10.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>11</v>
+      </c>
+      <c r="R293" t="n">
+        <v>9</v>
+      </c>
+      <c r="S293" t="n">
+        <v>4</v>
+      </c>
+      <c r="T293" t="n">
+        <v>1</v>
+      </c>
+      <c r="U293" t="n">
+        <v>2</v>
+      </c>
+      <c r="V293" t="n">
+        <v>4</v>
+      </c>
+      <c r="W293" t="n">
+        <v>5</v>
+      </c>
+      <c r="X293" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>393</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>400</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>329</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>338</v>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AT293" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AU293" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ293" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA293" t="inlineStr"/>
+      <c r="BB293" t="inlineStr"/>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
+      <c r="BI293" t="inlineStr"/>
+      <c r="BJ293" t="inlineStr"/>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="inlineStr"/>
+      <c r="BM293" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN293" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2g2mKBIE</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>19.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>40 800</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>16</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2</v>
+      </c>
+      <c r="S294" t="n">
+        <v>3</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1</v>
+      </c>
+      <c r="U294" t="n">
+        <v>10</v>
+      </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="n">
+        <v>3</v>
+      </c>
+      <c r="X294" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>604</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>268</v>
+      </c>
+      <c r="AO294" t="n">
+        <v>545</v>
+      </c>
+      <c r="AP294" t="n">
+        <v>209</v>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AT294" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AU294" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ294" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA294" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB294" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
+      <c r="BI294" t="inlineStr"/>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+      <c r="BM294" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN294" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>MLqgQlLa</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>23 860</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" t="n">
+        <v>5</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>10</v>
+      </c>
+      <c r="R295" t="n">
+        <v>14</v>
+      </c>
+      <c r="S295" t="n">
+        <v>5</v>
+      </c>
+      <c r="T295" t="n">
+        <v>6</v>
+      </c>
+      <c r="U295" t="n">
+        <v>2</v>
+      </c>
+      <c r="V295" t="n">
+        <v>6</v>
+      </c>
+      <c r="W295" t="n">
+        <v>3</v>
+      </c>
+      <c r="X295" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>448</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>407</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>388</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>341</v>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AT295" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AU295" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr"/>
+      <c r="BA295" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB295" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="inlineStr"/>
+      <c r="BF295" t="inlineStr"/>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
+      <c r="BI295" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ295" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="inlineStr"/>
+      <c r="BM295" t="inlineStr"/>
+      <c r="BN295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>lfWoSAjm</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Monaldi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>16</v>
+      </c>
+      <c r="R296" t="n">
+        <v>9</v>
+      </c>
+      <c r="S296" t="n">
+        <v>5</v>
+      </c>
+      <c r="T296" t="n">
+        <v>2</v>
+      </c>
+      <c r="U296" t="n">
+        <v>5</v>
+      </c>
+      <c r="V296" t="n">
+        <v>3</v>
+      </c>
+      <c r="W296" t="n">
+        <v>6</v>
+      </c>
+      <c r="X296" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>266</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>513</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>433</v>
+      </c>
+      <c r="AQ296" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AT296" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="AU296" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr"/>
+      <c r="BA296" t="inlineStr"/>
+      <c r="BB296" t="inlineStr"/>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="inlineStr"/>
+      <c r="BF296" t="inlineStr"/>
+      <c r="BG296" t="inlineStr"/>
+      <c r="BH296" t="inlineStr"/>
+      <c r="BI296" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK296" t="inlineStr"/>
+      <c r="BL296" t="inlineStr"/>
+      <c r="BM296" t="inlineStr"/>
+      <c r="BN296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>j1yAM6KO</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Caputi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Stadio Romeo Menti
+ (Castellammare di Stabia)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>13 000</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="n">
+        <v>1</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>15</v>
+      </c>
+      <c r="R297" t="n">
+        <v>16</v>
+      </c>
+      <c r="S297" t="n">
+        <v>4</v>
+      </c>
+      <c r="T297" t="n">
+        <v>6</v>
+      </c>
+      <c r="U297" t="n">
+        <v>6</v>
+      </c>
+      <c r="V297" t="n">
+        <v>4</v>
+      </c>
+      <c r="W297" t="n">
+        <v>5</v>
+      </c>
+      <c r="X297" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI297" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>398</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>343</v>
+      </c>
+      <c r="AO297" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>264</v>
+      </c>
+      <c r="AQ297" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>AgMBZSTl</t>
+        </is>
+      </c>
+      <c r="AT297" t="inlineStr">
+        <is>
+          <t>corini eugenio</t>
+        </is>
+      </c>
+      <c r="AU297" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV297" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr"/>
+      <c r="BA297" t="inlineStr"/>
+      <c r="BB297" t="inlineStr"/>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="inlineStr"/>
+      <c r="BF297" t="inlineStr"/>
+      <c r="BG297" t="inlineStr"/>
+      <c r="BH297" t="inlineStr"/>
+      <c r="BI297" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ297" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK297" t="inlineStr"/>
+      <c r="BL297" t="inlineStr"/>
+      <c r="BM297" t="inlineStr"/>
+      <c r="BN297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>zP9Svlzg</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>8 459</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>8</v>
+      </c>
+      <c r="R298" t="n">
+        <v>13</v>
+      </c>
+      <c r="S298" t="n">
+        <v>6</v>
+      </c>
+      <c r="T298" t="n">
+        <v>3</v>
+      </c>
+      <c r="U298" t="n">
+        <v>2</v>
+      </c>
+      <c r="V298" t="n">
+        <v>7</v>
+      </c>
+      <c r="W298" t="n">
+        <v>0</v>
+      </c>
+      <c r="X298" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>432</v>
+      </c>
+      <c r="AO298" t="n">
+        <v>274</v>
+      </c>
+      <c r="AP298" t="n">
+        <v>348</v>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AT298" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="AU298" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr"/>
+      <c r="BA298" t="inlineStr"/>
+      <c r="BB298" t="inlineStr"/>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="inlineStr"/>
+      <c r="BF298" t="inlineStr"/>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
+      <c r="BI298" t="n">
+        <v>31</v>
+      </c>
+      <c r="BJ298" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="inlineStr"/>
+      <c r="BM298" t="inlineStr"/>
+      <c r="BN298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>McP0d8Q7</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>21.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM299" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AN299" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AQ299" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AT299" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AU299" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV299" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA299" t="inlineStr"/>
+      <c r="BB299" t="inlineStr"/>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
+      <c r="BI299" t="inlineStr"/>
+      <c r="BJ299" t="inlineStr"/>
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="inlineStr"/>
+      <c r="BM299" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BN299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN299"/>
+  <dimension ref="A1:BN318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64052,15 +64052,11 @@
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>3</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -64082,15 +64078,11 @@
           <t>Monza</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
+      <c r="M299" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N299" t="n">
+        <v>1.51</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -64102,135 +64094,83 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T299" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA299" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE299" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM299" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AN299" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="AO299" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="AP299" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
+      <c r="Q299" t="n">
+        <v>16</v>
+      </c>
+      <c r="R299" t="n">
+        <v>10</v>
+      </c>
+      <c r="S299" t="n">
+        <v>4</v>
+      </c>
+      <c r="T299" t="n">
+        <v>4</v>
+      </c>
+      <c r="U299" t="n">
+        <v>8</v>
+      </c>
+      <c r="V299" t="n">
+        <v>3</v>
+      </c>
+      <c r="W299" t="n">
+        <v>4</v>
+      </c>
+      <c r="X299" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH299" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK299" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>480</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>347</v>
+      </c>
+      <c r="AO299" t="n">
+        <v>400</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>280</v>
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
@@ -64266,15 +64206,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY299" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AZ299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY299" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ299" t="n">
+        <v>2</v>
       </c>
       <c r="BA299" t="inlineStr"/>
       <c r="BB299" t="inlineStr"/>
@@ -64288,16 +64224,4476 @@
       <c r="BJ299" t="inlineStr"/>
       <c r="BK299" t="inlineStr"/>
       <c r="BL299" t="inlineStr"/>
-      <c r="BM299" t="inlineStr">
+      <c r="BM299" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN299" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>26.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>23 015</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>6</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>19</v>
+      </c>
+      <c r="R300" t="n">
+        <v>4</v>
+      </c>
+      <c r="S300" t="n">
+        <v>10</v>
+      </c>
+      <c r="T300" t="n">
+        <v>2</v>
+      </c>
+      <c r="U300" t="n">
+        <v>6</v>
+      </c>
+      <c r="V300" t="n">
+        <v>2</v>
+      </c>
+      <c r="W300" t="n">
+        <v>3</v>
+      </c>
+      <c r="X300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>785</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>349</v>
+      </c>
+      <c r="AO300" t="n">
+        <v>714</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>270</v>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AT300" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="AU300" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX300" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ300" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA300" t="inlineStr"/>
+      <c r="BB300" t="inlineStr"/>
+      <c r="BC300" t="inlineStr"/>
+      <c r="BD300" t="inlineStr"/>
+      <c r="BE300" t="inlineStr"/>
+      <c r="BF300" t="inlineStr"/>
+      <c r="BG300" t="inlineStr"/>
+      <c r="BH300" t="inlineStr"/>
+      <c r="BI300" t="inlineStr"/>
+      <c r="BJ300" t="inlineStr"/>
+      <c r="BK300" t="inlineStr"/>
+      <c r="BL300" t="inlineStr"/>
+      <c r="BM300" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN300" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>51 103</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>24</v>
+      </c>
+      <c r="R301" t="n">
+        <v>11</v>
+      </c>
+      <c r="S301" t="n">
+        <v>8</v>
+      </c>
+      <c r="T301" t="n">
+        <v>2</v>
+      </c>
+      <c r="U301" t="n">
+        <v>7</v>
+      </c>
+      <c r="V301" t="n">
+        <v>4</v>
+      </c>
+      <c r="W301" t="n">
+        <v>9</v>
+      </c>
+      <c r="X301" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>493</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>272</v>
+      </c>
+      <c r="AO301" t="n">
+        <v>423</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>198</v>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AR301" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AT301" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AU301" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY301" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ301" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA301" t="inlineStr"/>
+      <c r="BB301" t="inlineStr"/>
+      <c r="BC301" t="inlineStr"/>
+      <c r="BD301" t="inlineStr"/>
+      <c r="BE301" t="inlineStr"/>
+      <c r="BF301" t="inlineStr"/>
+      <c r="BG301" t="inlineStr"/>
+      <c r="BH301" t="inlineStr"/>
+      <c r="BI301" t="inlineStr"/>
+      <c r="BJ301" t="inlineStr"/>
+      <c r="BK301" t="inlineStr"/>
+      <c r="BL301" t="inlineStr"/>
+      <c r="BM301" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN301" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>23 571</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>8</v>
+      </c>
+      <c r="R302" t="n">
+        <v>20</v>
+      </c>
+      <c r="S302" t="n">
+        <v>2</v>
+      </c>
+      <c r="T302" t="n">
+        <v>6</v>
+      </c>
+      <c r="U302" t="n">
+        <v>3</v>
+      </c>
+      <c r="V302" t="n">
+        <v>6</v>
+      </c>
+      <c r="W302" t="n">
+        <v>3</v>
+      </c>
+      <c r="X302" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>628</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>211</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>552</v>
+      </c>
+      <c r="AQ302" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AT302" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AU302" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX302" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY302" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ302" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA302" t="inlineStr"/>
+      <c r="BB302" t="inlineStr"/>
+      <c r="BC302" t="inlineStr"/>
+      <c r="BD302" t="inlineStr"/>
+      <c r="BE302" t="inlineStr"/>
+      <c r="BF302" t="inlineStr"/>
+      <c r="BG302" t="inlineStr"/>
+      <c r="BH302" t="inlineStr"/>
+      <c r="BI302" t="inlineStr"/>
+      <c r="BJ302" t="inlineStr"/>
+      <c r="BK302" t="inlineStr"/>
+      <c r="BL302" t="inlineStr"/>
+      <c r="BM302" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN302" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>I5fXHFho</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>25.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>21 095</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>13</v>
+      </c>
+      <c r="R303" t="n">
+        <v>3</v>
+      </c>
+      <c r="S303" t="n">
+        <v>4</v>
+      </c>
+      <c r="T303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="n">
+        <v>7</v>
+      </c>
+      <c r="V303" t="n">
+        <v>3</v>
+      </c>
+      <c r="W303" t="n">
+        <v>2</v>
+      </c>
+      <c r="X303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>532</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>293</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>484</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>234</v>
+      </c>
+      <c r="AQ303" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AT303" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AU303" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX303" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC303" t="inlineStr"/>
+      <c r="BD303" t="inlineStr"/>
+      <c r="BE303" t="inlineStr"/>
+      <c r="BF303" t="inlineStr"/>
+      <c r="BG303" t="inlineStr"/>
+      <c r="BH303" t="inlineStr"/>
+      <c r="BI303" t="inlineStr"/>
+      <c r="BJ303" t="inlineStr"/>
+      <c r="BK303" t="inlineStr"/>
+      <c r="BL303" t="inlineStr"/>
+      <c r="BM303" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>0WfhZq4U</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>26.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Rutella D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Stadio dei Marmi
+ (Carrara)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>5 280</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="n">
+        <v>3</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>9</v>
+      </c>
+      <c r="R304" t="n">
+        <v>20</v>
+      </c>
+      <c r="S304" t="n">
+        <v>4</v>
+      </c>
+      <c r="T304" t="n">
+        <v>2</v>
+      </c>
+      <c r="U304" t="n">
+        <v>3</v>
+      </c>
+      <c r="V304" t="n">
+        <v>10</v>
+      </c>
+      <c r="W304" t="n">
+        <v>2</v>
+      </c>
+      <c r="X304" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>561</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>361</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>464</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>286</v>
+      </c>
+      <c r="AQ304" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AR304" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AT304" t="inlineStr">
+        <is>
+          <t>dal canto alessandro</t>
+        </is>
+      </c>
+      <c r="AU304" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX304" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr"/>
+      <c r="BA304" t="inlineStr"/>
+      <c r="BB304" t="inlineStr"/>
+      <c r="BC304" t="inlineStr"/>
+      <c r="BD304" t="inlineStr"/>
+      <c r="BE304" t="inlineStr"/>
+      <c r="BF304" t="inlineStr"/>
+      <c r="BG304" t="inlineStr"/>
+      <c r="BH304" t="inlineStr"/>
+      <c r="BI304" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK304" t="inlineStr"/>
+      <c r="BL304" t="inlineStr"/>
+      <c r="BM304" t="inlineStr"/>
+      <c r="BN304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>4vIh2rYG</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>26.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="n">
+        <v>2</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>12</v>
+      </c>
+      <c r="R305" t="n">
+        <v>14</v>
+      </c>
+      <c r="S305" t="n">
+        <v>5</v>
+      </c>
+      <c r="T305" t="n">
+        <v>5</v>
+      </c>
+      <c r="U305" t="n">
+        <v>3</v>
+      </c>
+      <c r="V305" t="n">
+        <v>5</v>
+      </c>
+      <c r="W305" t="n">
+        <v>4</v>
+      </c>
+      <c r="X305" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>489</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>456</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>431</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>381</v>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AR305" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AT305" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AU305" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX305" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr"/>
+      <c r="BA305" t="inlineStr"/>
+      <c r="BB305" t="inlineStr"/>
+      <c r="BC305" t="inlineStr"/>
+      <c r="BD305" t="inlineStr"/>
+      <c r="BE305" t="inlineStr"/>
+      <c r="BF305" t="inlineStr"/>
+      <c r="BG305" t="inlineStr"/>
+      <c r="BH305" t="inlineStr"/>
+      <c r="BI305" t="n">
+        <v>20</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>28</v>
+      </c>
+      <c r="BK305" t="inlineStr"/>
+      <c r="BL305" t="inlineStr"/>
+      <c r="BM305" t="inlineStr"/>
+      <c r="BN305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>zoo3iRJb</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>23 860</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>15</v>
+      </c>
+      <c r="R306" t="n">
+        <v>17</v>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="n">
+        <v>2</v>
+      </c>
+      <c r="U306" t="n">
+        <v>6</v>
+      </c>
+      <c r="V306" t="n">
+        <v>11</v>
+      </c>
+      <c r="W306" t="n">
+        <v>4</v>
+      </c>
+      <c r="X306" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>334</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>424</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>267</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>355</v>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AR306" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AT306" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AU306" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX306" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr"/>
+      <c r="BA306" t="inlineStr"/>
+      <c r="BB306" t="inlineStr"/>
+      <c r="BC306" t="inlineStr"/>
+      <c r="BD306" t="inlineStr"/>
+      <c r="BE306" t="inlineStr"/>
+      <c r="BF306" t="inlineStr"/>
+      <c r="BG306" t="inlineStr"/>
+      <c r="BH306" t="inlineStr"/>
+      <c r="BI306" t="n">
+        <v>27</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK306" t="inlineStr"/>
+      <c r="BL306" t="inlineStr"/>
+      <c r="BM306" t="inlineStr"/>
+      <c r="BN306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>rBlBk5lB</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Galipo S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>13</v>
+      </c>
+      <c r="R307" t="n">
+        <v>10</v>
+      </c>
+      <c r="S307" t="n">
+        <v>5</v>
+      </c>
+      <c r="T307" t="n">
+        <v>3</v>
+      </c>
+      <c r="U307" t="n">
+        <v>6</v>
+      </c>
+      <c r="V307" t="n">
+        <v>5</v>
+      </c>
+      <c r="W307" t="n">
+        <v>2</v>
+      </c>
+      <c r="X307" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>283</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>166</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>197</v>
+      </c>
+      <c r="AQ307" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AR307" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AT307" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="AU307" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX307" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr"/>
+      <c r="BA307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC307" t="inlineStr"/>
+      <c r="BD307" t="inlineStr"/>
+      <c r="BE307" t="inlineStr"/>
+      <c r="BF307" t="inlineStr"/>
+      <c r="BG307" t="inlineStr"/>
+      <c r="BH307" t="inlineStr"/>
+      <c r="BI307" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>38</v>
+      </c>
+      <c r="BK307" t="inlineStr"/>
+      <c r="BL307" t="inlineStr"/>
+      <c r="BM307" t="inlineStr"/>
+      <c r="BN307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>4QxKmqJN</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="n">
+        <v>2</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>9</v>
+      </c>
+      <c r="R308" t="n">
+        <v>6</v>
+      </c>
+      <c r="S308" t="n">
+        <v>3</v>
+      </c>
+      <c r="T308" t="n">
+        <v>3</v>
+      </c>
+      <c r="U308" t="n">
+        <v>3</v>
+      </c>
+      <c r="V308" t="n">
+        <v>1</v>
+      </c>
+      <c r="W308" t="n">
+        <v>3</v>
+      </c>
+      <c r="X308" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>428</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>568</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>356</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>475</v>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>AgMBZSTl</t>
+        </is>
+      </c>
+      <c r="AR308" t="inlineStr">
+        <is>
+          <t>corini eugenio</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AT308" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AU308" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr"/>
+      <c r="BA308" t="inlineStr"/>
+      <c r="BB308" t="inlineStr"/>
+      <c r="BC308" t="inlineStr"/>
+      <c r="BD308" t="inlineStr"/>
+      <c r="BE308" t="inlineStr"/>
+      <c r="BF308" t="inlineStr"/>
+      <c r="BG308" t="inlineStr"/>
+      <c r="BH308" t="inlineStr"/>
+      <c r="BI308" t="n">
+        <v>24</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK308" t="inlineStr"/>
+      <c r="BL308" t="inlineStr"/>
+      <c r="BM308" t="inlineStr"/>
+      <c r="BN308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>zaQy6QYi</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Massimi L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Stadio Renzo Barbera
+ (Palermo)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>36 349</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>19</v>
+      </c>
+      <c r="R309" t="n">
+        <v>6</v>
+      </c>
+      <c r="S309" t="n">
+        <v>4</v>
+      </c>
+      <c r="T309" t="n">
+        <v>3</v>
+      </c>
+      <c r="U309" t="n">
+        <v>8</v>
+      </c>
+      <c r="V309" t="n">
+        <v>2</v>
+      </c>
+      <c r="W309" t="n">
+        <v>7</v>
+      </c>
+      <c r="X309" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>426</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>397</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>363</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>317</v>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AR309" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AT309" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AU309" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX309" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr"/>
+      <c r="BA309" t="inlineStr"/>
+      <c r="BB309" t="inlineStr"/>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="inlineStr"/>
+      <c r="BF309" t="inlineStr"/>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
+      <c r="BI309" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ309" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK309" t="inlineStr"/>
+      <c r="BL309" t="inlineStr"/>
+      <c r="BM309" t="inlineStr"/>
+      <c r="BN309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>AwpQqzIk</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Arena A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Picco
+ (La Spezia)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>11 466</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>7 460</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>16</v>
+      </c>
+      <c r="R310" t="n">
+        <v>4</v>
+      </c>
+      <c r="S310" t="n">
+        <v>5</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0</v>
+      </c>
+      <c r="U310" t="n">
+        <v>7</v>
+      </c>
+      <c r="V310" t="n">
+        <v>4</v>
+      </c>
+      <c r="W310" t="n">
+        <v>4</v>
+      </c>
+      <c r="X310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>306</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>353</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>219</v>
+      </c>
+      <c r="AQ310" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AR310" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AT310" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AU310" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX310" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr"/>
+      <c r="BA310" t="inlineStr"/>
+      <c r="BB310" t="inlineStr"/>
+      <c r="BC310" t="inlineStr"/>
+      <c r="BD310" t="inlineStr"/>
+      <c r="BE310" t="inlineStr"/>
+      <c r="BF310" t="inlineStr"/>
+      <c r="BG310" t="inlineStr"/>
+      <c r="BH310" t="inlineStr"/>
+      <c r="BI310" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ310" t="n">
+        <v>34</v>
+      </c>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="inlineStr"/>
+      <c r="BM310" t="inlineStr"/>
+      <c r="BN310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>27.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>20 440</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BN299" t="inlineStr">
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="AN311" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AQ311" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AR311" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AT311" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="AU311" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX311" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY311" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA311" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC311" t="inlineStr"/>
+      <c r="BD311" t="inlineStr"/>
+      <c r="BE311" t="inlineStr"/>
+      <c r="BF311" t="inlineStr"/>
+      <c r="BG311" t="inlineStr"/>
+      <c r="BH311" t="inlineStr"/>
+      <c r="BI311" t="inlineStr"/>
+      <c r="BJ311" t="inlineStr"/>
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="inlineStr"/>
+      <c r="BM311" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BN311" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>27.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
+      <c r="AF312" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM312" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN312" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AR312" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AT312" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="AU312" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX312" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA312" t="inlineStr"/>
+      <c r="BB312" t="inlineStr"/>
+      <c r="BC312" t="inlineStr"/>
+      <c r="BD312" t="inlineStr"/>
+      <c r="BE312" t="inlineStr"/>
+      <c r="BF312" t="inlineStr"/>
+      <c r="BG312" t="inlineStr"/>
+      <c r="BH312" t="inlineStr"/>
+      <c r="BI312" t="inlineStr"/>
+      <c r="BJ312" t="inlineStr"/>
+      <c r="BK312" t="inlineStr"/>
+      <c r="BL312" t="inlineStr"/>
+      <c r="BM312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BN312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="AN313" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AT313" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AU313" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr"/>
+      <c r="BB313" t="inlineStr"/>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr"/>
+      <c r="BE313" t="inlineStr"/>
+      <c r="BF313" t="inlineStr"/>
+      <c r="BG313" t="inlineStr"/>
+      <c r="BH313" t="inlineStr"/>
+      <c r="BI313" t="inlineStr"/>
+      <c r="BJ313" t="inlineStr"/>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="inlineStr"/>
+      <c r="BM313" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BN313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>10 141</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AN314" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AT314" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="AU314" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX314" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY314" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BA314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr"/>
+      <c r="BE314" t="inlineStr"/>
+      <c r="BF314" t="inlineStr"/>
+      <c r="BG314" t="inlineStr"/>
+      <c r="BH314" t="inlineStr"/>
+      <c r="BI314" t="inlineStr"/>
+      <c r="BJ314" t="inlineStr"/>
+      <c r="BK314" t="inlineStr"/>
+      <c r="BL314" t="inlineStr"/>
+      <c r="BM314" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BN314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>27.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>17 802</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="AN315" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AU315" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr"/>
+      <c r="BB315" t="inlineStr"/>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr"/>
+      <c r="BE315" t="inlineStr"/>
+      <c r="BF315" t="inlineStr"/>
+      <c r="BG315" t="inlineStr"/>
+      <c r="BH315" t="inlineStr"/>
+      <c r="BI315" t="inlineStr"/>
+      <c r="BJ315" t="inlineStr"/>
+      <c r="BK315" t="inlineStr"/>
+      <c r="BL315" t="inlineStr"/>
+      <c r="BM315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BN315" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>GrV1gmkn</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Santoro A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AN316" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AU316" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV316" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr"/>
+      <c r="BA316" t="inlineStr"/>
+      <c r="BB316" t="inlineStr"/>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr"/>
+      <c r="BE316" t="inlineStr"/>
+      <c r="BF316" t="inlineStr"/>
+      <c r="BG316" t="inlineStr"/>
+      <c r="BH316" t="inlineStr"/>
+      <c r="BI316" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ316" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="inlineStr"/>
+      <c r="BM316" t="inlineStr"/>
+      <c r="BN316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>z9TkrNto</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="AN317" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AU317" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV317" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr"/>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr"/>
+      <c r="BE317" t="inlineStr"/>
+      <c r="BF317" t="inlineStr"/>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
+      <c r="BI317" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BJ317" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="inlineStr"/>
+      <c r="BM317" t="inlineStr"/>
+      <c r="BN317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>8COq4434</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="AN318" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AT318" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="AU318" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV318" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr"/>
+      <c r="BA318" t="inlineStr"/>
+      <c r="BB318" t="inlineStr"/>
+      <c r="BC318" t="inlineStr"/>
+      <c r="BD318" t="inlineStr"/>
+      <c r="BE318" t="inlineStr"/>
+      <c r="BF318" t="inlineStr"/>
+      <c r="BG318" t="inlineStr"/>
+      <c r="BH318" t="inlineStr"/>
+      <c r="BI318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BJ318" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK318" t="inlineStr"/>
+      <c r="BL318" t="inlineStr"/>
+      <c r="BM318" t="inlineStr"/>
+      <c r="BN318" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN318"/>
+  <dimension ref="A1:BN338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66524,15 +66524,11 @@
           <t>20 440</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G311" t="n">
+        <v>5</v>
+      </c>
+      <c r="H311" t="n">
+        <v>1</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -66554,15 +66550,11 @@
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="M311" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0.65</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -66574,135 +66566,83 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q311" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R311" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA311" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM311" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="AN311" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="AO311" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="AP311" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
+      <c r="Q311" t="n">
+        <v>21</v>
+      </c>
+      <c r="R311" t="n">
+        <v>14</v>
+      </c>
+      <c r="S311" t="n">
+        <v>10</v>
+      </c>
+      <c r="T311" t="n">
+        <v>5</v>
+      </c>
+      <c r="U311" t="n">
+        <v>8</v>
+      </c>
+      <c r="V311" t="n">
+        <v>1</v>
+      </c>
+      <c r="W311" t="n">
+        <v>3</v>
+      </c>
+      <c r="X311" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>343</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>547</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>304</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>503</v>
       </c>
       <c r="AQ311" t="inlineStr">
         <is>
@@ -66738,25 +66678,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY311" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AZ311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BA311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY311" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA311" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB311" t="n">
+        <v>1</v>
       </c>
       <c r="BC311" t="inlineStr"/>
       <c r="BD311" t="inlineStr"/>
@@ -66768,15 +66700,11 @@
       <c r="BJ311" t="inlineStr"/>
       <c r="BK311" t="inlineStr"/>
       <c r="BL311" t="inlineStr"/>
-      <c r="BM311" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BN311" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BM311" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN311" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="312">
@@ -66812,15 +66740,11 @@
           <t>75 000</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G312" t="n">
+        <v>4</v>
+      </c>
+      <c r="H312" t="n">
+        <v>4</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -66842,15 +66766,11 @@
           <t>Juventus</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
+      <c r="M312" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N312" t="n">
+        <v>2.17</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -66862,135 +66782,83 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q312" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R312" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X312" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y312" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA312" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE312" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AF312" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ312" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK312" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL312" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM312" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AN312" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AO312" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="AP312" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
+      <c r="Q312" t="n">
+        <v>18</v>
+      </c>
+      <c r="R312" t="n">
+        <v>10</v>
+      </c>
+      <c r="S312" t="n">
+        <v>9</v>
+      </c>
+      <c r="T312" t="n">
+        <v>5</v>
+      </c>
+      <c r="U312" t="n">
+        <v>4</v>
+      </c>
+      <c r="V312" t="n">
+        <v>3</v>
+      </c>
+      <c r="W312" t="n">
+        <v>5</v>
+      </c>
+      <c r="X312" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>383</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>445</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>327</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>392</v>
       </c>
       <c r="AQ312" t="inlineStr">
         <is>
@@ -67026,15 +66894,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AZ312" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>2</v>
       </c>
       <c r="BA312" t="inlineStr"/>
       <c r="BB312" t="inlineStr"/>
@@ -67048,15 +66912,11 @@
       <c r="BJ312" t="inlineStr"/>
       <c r="BK312" t="inlineStr"/>
       <c r="BL312" t="inlineStr"/>
-      <c r="BM312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BN312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BM312" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN312" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="313">
@@ -67092,15 +66952,11 @@
           <t>40 000</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G313" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -67122,15 +66978,11 @@
           <t>Genoa</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
+      <c r="M313" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0.27</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -67142,135 +66994,83 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q313" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R313" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T313" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA313" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE313" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG313" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM313" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="AN313" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="AO313" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="AP313" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
+      <c r="Q313" t="n">
+        <v>18</v>
+      </c>
+      <c r="R313" t="n">
+        <v>6</v>
+      </c>
+      <c r="S313" t="n">
+        <v>4</v>
+      </c>
+      <c r="T313" t="n">
+        <v>2</v>
+      </c>
+      <c r="U313" t="n">
+        <v>10</v>
+      </c>
+      <c r="V313" t="n">
+        <v>4</v>
+      </c>
+      <c r="W313" t="n">
+        <v>4</v>
+      </c>
+      <c r="X313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>550</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>352</v>
+      </c>
+      <c r="AO313" t="n">
+        <v>486</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>276</v>
       </c>
       <c r="AQ313" t="inlineStr">
         <is>
@@ -67306,15 +67106,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY313" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AZ313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AY313" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ313" t="n">
+        <v>3</v>
       </c>
       <c r="BA313" t="inlineStr"/>
       <c r="BB313" t="inlineStr"/>
@@ -67328,15 +67124,11 @@
       <c r="BJ313" t="inlineStr"/>
       <c r="BK313" t="inlineStr"/>
       <c r="BL313" t="inlineStr"/>
-      <c r="BM313" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BN313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BM313" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN313" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="314">
@@ -67372,15 +67164,11 @@
           <t>10 141</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" t="n">
+        <v>2</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -67402,15 +67190,11 @@
           <t>Venezia</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+      <c r="M314" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.58</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -67422,135 +67206,83 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="AN314" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="AO314" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="AP314" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
+      <c r="Q314" t="n">
+        <v>13</v>
+      </c>
+      <c r="R314" t="n">
+        <v>6</v>
+      </c>
+      <c r="S314" t="n">
+        <v>2</v>
+      </c>
+      <c r="T314" t="n">
+        <v>2</v>
+      </c>
+      <c r="U314" t="n">
+        <v>8</v>
+      </c>
+      <c r="V314" t="n">
+        <v>2</v>
+      </c>
+      <c r="W314" t="n">
+        <v>3</v>
+      </c>
+      <c r="X314" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>347</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>416</v>
+      </c>
+      <c r="AO314" t="n">
+        <v>273</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>338</v>
       </c>
       <c r="AQ314" t="inlineStr">
         <is>
@@ -67586,25 +67318,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY314" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AZ314" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BA314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BB314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY314" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ314" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA314" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB314" t="n">
+        <v>0</v>
       </c>
       <c r="BC314" t="inlineStr"/>
       <c r="BD314" t="inlineStr"/>
@@ -67616,15 +67340,11 @@
       <c r="BJ314" t="inlineStr"/>
       <c r="BK314" t="inlineStr"/>
       <c r="BL314" t="inlineStr"/>
-      <c r="BM314" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BN314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BM314" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN314" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="315">
@@ -67660,15 +67380,11 @@
           <t>17 802</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G315" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -67690,15 +67406,11 @@
           <t>Empoli</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
+      <c r="M315" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0.13</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -67710,135 +67422,83 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="AN315" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+      <c r="Q315" t="n">
+        <v>17</v>
+      </c>
+      <c r="R315" t="n">
+        <v>6</v>
+      </c>
+      <c r="S315" t="n">
+        <v>4</v>
+      </c>
+      <c r="T315" t="n">
+        <v>2</v>
+      </c>
+      <c r="U315" t="n">
+        <v>8</v>
+      </c>
+      <c r="V315" t="n">
+        <v>4</v>
+      </c>
+      <c r="W315" t="n">
+        <v>5</v>
+      </c>
+      <c r="X315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>527</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>350</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>279</v>
       </c>
       <c r="AQ315" t="inlineStr">
         <is>
@@ -67874,15 +67534,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AZ315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ315" t="n">
+        <v>1</v>
       </c>
       <c r="BA315" t="inlineStr"/>
       <c r="BB315" t="inlineStr"/>
@@ -67896,15 +67552,11 @@
       <c r="BJ315" t="inlineStr"/>
       <c r="BK315" t="inlineStr"/>
       <c r="BL315" t="inlineStr"/>
-      <c r="BM315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BN315" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BM315" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN315" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="316">
@@ -67936,15 +67588,11 @@
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -67978,135 +67626,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q316" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R316" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="AN316" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AO316" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AP316" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
+      <c r="Q316" t="n">
+        <v>10</v>
+      </c>
+      <c r="R316" t="n">
+        <v>11</v>
+      </c>
+      <c r="S316" t="n">
+        <v>6</v>
+      </c>
+      <c r="T316" t="n">
+        <v>1</v>
+      </c>
+      <c r="U316" t="n">
+        <v>2</v>
+      </c>
+      <c r="V316" t="n">
+        <v>8</v>
+      </c>
+      <c r="W316" t="n">
+        <v>2</v>
+      </c>
+      <c r="X316" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>497</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>383</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>442</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>343</v>
       </c>
       <c r="AQ316" t="inlineStr">
         <is>
@@ -68152,15 +67748,11 @@
       <c r="BF316" t="inlineStr"/>
       <c r="BG316" t="inlineStr"/>
       <c r="BH316" t="inlineStr"/>
-      <c r="BI316" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BJ316" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BI316" t="n">
+        <v>19</v>
+      </c>
+      <c r="BJ316" t="n">
+        <v>15</v>
       </c>
       <c r="BK316" t="inlineStr"/>
       <c r="BL316" t="inlineStr"/>
@@ -68196,15 +67788,11 @@
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -68238,135 +67826,83 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="AN317" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="AO317" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AP317" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
+      <c r="Q317" t="n">
+        <v>11</v>
+      </c>
+      <c r="R317" t="n">
+        <v>20</v>
+      </c>
+      <c r="S317" t="n">
+        <v>3</v>
+      </c>
+      <c r="T317" t="n">
+        <v>4</v>
+      </c>
+      <c r="U317" t="n">
+        <v>6</v>
+      </c>
+      <c r="V317" t="n">
+        <v>11</v>
+      </c>
+      <c r="W317" t="n">
+        <v>2</v>
+      </c>
+      <c r="X317" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>485</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>423</v>
       </c>
       <c r="AQ317" t="inlineStr">
         <is>
@@ -68404,15 +67940,11 @@
       </c>
       <c r="AY317" t="inlineStr"/>
       <c r="AZ317" t="inlineStr"/>
-      <c r="BA317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BB317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BA317" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB317" t="n">
+        <v>0</v>
       </c>
       <c r="BC317" t="inlineStr"/>
       <c r="BD317" t="inlineStr"/>
@@ -68420,15 +67952,11 @@
       <c r="BF317" t="inlineStr"/>
       <c r="BG317" t="inlineStr"/>
       <c r="BH317" t="inlineStr"/>
-      <c r="BI317" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BJ317" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="BI317" t="n">
+        <v>27</v>
+      </c>
+      <c r="BJ317" t="n">
+        <v>30</v>
       </c>
       <c r="BK317" t="inlineStr"/>
       <c r="BL317" t="inlineStr"/>
@@ -68464,15 +67992,11 @@
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -68506,135 +68030,83 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AG318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI318" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ318" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM318" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="AN318" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="AO318" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="AP318" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
+      <c r="Q318" t="n">
+        <v>20</v>
+      </c>
+      <c r="R318" t="n">
+        <v>11</v>
+      </c>
+      <c r="S318" t="n">
+        <v>7</v>
+      </c>
+      <c r="T318" t="n">
+        <v>5</v>
+      </c>
+      <c r="U318" t="n">
+        <v>9</v>
+      </c>
+      <c r="V318" t="n">
+        <v>2</v>
+      </c>
+      <c r="W318" t="n">
+        <v>4</v>
+      </c>
+      <c r="X318" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>258</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>616</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>189</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>555</v>
       </c>
       <c r="AQ318" t="inlineStr">
         <is>
@@ -68680,21 +68152,5505 @@
       <c r="BF318" t="inlineStr"/>
       <c r="BG318" t="inlineStr"/>
       <c r="BH318" t="inlineStr"/>
-      <c r="BI318" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BJ318" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BI318" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ318" t="n">
+        <v>9</v>
       </c>
       <c r="BK318" t="inlineStr"/>
       <c r="BL318" t="inlineStr"/>
       <c r="BM318" t="inlineStr"/>
       <c r="BN318" t="inlineStr"/>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>60 920</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="AN319" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AT319" t="inlineStr">
+        <is>
+          <t>vanoli paolo</t>
+        </is>
+      </c>
+      <c r="AU319" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV319" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr"/>
+      <c r="BB319" t="inlineStr"/>
+      <c r="BC319" t="inlineStr"/>
+      <c r="BD319" t="inlineStr"/>
+      <c r="BE319" t="inlineStr"/>
+      <c r="BF319" t="inlineStr"/>
+      <c r="BG319" t="inlineStr"/>
+      <c r="BH319" t="inlineStr"/>
+      <c r="BI319" t="inlineStr"/>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+      <c r="BM319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BN319" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>10 750</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AN320" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AT320" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AU320" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV320" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr"/>
+      <c r="BD320" t="inlineStr"/>
+      <c r="BE320" t="inlineStr"/>
+      <c r="BF320" t="inlineStr"/>
+      <c r="BG320" t="inlineStr"/>
+      <c r="BH320" t="inlineStr"/>
+      <c r="BI320" t="inlineStr"/>
+      <c r="BJ320" t="inlineStr"/>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="inlineStr"/>
+      <c r="BM320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BN320" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>31.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>30 254</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AN321" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AT321" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="AU321" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV321" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr"/>
+      <c r="BB321" t="inlineStr"/>
+      <c r="BC321" t="inlineStr"/>
+      <c r="BD321" t="inlineStr"/>
+      <c r="BE321" t="inlineStr"/>
+      <c r="BF321" t="inlineStr"/>
+      <c r="BG321" t="inlineStr"/>
+      <c r="BH321" t="inlineStr"/>
+      <c r="BI321" t="inlineStr"/>
+      <c r="BJ321" t="inlineStr"/>
+      <c r="BK321" t="inlineStr"/>
+      <c r="BL321" t="inlineStr"/>
+      <c r="BM321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BN321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>22 142</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM322" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="AN322" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AT322" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AU322" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr"/>
+      <c r="BB322" t="inlineStr"/>
+      <c r="BC322" t="inlineStr"/>
+      <c r="BD322" t="inlineStr"/>
+      <c r="BE322" t="inlineStr"/>
+      <c r="BF322" t="inlineStr"/>
+      <c r="BG322" t="inlineStr"/>
+      <c r="BH322" t="inlineStr"/>
+      <c r="BI322" t="inlineStr"/>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+      <c r="BM322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BN322" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>40 809</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="AN323" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AT323" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AU323" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr"/>
+      <c r="BB323" t="inlineStr"/>
+      <c r="BC323" t="inlineStr"/>
+      <c r="BD323" t="inlineStr"/>
+      <c r="BE323" t="inlineStr"/>
+      <c r="BF323" t="inlineStr"/>
+      <c r="BG323" t="inlineStr"/>
+      <c r="BH323" t="inlineStr"/>
+      <c r="BI323" t="inlineStr"/>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+      <c r="BM323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BN323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>15 706</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="AN324" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AT324" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="AU324" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr"/>
+      <c r="BD324" t="inlineStr"/>
+      <c r="BE324" t="inlineStr"/>
+      <c r="BF324" t="inlineStr"/>
+      <c r="BG324" t="inlineStr"/>
+      <c r="BH324" t="inlineStr"/>
+      <c r="BI324" t="inlineStr"/>
+      <c r="BJ324" t="inlineStr"/>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="inlineStr"/>
+      <c r="BM324" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BN324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM325" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="AN325" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AQ325" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AT325" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AU325" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV325" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr"/>
+      <c r="BD325" t="inlineStr"/>
+      <c r="BE325" t="inlineStr"/>
+      <c r="BF325" t="inlineStr"/>
+      <c r="BG325" t="inlineStr"/>
+      <c r="BH325" t="inlineStr"/>
+      <c r="BI325" t="inlineStr"/>
+      <c r="BJ325" t="inlineStr"/>
+      <c r="BK325" t="inlineStr"/>
+      <c r="BL325" t="inlineStr"/>
+      <c r="BM325" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BN325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>73 507</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM326" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="AN326" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AR326" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AT326" t="inlineStr">
+        <is>
+          <t>conte antonio</t>
+        </is>
+      </c>
+      <c r="AU326" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV326" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr"/>
+      <c r="BB326" t="inlineStr"/>
+      <c r="BC326" t="inlineStr"/>
+      <c r="BD326" t="inlineStr"/>
+      <c r="BE326" t="inlineStr"/>
+      <c r="BF326" t="inlineStr"/>
+      <c r="BG326" t="inlineStr"/>
+      <c r="BH326" t="inlineStr"/>
+      <c r="BI326" t="inlineStr"/>
+      <c r="BJ326" t="inlineStr"/>
+      <c r="BK326" t="inlineStr"/>
+      <c r="BL326" t="inlineStr"/>
+      <c r="BM326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BN326" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>15 977</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AN327" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AT327" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="AU327" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV327" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr"/>
+      <c r="BB327" t="inlineStr"/>
+      <c r="BC327" t="inlineStr"/>
+      <c r="BD327" t="inlineStr"/>
+      <c r="BE327" t="inlineStr"/>
+      <c r="BF327" t="inlineStr"/>
+      <c r="BG327" t="inlineStr"/>
+      <c r="BH327" t="inlineStr"/>
+      <c r="BI327" t="inlineStr"/>
+      <c r="BJ327" t="inlineStr"/>
+      <c r="BK327" t="inlineStr"/>
+      <c r="BL327" t="inlineStr"/>
+      <c r="BM327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BN327" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>23 698</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM328" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AN328" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AR328" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AT328" t="inlineStr">
+        <is>
+          <t>zanetti paolo</t>
+        </is>
+      </c>
+      <c r="AU328" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV328" t="n">
+        <v>771</v>
+      </c>
+      <c r="AW328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr"/>
+      <c r="BD328" t="inlineStr"/>
+      <c r="BE328" t="inlineStr"/>
+      <c r="BF328" t="inlineStr"/>
+      <c r="BG328" t="inlineStr"/>
+      <c r="BH328" t="inlineStr"/>
+      <c r="BI328" t="inlineStr"/>
+      <c r="BJ328" t="inlineStr"/>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="inlineStr"/>
+      <c r="BM328" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BN328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>YHET3e9L</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Santoro A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AN329" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>dal canto alessandro</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AT329" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AU329" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV329" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr"/>
+      <c r="BA329" t="inlineStr"/>
+      <c r="BB329" t="inlineStr"/>
+      <c r="BC329" t="inlineStr"/>
+      <c r="BD329" t="inlineStr"/>
+      <c r="BE329" t="inlineStr"/>
+      <c r="BF329" t="inlineStr"/>
+      <c r="BG329" t="inlineStr"/>
+      <c r="BH329" t="inlineStr"/>
+      <c r="BI329" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BJ329" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BK329" t="inlineStr"/>
+      <c r="BL329" t="inlineStr"/>
+      <c r="BM329" t="inlineStr"/>
+      <c r="BN329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>QFg8dD1e</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Stadio Danilo Martelli
+ (Mantova)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL330" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM330" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AN330" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AR330" t="inlineStr">
+        <is>
+          <t>possanzini davide</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AT330" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AU330" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV330" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr"/>
+      <c r="BA330" t="inlineStr"/>
+      <c r="BB330" t="inlineStr"/>
+      <c r="BC330" t="inlineStr"/>
+      <c r="BD330" t="inlineStr"/>
+      <c r="BE330" t="inlineStr"/>
+      <c r="BF330" t="inlineStr"/>
+      <c r="BG330" t="inlineStr"/>
+      <c r="BH330" t="inlineStr"/>
+      <c r="BI330" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ330" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BK330" t="inlineStr"/>
+      <c r="BL330" t="inlineStr"/>
+      <c r="BM330" t="inlineStr"/>
+      <c r="BN330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>C8Z2IfOE</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="AN331" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AR331" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AT331" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="AU331" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV331" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr"/>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr"/>
+      <c r="BD331" t="inlineStr"/>
+      <c r="BE331" t="inlineStr"/>
+      <c r="BF331" t="inlineStr"/>
+      <c r="BG331" t="inlineStr"/>
+      <c r="BH331" t="inlineStr"/>
+      <c r="BI331" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BJ331" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="inlineStr"/>
+      <c r="BM331" t="inlineStr"/>
+      <c r="BN331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>CWHk9jo1</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM332" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AN332" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AQ332" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AR332" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr">
+        <is>
+          <t>6gFji4JC</t>
+        </is>
+      </c>
+      <c r="AT332" t="inlineStr">
+        <is>
+          <t>greco leandro</t>
+        </is>
+      </c>
+      <c r="AU332" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV332" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr"/>
+      <c r="BA332" t="inlineStr"/>
+      <c r="BB332" t="inlineStr"/>
+      <c r="BC332" t="inlineStr"/>
+      <c r="BD332" t="inlineStr"/>
+      <c r="BE332" t="inlineStr"/>
+      <c r="BF332" t="inlineStr"/>
+      <c r="BG332" t="inlineStr"/>
+      <c r="BH332" t="inlineStr"/>
+      <c r="BI332" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BJ332" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="inlineStr"/>
+      <c r="BM332" t="inlineStr"/>
+      <c r="BN332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>WhYYsEn2</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>14 603</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="AN333" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AT333" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AU333" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV333" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr"/>
+      <c r="BA333" t="inlineStr"/>
+      <c r="BB333" t="inlineStr"/>
+      <c r="BC333" t="inlineStr"/>
+      <c r="BD333" t="inlineStr"/>
+      <c r="BE333" t="inlineStr"/>
+      <c r="BF333" t="inlineStr"/>
+      <c r="BG333" t="inlineStr"/>
+      <c r="BH333" t="inlineStr"/>
+      <c r="BI333" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BJ333" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="BK333" t="inlineStr"/>
+      <c r="BL333" t="inlineStr"/>
+      <c r="BM333" t="inlineStr"/>
+      <c r="BN333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>xjLK5Hv9</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>5 181</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM334" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN334" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AT334" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AU334" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV334" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr"/>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr"/>
+      <c r="BD334" t="inlineStr"/>
+      <c r="BE334" t="inlineStr"/>
+      <c r="BF334" t="inlineStr"/>
+      <c r="BG334" t="inlineStr"/>
+      <c r="BH334" t="inlineStr"/>
+      <c r="BI334" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BJ334" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BK334" t="inlineStr"/>
+      <c r="BL334" t="inlineStr"/>
+      <c r="BM334" t="inlineStr"/>
+      <c r="BN334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>Um0abZWr</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Stadio Romeo Menti
+ (Castellammare di Stabia)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>13 000</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>4 589</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AN335" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AP335" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AQ335" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AR335" t="inlineStr">
+        <is>
+          <t>pagliuca guido</t>
+        </is>
+      </c>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AT335" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AU335" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV335" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr"/>
+      <c r="BA335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC335" t="inlineStr"/>
+      <c r="BD335" t="inlineStr"/>
+      <c r="BE335" t="inlineStr"/>
+      <c r="BF335" t="inlineStr"/>
+      <c r="BG335" t="inlineStr"/>
+      <c r="BH335" t="inlineStr"/>
+      <c r="BI335" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BJ335" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="inlineStr"/>
+      <c r="BM335" t="inlineStr"/>
+      <c r="BN335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WCdGfiW7</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>8 251</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM336" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="AN336" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="AO336" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="AP336" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AR336" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr">
+        <is>
+          <t>AgMBZSTl</t>
+        </is>
+      </c>
+      <c r="AT336" t="inlineStr">
+        <is>
+          <t>corini eugenio</t>
+        </is>
+      </c>
+      <c r="AU336" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV336" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr"/>
+      <c r="BA336" t="inlineStr"/>
+      <c r="BB336" t="inlineStr"/>
+      <c r="BC336" t="inlineStr"/>
+      <c r="BD336" t="inlineStr"/>
+      <c r="BE336" t="inlineStr"/>
+      <c r="BF336" t="inlineStr"/>
+      <c r="BG336" t="inlineStr"/>
+      <c r="BH336" t="inlineStr"/>
+      <c r="BI336" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BJ336" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BK336" t="inlineStr"/>
+      <c r="BL336" t="inlineStr"/>
+      <c r="BM336" t="inlineStr"/>
+      <c r="BN336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>KYxBGYhR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Monaldi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>8 529</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL337" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AN337" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AT337" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AU337" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV337" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX337" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr"/>
+      <c r="BA337" t="inlineStr"/>
+      <c r="BB337" t="inlineStr"/>
+      <c r="BC337" t="inlineStr"/>
+      <c r="BD337" t="inlineStr"/>
+      <c r="BE337" t="inlineStr"/>
+      <c r="BF337" t="inlineStr"/>
+      <c r="BG337" t="inlineStr"/>
+      <c r="BH337" t="inlineStr"/>
+      <c r="BI337" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BJ337" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BK337" t="inlineStr"/>
+      <c r="BL337" t="inlineStr"/>
+      <c r="BM337" t="inlineStr"/>
+      <c r="BN337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>vJJsBCGl</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>10 141</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM338" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AN338" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AO338" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="AP338" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AR338" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AT338" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AU338" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV338" t="n">
+        <v>774</v>
+      </c>
+      <c r="AW338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr"/>
+      <c r="BA338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC338" t="inlineStr"/>
+      <c r="BD338" t="inlineStr"/>
+      <c r="BE338" t="inlineStr"/>
+      <c r="BF338" t="inlineStr"/>
+      <c r="BG338" t="inlineStr"/>
+      <c r="BH338" t="inlineStr"/>
+      <c r="BI338" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BJ338" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BK338" t="inlineStr"/>
+      <c r="BL338" t="inlineStr"/>
+      <c r="BM338" t="inlineStr"/>
+      <c r="BN338" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
